--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597E7291-0AF7-4835-8414-9D5551DBF842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9B4146-92C4-446E-A1A7-77CA03C45A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-67" yWindow="-67" windowWidth="25734" windowHeight="13814" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="6453" yWindow="2853" windowWidth="19020" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -1456,10 +1456,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;るい&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>飯田沙耶
 上谷沙弥
 向後桃
@@ -1748,6 +1744,13 @@
       <t>インタイ</t>
     </rPh>
     <rPh sb="11" eb="13">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;陽岬来永&gt;(2.10デビュー予定)</t>
+    <rPh sb="15" eb="17">
       <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -3041,7 +3044,7 @@
         <v>57</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>51</v>
@@ -4211,7 +4214,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4289,7 +4292,7 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z40" s="3"/>
       <c r="AD40" s="1"/>
@@ -4374,7 +4377,7 @@
         <v>141</v>
       </c>
       <c r="Z42" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD42" s="1"/>
     </row>
@@ -4383,7 +4386,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4423,7 +4426,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
@@ -4454,7 +4457,7 @@
         <v>124</v>
       </c>
       <c r="Z44" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AD44" s="1"/>
     </row>
@@ -4463,7 +4466,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4486,7 +4489,7 @@
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
@@ -4513,7 +4516,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>172</v>
@@ -4557,7 +4560,7 @@
         <v>101</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Z46" s="3" t="s">
         <v>149</v>
@@ -4569,7 +4572,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4583,7 +4586,7 @@
         <v>23</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>73</v>
@@ -4612,7 +4615,7 @@
         <v>174</v>
       </c>
       <c r="Z47" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AD47" s="1"/>
     </row>
@@ -4666,7 +4669,7 @@
         <v>50</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>45</v>
@@ -4715,7 +4718,7 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>164</v>
@@ -4774,16 +4777,16 @@
         <v>25</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>112</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>117</v>
@@ -4897,10 +4900,10 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>188</v>
@@ -4919,7 +4922,7 @@
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -4928,7 +4931,7 @@
         <v>200</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>184</v>
@@ -4945,7 +4948,7 @@
         <v>145</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="3" t="s">
@@ -4961,7 +4964,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
@@ -4969,7 +4972,7 @@
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
@@ -4994,10 +4997,10 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
@@ -5007,7 +5010,7 @@
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5019,7 +5022,7 @@
         <v>187</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
@@ -5029,7 +5032,7 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z55" s="3"/>
       <c r="AD55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9B4146-92C4-446E-A1A7-77CA03C45A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21542709-48B8-417D-AAD3-4AE262AFE736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6453" yWindow="2853" windowWidth="19020" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1537,35 +1537,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>櫻井裕子(COLORS)
-網倉理奈(COLORS)
-KONOHA(銀河)(2026.5引退予定)
-花園桃花(アップタウン)
-杏ちゃむ(信州, DIE)</t>
-    <rPh sb="0" eb="4">
-      <t>サクライユウコ</t>
-    </rPh>
-    <rPh sb="13" eb="17">
-      <t>アミクラリナ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ギンガ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>インタイ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ヨテイ</t>
-    </rPh>
-    <rPh sb="49" eb="53">
-      <t>ハナゾノモモカ</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>シンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>稲葉ともか</t>
     <rPh sb="0" eb="2">
       <t>イナバ</t>
@@ -1752,6 +1723,35 @@
     <t>&lt;陽岬来永&gt;(2.10デビュー予定)</t>
     <rPh sb="15" eb="17">
       <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>櫻井裕子(COLORS)
+網倉理奈(COLORS)
+KONOHA(銀河)(2026.5.24引退予定)
+花園桃花(アップタウン)
+杏ちゃむ(信州, DIE)</t>
+    <rPh sb="0" eb="4">
+      <t>サクライユウコ</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>アミクラリナ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ギンガ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>インタイ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="52" eb="56">
+      <t>ハナゾノモモカ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>シンシュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3044,7 +3044,7 @@
         <v>57</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>51</v>
@@ -4214,7 +4214,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4292,7 +4292,7 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Z40" s="3"/>
       <c r="AD40" s="1"/>
@@ -4377,7 +4377,7 @@
         <v>141</v>
       </c>
       <c r="Z42" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AD42" s="1"/>
     </row>
@@ -4386,7 +4386,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4426,7 +4426,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
@@ -4457,7 +4457,7 @@
         <v>124</v>
       </c>
       <c r="Z44" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AD44" s="1"/>
     </row>
@@ -4466,7 +4466,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4489,7 +4489,7 @@
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
@@ -4560,7 +4560,7 @@
         <v>101</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="Z46" s="3" t="s">
         <v>149</v>
@@ -4586,7 +4586,7 @@
         <v>23</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>73</v>
@@ -4615,7 +4615,7 @@
         <v>174</v>
       </c>
       <c r="Z47" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AD47" s="1"/>
     </row>
@@ -4669,7 +4669,7 @@
         <v>50</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>45</v>
@@ -4718,7 +4718,7 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>164</v>
@@ -4783,7 +4783,7 @@
         <v>112</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>205</v>
@@ -4900,7 +4900,7 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>207</v>
@@ -4931,7 +4931,7 @@
         <v>200</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>184</v>
@@ -4964,7 +4964,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
@@ -4972,7 +4972,7 @@
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
@@ -4997,10 +4997,10 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5022,7 +5022,7 @@
         <v>187</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
@@ -5032,7 +5032,7 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z55" s="3"/>
       <c r="AD55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21542709-48B8-417D-AAD3-4AE262AFE736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2852EE14-0217-4D4D-8FE2-3AB327E0B4F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6453" yWindow="2853" windowWidth="19020" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -493,16 +493,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>松本都</t>
-    <rPh sb="0" eb="2">
-      <t>マツモト</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ミヤコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>桜花由美</t>
     <rPh sb="0" eb="4">
       <t>オウカユミ</t>
@@ -1406,23 +1396,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>藤本つかさ(IR)(休)
-星ハム子(IR)(休)</t>
-    <rPh sb="0" eb="2">
-      <t>フジモト</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ホシ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>コ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>優華(IR,V)</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1752,6 +1725,27 @@
     </rPh>
     <rPh sb="70" eb="72">
       <t>シンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>星ハム子(IR)(休)</t>
+    <rPh sb="0" eb="1">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>松本都
+藤本つかさ(休)</t>
+    <rPh sb="0" eb="2">
+      <t>マツモト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミヤコ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2785,7 +2779,7 @@
   <sheetData>
     <row r="1" spans="1:30" ht="16" x14ac:dyDescent="0.8">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2844,7 +2838,7 @@
      LEN(G5:G1001) - LEN(SUBSTITUTE(G5:G1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H2" s="1" cm="1">
         <f t="array" ref="H2">SUMPRODUCT(
@@ -2996,7 +2990,7 @@
      LEN(Z5:Z1001) - LEN(SUBSTITUTE(Z5:Z1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD2" s="1"/>
     </row>
@@ -3032,7 +3026,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>17</v>
@@ -3044,19 +3038,19 @@
         <v>57</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>19</v>
@@ -3071,19 +3065,19 @@
         <v>7</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Y4" s="2" t="s">
         <v>35</v>
@@ -3366,7 +3360,7 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Z13" s="3"/>
       <c r="AD13" s="1"/>
@@ -3435,7 +3429,7 @@
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD15" s="1"/>
     </row>
@@ -3500,10 +3494,10 @@
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Z17" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AD17" s="1"/>
     </row>
@@ -3686,7 +3680,7 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>64</v>
@@ -3721,7 +3715,7 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AD24" s="1"/>
     </row>
@@ -3740,7 +3734,7 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -3755,7 +3749,7 @@
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD25" s="1"/>
     </row>
@@ -3786,7 +3780,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>32</v>
@@ -3822,7 +3816,7 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Z27" s="3"/>
       <c r="AD27" s="1"/>
@@ -3844,7 +3838,7 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -3859,7 +3853,7 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AD28" s="1"/>
     </row>
@@ -3885,7 +3879,7 @@
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
@@ -3924,7 +3918,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z30" s="3"/>
       <c r="AD30" s="1"/>
@@ -3989,7 +3983,7 @@
         <v>60</v>
       </c>
       <c r="Z32" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD32" s="1"/>
     </row>
@@ -4014,7 +4008,7 @@
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
@@ -4022,7 +4016,7 @@
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Z33" s="3"/>
       <c r="AD33" s="1"/>
@@ -4036,19 +4030,19 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>52</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
@@ -4065,7 +4059,7 @@
       </c>
       <c r="Y34" s="3"/>
       <c r="Z34" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AD34" s="1"/>
     </row>
@@ -4095,11 +4089,11 @@
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
       <c r="X35" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AD35" s="1"/>
     </row>
@@ -4108,13 +4102,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4137,7 +4131,7 @@
       </c>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3" t="s">
-        <v>65</v>
+        <v>231</v>
       </c>
       <c r="AD36" s="1"/>
     </row>
@@ -4185,7 +4179,7 @@
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
@@ -4204,7 +4198,7 @@
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z38" s="3"/>
       <c r="AD38" s="1"/>
@@ -4214,22 +4208,22 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
@@ -4245,11 +4239,11 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AD39" s="1"/>
     </row>
@@ -4258,16 +4252,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4276,7 +4270,7 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N40" s="3" t="s">
         <v>1</v>
@@ -4292,7 +4286,7 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Z40" s="3"/>
       <c r="AD40" s="1"/>
@@ -4302,21 +4296,21 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4333,13 +4327,13 @@
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
       <c r="X41" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Z41" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AD41" s="1"/>
     </row>
@@ -4348,7 +4342,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4374,10 +4368,10 @@
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
       <c r="Y42" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Z42" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AD42" s="1"/>
     </row>
@@ -4386,7 +4380,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4413,11 +4407,11 @@
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Y43" s="3"/>
       <c r="Z43" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AD43" s="1"/>
     </row>
@@ -4426,7 +4420,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
@@ -4454,10 +4448,10 @@
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
       <c r="Y44" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z44" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AD44" s="1"/>
     </row>
@@ -4466,7 +4460,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4474,40 +4468,40 @@
         <v>12</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
       <c r="X45" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Z45" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AD45" s="1"/>
     </row>
@@ -4516,13 +4510,13 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>14</v>
@@ -4531,12 +4525,12 @@
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>29</v>
@@ -4545,25 +4539,25 @@
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W46" s="3"/>
       <c r="X46" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Z46" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AD46" s="1"/>
     </row>
@@ -4572,7 +4566,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4580,23 +4574,23 @@
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
         <v>54</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -4607,15 +4601,15 @@
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="W47" s="3"/>
       <c r="X47" s="3"/>
       <c r="Y47" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Z47" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AD47" s="1"/>
     </row>
@@ -4638,7 +4632,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
@@ -4646,7 +4640,7 @@
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
       <c r="S48" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
@@ -4654,10 +4648,10 @@
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
       <c r="Y48" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Z48" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AD48" s="1"/>
     </row>
@@ -4669,7 +4663,7 @@
         <v>50</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>45</v>
@@ -4678,11 +4672,11 @@
         <v>11</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
@@ -4697,18 +4691,18 @@
         <v>62</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="X49" s="3"/>
       <c r="Y49" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Z49" s="3"/>
       <c r="AD49" s="1"/>
@@ -4718,37 +4712,37 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4758,14 +4752,14 @@
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
       <c r="W50" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X50" s="3"/>
       <c r="Y50" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Z50" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AD50" s="1"/>
     </row>
@@ -4777,59 +4771,59 @@
         <v>25</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>49</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
       <c r="O51" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="X51" s="3"/>
       <c r="Y51" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Z51" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD51" s="1"/>
     </row>
@@ -4838,7 +4832,7 @@
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>34</v>
@@ -4847,32 +4841,32 @@
         <v>44</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G52" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="K52" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="L52" s="3"/>
       <c r="M52" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
@@ -4881,16 +4875,16 @@
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
       <c r="Y52" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Z52" s="3"/>
       <c r="AD52" s="1"/>
@@ -4900,59 +4894,59 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Z53" s="3"/>
       <c r="AD53" s="1"/>
@@ -4964,7 +4958,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
@@ -4972,7 +4966,7 @@
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
@@ -4993,36 +4987,36 @@
     </row>
     <row r="55" spans="2:30" ht="83.35" x14ac:dyDescent="0.8">
       <c r="B55" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
@@ -5032,7 +5026,7 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Z55" s="3"/>
       <c r="AD55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2852EE14-0217-4D4D-8FE2-3AB327E0B4F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF5BCF98-A8FB-4F90-ACF4-C7852E56879B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6453" yWindow="2853" windowWidth="19020" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1630,18 +1630,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;堀このみ&gt;(ZeroOne)26.2.7デビュー予定
-&lt;七世真理子&gt;(ZeroOne)
-&lt;星野 さやか&gt;(九州女子プロレス)</t>
-    <rPh sb="25" eb="27">
-      <t>ヨテイ</t>
-    </rPh>
-    <rPh sb="54" eb="58">
-      <t>キュウシュウジョシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>雪妃真矢(休)</t>
     <rPh sb="5" eb="6">
       <t>キュウ</t>
@@ -1746,6 +1734,31 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>ミヤコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;堀このみ&gt;(ZeroOne)26.2.7デビュー予定
+&lt;七世真理子&gt;(ZeroOne)
+&lt;星野 さやか&gt;(九州女子プロレス)
+&lt;今野結菜&gt;(伊藤道場)仮合格</t>
+    <rPh sb="25" eb="27">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="54" eb="58">
+      <t>キュウシュウジョシ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>イトウ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ドウジョウ</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>ゴウカク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2798,7 +2811,7 @@
     <row r="2" spans="1:30" ht="16" x14ac:dyDescent="0.8">
       <c r="B2" s="1">
         <f>SUM(C2:RZ2)</f>
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2982,7 +2995,7 @@
      LEN(Y5:Y1001) - LEN(SUBSTITUTE(Y5:Y1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Z2" s="1" cm="1">
         <f t="array" ref="Z2">SUMPRODUCT(
@@ -4108,7 +4121,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4131,7 +4144,7 @@
       </c>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AD36" s="1"/>
     </row>
@@ -4371,7 +4384,7 @@
         <v>140</v>
       </c>
       <c r="Z42" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AD42" s="1"/>
     </row>
@@ -4460,7 +4473,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4483,7 +4496,7 @@
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
@@ -4554,7 +4567,7 @@
         <v>100</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Z46" s="3" t="s">
         <v>148</v>
@@ -4663,7 +4676,7 @@
         <v>50</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>45</v>
@@ -4777,7 +4790,7 @@
         <v>111</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>203</v>
@@ -5016,7 +5029,7 @@
         <v>186</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
@@ -5026,7 +5039,7 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="Z55" s="3"/>
       <c r="AD55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF5BCF98-A8FB-4F90-ACF4-C7852E56879B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA539FCA-EC28-42CF-ABFB-86C01FB4683C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6453" yWindow="2853" windowWidth="19020" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -845,10 +845,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>鈴木ユラ(アルマリブレ)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>結奈(REINA)</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -938,15 +934,6 @@
     </rPh>
     <rPh sb="5" eb="6">
       <t>ナギサ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>真白優希
-柳川澄樺
-神姫楽ミサ</t>
-    <rPh sb="0" eb="4">
-      <t>マシロ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1738,28 +1725,38 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;堀このみ&gt;(ZeroOne)26.2.7デビュー予定
-&lt;七世真理子&gt;(ZeroOne)
+    <t>&lt;堀このみ&gt;(Rose)26.2.7デビュー予定
+&lt;七世真理子&gt;(Rose)
 &lt;星野 さやか&gt;(九州女子プロレス)
 &lt;今野結菜&gt;(伊藤道場)仮合格</t>
-    <rPh sb="25" eb="27">
+    <rPh sb="22" eb="24">
       <t>ヨテイ</t>
     </rPh>
-    <rPh sb="54" eb="58">
+    <rPh sb="48" eb="52">
       <t>キュウシュウジョシ</t>
     </rPh>
+    <rPh sb="65" eb="67">
+      <t>イトウ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>ドウジョウ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>カリ</t>
+    </rPh>
     <rPh sb="71" eb="73">
-      <t>イトウ</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>ドウジョウ</t>
-    </rPh>
-    <rPh sb="76" eb="77">
-      <t>カリ</t>
-    </rPh>
-    <rPh sb="77" eb="79">
       <t>ゴウカク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>柳川澄樺
+神姫楽ミサ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鈴木ユラ(アルマリブレ)
+真白優希(Rose)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2995,7 +2992,7 @@
      LEN(Y5:Y1001) - LEN(SUBSTITUTE(Y5:Y1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z2" s="1" cm="1">
         <f t="array" ref="Z2">SUMPRODUCT(
@@ -3003,7 +3000,7 @@
      LEN(Z5:Z1001) - LEN(SUBSTITUTE(Z5:Z1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD2" s="1"/>
     </row>
@@ -3051,7 +3048,7 @@
         <v>57</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>51</v>
@@ -3063,7 +3060,7 @@
         <v>8</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>19</v>
@@ -3078,16 +3075,16 @@
         <v>7</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>96</v>
@@ -3373,7 +3370,7 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z13" s="3"/>
       <c r="AD13" s="1"/>
@@ -3507,10 +3504,10 @@
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Z17" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD17" s="1"/>
     </row>
@@ -3693,7 +3690,7 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>64</v>
@@ -3728,7 +3725,7 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AD24" s="1"/>
     </row>
@@ -4029,7 +4026,7 @@
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Z33" s="3"/>
       <c r="AD33" s="1"/>
@@ -4043,13 +4040,13 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>52</v>
@@ -4106,7 +4103,7 @@
       </c>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AD35" s="1"/>
     </row>
@@ -4115,13 +4112,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4144,7 +4141,7 @@
       </c>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AD36" s="1"/>
     </row>
@@ -4221,7 +4218,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4256,7 +4253,7 @@
       </c>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AD39" s="1"/>
     </row>
@@ -4265,10 +4262,10 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>41</v>
@@ -4299,7 +4296,7 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Z40" s="3"/>
       <c r="AD40" s="1"/>
@@ -4313,17 +4310,17 @@
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4343,10 +4340,10 @@
         <v>101</v>
       </c>
       <c r="Y41" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z41" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="Z41" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="AD41" s="1"/>
     </row>
@@ -4355,7 +4352,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4381,10 +4378,10 @@
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
       <c r="Y42" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Z42" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AD42" s="1"/>
     </row>
@@ -4393,7 +4390,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4424,7 +4421,7 @@
       </c>
       <c r="Y43" s="3"/>
       <c r="Z43" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AD43" s="1"/>
     </row>
@@ -4433,7 +4430,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
@@ -4461,10 +4458,10 @@
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
       <c r="Y44" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Z44" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AD44" s="1"/>
     </row>
@@ -4473,7 +4470,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4484,7 +4481,7 @@
         <v>104</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -4496,13 +4493,13 @@
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
@@ -4511,7 +4508,7 @@
         <v>112</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>120</v>
@@ -4523,13 +4520,13 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>14</v>
@@ -4556,21 +4553,21 @@
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="W46" s="3"/>
       <c r="X46" s="3" t="s">
         <v>100</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Z46" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AD46" s="1"/>
     </row>
@@ -4579,7 +4576,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4593,7 +4590,7 @@
         <v>23</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>72</v>
@@ -4614,15 +4611,15 @@
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="W47" s="3"/>
       <c r="X47" s="3"/>
       <c r="Y47" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Z47" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AD47" s="1"/>
     </row>
@@ -4661,10 +4658,10 @@
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
       <c r="Y48" s="3" t="s">
-        <v>122</v>
+        <v>231</v>
       </c>
       <c r="Z48" s="3" t="s">
-        <v>139</v>
+        <v>230</v>
       </c>
       <c r="AD48" s="1"/>
     </row>
@@ -4676,7 +4673,7 @@
         <v>50</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>45</v>
@@ -4685,7 +4682,7 @@
         <v>11</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4711,11 +4708,11 @@
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="X49" s="3"/>
       <c r="Y49" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Z49" s="3"/>
       <c r="AD49" s="1"/>
@@ -4725,19 +4722,19 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>22</v>
@@ -4749,13 +4746,13 @@
         <v>73</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4765,14 +4762,14 @@
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
       <c r="W50" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="X50" s="3"/>
       <c r="Y50" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Z50" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AD50" s="1"/>
     </row>
@@ -4784,16 +4781,16 @@
         <v>25</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>111</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>116</v>
@@ -4806,7 +4803,7 @@
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
@@ -4814,29 +4811,29 @@
         <v>117</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="X51" s="3"/>
       <c r="Y51" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Z51" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AD51" s="1"/>
     </row>
@@ -4854,13 +4851,13 @@
         <v>44</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>78</v>
@@ -4869,7 +4866,7 @@
         <v>75</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L52" s="3"/>
       <c r="M52" s="3" t="s">
@@ -4879,7 +4876,7 @@
         <v>113</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
@@ -4888,16 +4885,16 @@
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
       <c r="Y52" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="Z52" s="3"/>
       <c r="AD52" s="1"/>
@@ -4907,13 +4904,13 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>110</v>
@@ -4922,44 +4919,44 @@
         <v>102</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Z53" s="3"/>
       <c r="AD53" s="1"/>
@@ -4971,7 +4968,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
@@ -4979,7 +4976,7 @@
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
@@ -5000,36 +4997,36 @@
     </row>
     <row r="55" spans="2:30" ht="83.35" x14ac:dyDescent="0.8">
       <c r="B55" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
@@ -5039,7 +5036,7 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Z55" s="3"/>
       <c r="AD55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA539FCA-EC28-42CF-ABFB-86C01FB4683C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE473FC-CD74-425B-B5CF-1FB3F4A68635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6453" yWindow="2853" windowWidth="19020" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="6453" yWindow="213" windowWidth="19020" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="233">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1725,38 +1725,38 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;堀このみ&gt;(Rose)26.2.7デビュー予定
-&lt;七世真理子&gt;(Rose)
+    <t>柳川澄樺
+神姫楽ミサ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鈴木ユラ(アルマリブレ)
+真白優希(Rose)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;七世真理子&gt;(Rose)
 &lt;星野 さやか&gt;(九州女子プロレス)
 &lt;今野結菜&gt;(伊藤道場)仮合格</t>
-    <rPh sb="22" eb="24">
-      <t>ヨテイ</t>
-    </rPh>
-    <rPh sb="48" eb="52">
+    <rPh sb="23" eb="27">
       <t>キュウシュウジョシ</t>
     </rPh>
-    <rPh sb="65" eb="67">
+    <rPh sb="40" eb="42">
       <t>イトウ</t>
     </rPh>
-    <rPh sb="67" eb="69">
+    <rPh sb="42" eb="44">
       <t>ドウジョウ</t>
     </rPh>
-    <rPh sb="70" eb="71">
+    <rPh sb="45" eb="46">
       <t>カリ</t>
     </rPh>
-    <rPh sb="71" eb="73">
+    <rPh sb="46" eb="48">
       <t>ゴウカク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>柳川澄樺
-神姫楽ミサ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>鈴木ユラ(アルマリブレ)
-真白優希(Rose)</t>
+    <t>&lt;堀このみ&gt;(Rose)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4658,10 +4658,10 @@
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
       <c r="Y48" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Z48" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AD48" s="1"/>
     </row>
@@ -4991,7 +4991,9 @@
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
-      <c r="Y54" s="3"/>
+      <c r="Y54" s="3" t="s">
+        <v>232</v>
+      </c>
       <c r="Z54" s="3"/>
       <c r="AD54" s="1"/>
     </row>
@@ -5036,7 +5038,7 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Z55" s="3"/>
       <c r="AD55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE473FC-CD74-425B-B5CF-1FB3F4A68635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295B71E9-A019-4E0D-8A34-3AB8F28EF317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6453" yWindow="213" windowWidth="19020" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1668,13 +1668,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;陽岬来永&gt;(2.10デビュー予定)</t>
-    <rPh sb="15" eb="17">
-      <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>櫻井裕子(COLORS)
 網倉理奈(COLORS)
 KONOHA(銀河)(2026.5.24引退予定)
@@ -1756,7 +1749,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;堀このみ&gt;(Rose)</t>
+    <t>堀このみ(Rose)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>陽岬来永</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4118,7 +4115,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4141,7 +4138,7 @@
       </c>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AD36" s="1"/>
     </row>
@@ -4564,7 +4561,7 @@
         <v>100</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z46" s="3" t="s">
         <v>146</v>
@@ -4658,10 +4655,10 @@
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
       <c r="Y48" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z48" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AD48" s="1"/>
     </row>
@@ -4983,7 +4980,9 @@
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
-      <c r="Q54" s="3"/>
+      <c r="Q54" s="3" t="s">
+        <v>232</v>
+      </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
@@ -4992,7 +4991,7 @@
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
       <c r="Y54" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Z54" s="3"/>
       <c r="AD54" s="1"/>
@@ -5027,9 +5026,7 @@
       <c r="P55" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="Q55" s="3" t="s">
-        <v>225</v>
-      </c>
+      <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
@@ -5038,7 +5035,7 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Z55" s="3"/>
       <c r="AD55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295B71E9-A019-4E0D-8A34-3AB8F28EF317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3045E3-3142-4C66-9BBE-973F2A209958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6453" yWindow="213" windowWidth="19020" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1310,19 +1310,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>苺畑ひより(666)
-横井真菜(REINA)
-タギリヒメ真夢(九州女子プロレス)
-彩月悠叶(2AW)</t>
-    <rPh sb="31" eb="33">
-      <t>キュウシュウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ジョシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>風南ユキ
 望天セレネ</t>
     <phoneticPr fontId="1"/>
@@ -1754,6 +1741,21 @@
   </si>
   <si>
     <t>陽岬来永</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>苺畑ひより(666)
+横井真菜(REINA)
+タギリヒメ真夢(九州女子プロレス)
+彩月悠叶(2AW)
+さいとう(アップタウン)
+しおの(アップタウン)</t>
+    <rPh sb="31" eb="33">
+      <t>キュウシュウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジョシ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2805,7 +2807,7 @@
     <row r="2" spans="1:30" ht="16" x14ac:dyDescent="0.8">
       <c r="B2" s="1">
         <f>SUM(C2:RZ2)</f>
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2989,7 +2991,7 @@
      LEN(Y5:Y1001) - LEN(SUBSTITUTE(Y5:Y1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Z2" s="1" cm="1">
         <f t="array" ref="Z2">SUMPRODUCT(
@@ -3045,7 +3047,7 @@
         <v>57</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>51</v>
@@ -3057,7 +3059,7 @@
         <v>8</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>19</v>
@@ -3687,7 +3689,7 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>64</v>
@@ -3722,7 +3724,7 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AD24" s="1"/>
     </row>
@@ -4115,7 +4117,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4138,7 +4140,7 @@
       </c>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD36" s="1"/>
     </row>
@@ -4215,7 +4217,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4293,7 +4295,7 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Z40" s="3"/>
       <c r="AD40" s="1"/>
@@ -4311,13 +4313,13 @@
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4349,7 +4351,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4378,7 +4380,7 @@
         <v>138</v>
       </c>
       <c r="Z42" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AD42" s="1"/>
     </row>
@@ -4387,7 +4389,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4427,7 +4429,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
@@ -4458,7 +4460,7 @@
         <v>122</v>
       </c>
       <c r="Z44" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AD44" s="1"/>
     </row>
@@ -4467,7 +4469,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4490,7 +4492,7 @@
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
@@ -4517,7 +4519,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>169</v>
@@ -4561,7 +4563,7 @@
         <v>100</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z46" s="3" t="s">
         <v>146</v>
@@ -4573,7 +4575,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4587,7 +4589,7 @@
         <v>23</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>72</v>
@@ -4616,7 +4618,7 @@
         <v>171</v>
       </c>
       <c r="Z47" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AD47" s="1"/>
     </row>
@@ -4655,10 +4657,10 @@
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
       <c r="Y48" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Z48" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AD48" s="1"/>
     </row>
@@ -4670,7 +4672,7 @@
         <v>50</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>45</v>
@@ -4719,7 +4721,7 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>161</v>
@@ -4749,7 +4751,7 @@
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4766,7 +4768,7 @@
         <v>164</v>
       </c>
       <c r="Z50" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AD50" s="1"/>
     </row>
@@ -4778,16 +4780,16 @@
         <v>25</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>111</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>116</v>
@@ -4873,7 +4875,7 @@
         <v>113</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
@@ -4901,13 +4903,13 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>110</v>
@@ -4919,23 +4921,23 @@
         <v>179</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
@@ -4949,11 +4951,11 @@
         <v>142</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="3" t="s">
-        <v>180</v>
+        <v>232</v>
       </c>
       <c r="Z53" s="3"/>
       <c r="AD53" s="1"/>
@@ -4965,7 +4967,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
@@ -4973,7 +4975,7 @@
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
@@ -4981,7 +4983,7 @@
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4991,40 +4993,40 @@
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
       <c r="Y54" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Z54" s="3"/>
       <c r="AD54" s="1"/>
     </row>
     <row r="55" spans="2:30" ht="83.35" x14ac:dyDescent="0.8">
       <c r="B55" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -5035,7 +5037,7 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z55" s="3"/>
       <c r="AD55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3045E3-3142-4C66-9BBE-973F2A209958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E5811D1-E3C3-476E-9081-8E0CF672E93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6453" yWindow="213" windowWidth="19020" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1715,27 +1715,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;七世真理子&gt;(Rose)
-&lt;星野 さやか&gt;(九州女子プロレス)
-&lt;今野結菜&gt;(伊藤道場)仮合格</t>
-    <rPh sb="23" eb="27">
-      <t>キュウシュウジョシ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>イトウ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ドウジョウ</t>
-    </rPh>
-    <rPh sb="45" eb="46">
-      <t>カリ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>ゴウカク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>堀このみ(Rose)</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1755,6 +1734,31 @@
     </rPh>
     <rPh sb="33" eb="35">
       <t>ジョシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;七世真理子&gt;(Rose)
+&lt;星野 さやか&gt;(九州女子プロレス)
+&lt;今野結菜&gt;(伊藤道場)仮合格
+&lt;未愛&gt;(Pure-J)(2.23デビュー予定)</t>
+    <rPh sb="23" eb="27">
+      <t>キュウシュウジョシ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>イトウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ドウジョウ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ゴウカク</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2807,7 +2811,7 @@
     <row r="2" spans="1:30" ht="16" x14ac:dyDescent="0.8">
       <c r="B2" s="1">
         <f>SUM(C2:RZ2)</f>
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2991,7 +2995,7 @@
      LEN(Y5:Y1001) - LEN(SUBSTITUTE(Y5:Y1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z2" s="1" cm="1">
         <f t="array" ref="Z2">SUMPRODUCT(
@@ -4955,7 +4959,7 @@
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Z53" s="3"/>
       <c r="AD53" s="1"/>
@@ -4983,7 +4987,7 @@
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4993,7 +4997,7 @@
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
       <c r="Y54" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z54" s="3"/>
       <c r="AD54" s="1"/>
@@ -5037,7 +5041,7 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Z55" s="3"/>
       <c r="AD55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E5811D1-E3C3-476E-9081-8E0CF672E93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2405F96C-40D8-42CB-B937-1E3C5749AA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6453" yWindow="213" windowWidth="19020" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="228">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -957,25 +957,6 @@
     <rPh sb="4" eb="5">
       <t>マレ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>BBJ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>小久保アリサ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>大竹仁美</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>山中絵里奈</t>
-  </si>
-  <si>
-    <t>竹林早苗</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1203,20 +1184,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>志真うた(伊藤道場)
-CoCo(MyWay)</t>
-    <rPh sb="0" eb="2">
-      <t>シマ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>イトウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ドウジョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ちゃんよた</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1491,20 +1458,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>バニー及川
-マドレーヌ
-ウナギ・サヤカ
-松澤さん
-rhythm</t>
-    <rPh sb="3" eb="5">
-      <t>オイカワ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>マツザワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Venus</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1655,35 +1608,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>櫻井裕子(COLORS)
-網倉理奈(COLORS)
-KONOHA(銀河)(2026.5.24引退予定)
-花園桃花(アップタウン)
-杏ちゃむ(信州, DIE)</t>
-    <rPh sb="0" eb="4">
-      <t>サクライユウコ</t>
-    </rPh>
-    <rPh sb="13" eb="17">
-      <t>アミクラリナ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ギンガ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>インタイ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ヨテイ</t>
-    </rPh>
-    <rPh sb="52" eb="56">
-      <t>ハナゾノモモカ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>シンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>星ハム子(IR)(休)</t>
     <rPh sb="0" eb="1">
       <t>ホシ</t>
@@ -1720,21 +1644,6 @@
   </si>
   <si>
     <t>陽岬来永</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>苺畑ひより(666)
-横井真菜(REINA)
-タギリヒメ真夢(九州女子プロレス)
-彩月悠叶(2AW)
-さいとう(アップタウン)
-しおの(アップタウン)</t>
-    <rPh sb="31" eb="33">
-      <t>キュウシュウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ジョシ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1759,6 +1668,82 @@
     </rPh>
     <rPh sb="70" eb="72">
       <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バニー及川
+マドレーヌ
+ウナギ・サヤカ
+松澤さん
+rhythm
+山中絵里奈</t>
+    <rPh sb="3" eb="5">
+      <t>オイカワ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>マツザワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>櫻井裕子(COLORS)
+網倉理奈(COLORS)
+KONOHA(銀河)(2026.5.24引退予定)
+花園桃花(アップタウン)
+杏ちゃむ(信州, DIE)
+竹林早苗(BBJ)</t>
+    <rPh sb="0" eb="4">
+      <t>サクライユウコ</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>アミクラリナ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ギンガ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>インタイ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="52" eb="56">
+      <t>ハナゾノモモカ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>シンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>志真うた(伊藤道場)
+CoCo(MyWay)
+大竹仁美(BBJ)</t>
+    <rPh sb="0" eb="2">
+      <t>シマ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イトウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ドウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>苺畑ひより(666)
+横井真菜(REINA)
+タギリヒメ真夢(九州女子プロレス)
+彩月悠叶(2AW)
+さいとう(アップタウン)
+しおの(アップタウン)
+小久保アリサ(BBJ)</t>
+    <rPh sb="31" eb="33">
+      <t>キュウシュウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジョシ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1844,7 +1829,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="26">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1865,26 +1850,6 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2406,30 +2371,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}" name="テーブル1" displayName="テーブル1" ref="B4:Z56" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
-  <autoFilter ref="B4:Z56" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}"/>
-  <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{C5BCADDE-F600-4480-BD2B-E93168A1BF7F}" name="デビュー年" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{7319872F-B1DE-47E8-ADFA-F5962E445AE2}" name="Stardom" dataDxfId="23"/>
-    <tableColumn id="18" xr3:uid="{6DD05DFF-D195-4CF5-BFC5-531553A9ADC5}" name="AWG" dataDxfId="22"/>
-    <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリゴ" dataDxfId="20"/>
-    <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ" dataDxfId="19"/>
-    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="18"/>
-    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="17"/>
-    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{0D2ABC96-F0CF-44E9-912A-CA35E8452616}" name="Venus" dataDxfId="15"/>
-    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="14"/>
-    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="13"/>
-    <tableColumn id="21" xr3:uid="{ACF43FBE-31D7-4ED6-A997-E4AF4BF0B9D4}" name="マーベラス" dataDxfId="12"/>
-    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="11"/>
-    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="10"/>
-    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="9"/>
-    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{3CAB629B-BA9F-4560-89E7-0980EE2B0905}" name="エボリューション" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{5C631C06-2946-4CE3-901A-57A0BABE156F}" name="BBJ" dataDxfId="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}" name="テーブル1" displayName="テーブル1" ref="B4:Y56" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+  <autoFilter ref="B4:Y56" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}"/>
+  <tableColumns count="24">
+    <tableColumn id="1" xr3:uid="{C5BCADDE-F600-4480-BD2B-E93168A1BF7F}" name="デビュー年" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{7319872F-B1DE-47E8-ADFA-F5962E445AE2}" name="Stardom" dataDxfId="22"/>
+    <tableColumn id="18" xr3:uid="{6DD05DFF-D195-4CF5-BFC5-531553A9ADC5}" name="AWG" dataDxfId="21"/>
+    <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリゴ" dataDxfId="19"/>
+    <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ" dataDxfId="18"/>
+    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="17"/>
+    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="16"/>
+    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{0D2ABC96-F0CF-44E9-912A-CA35E8452616}" name="Venus" dataDxfId="14"/>
+    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="13"/>
+    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="12"/>
+    <tableColumn id="21" xr3:uid="{ACF43FBE-31D7-4ED6-A997-E4AF4BF0B9D4}" name="マーベラス" dataDxfId="11"/>
+    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="10"/>
+    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="9"/>
+    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="8"/>
+    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{3CAB629B-BA9F-4560-89E7-0980EE2B0905}" name="エボリューション" dataDxfId="4"/>
     <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="3"/>
     <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="2"/>
     <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="1"/>
@@ -2756,7 +2720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4F8F56-06F6-4E1D-8D81-5A485042419D}">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr defaultColWidth="27.33203125" defaultRowHeight="18" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="1.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -2779,18 +2743,17 @@
     <col min="19" max="19" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10.27734375" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="19.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.94140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="30.27734375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="30.0546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="27.33203125" style="1"/>
-    <col min="31" max="16384" width="27.33203125" style="1"/>
+    <col min="22" max="22" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="30.27734375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="30.0546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="27.33203125" style="1"/>
+    <col min="30" max="16384" width="27.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="16" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.8">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
@@ -2802,15 +2765,15 @@
       <c r="O1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
+      <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AD1" s="1"/>
-    </row>
-    <row r="2" spans="1:30" ht="16" x14ac:dyDescent="0.8">
+      <c r="AC1" s="1"/>
+    </row>
+    <row r="2" spans="1:29" ht="16" x14ac:dyDescent="0.8">
       <c r="B2" s="1">
-        <f>SUM(C2:RZ2)</f>
+        <f>SUM(C2:RY2)</f>
         <v>369</v>
       </c>
       <c r="C2" s="1" cm="1">
@@ -2979,7 +2942,7 @@
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X2" s="1" cm="1">
         <f t="array" ref="X2">SUMPRODUCT(
@@ -2987,7 +2950,7 @@
      LEN(X5:X1001) - LEN(SUBSTITUTE(X5:X1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="Y2" s="1" cm="1">
         <f t="array" ref="Y2">SUMPRODUCT(
@@ -2995,19 +2958,11 @@
      LEN(Y5:Y1001) - LEN(SUBSTITUTE(Y5:Y1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>48</v>
-      </c>
-      <c r="Z2" s="1" cm="1">
-        <f t="array" ref="Z2">SUMPRODUCT(
-  IF(LEN(Z5:Z1001)=0, 0,
-     LEN(Z5:Z1001) - LEN(SUBSTITUTE(Z5:Z1001, CHAR(10), "")) + 1
-  )
-)</f>
-        <v>49</v>
-      </c>
-      <c r="AD2" s="1"/>
-    </row>
-    <row r="3" spans="1:30" ht="16" x14ac:dyDescent="0.8">
+        <v>50</v>
+      </c>
+      <c r="AC2" s="1"/>
+    </row>
+    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.8">
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="L3" s="1"/>
@@ -3016,13 +2971,13 @@
       <c r="O3" s="1"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
+      <c r="V3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
-      <c r="AD3" s="1"/>
-    </row>
-    <row r="4" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC3" s="1"/>
+    </row>
+    <row r="4" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
@@ -3051,7 +3006,7 @@
         <v>57</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>51</v>
@@ -3063,7 +3018,7 @@
         <v>8</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>19</v>
@@ -3084,23 +3039,20 @@
         <v>133</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AD4" s="1"/>
-    </row>
-    <row r="5" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC4" s="1"/>
+    </row>
+    <row r="5" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B5" s="3">
         <v>1977</v>
       </c>
@@ -3129,10 +3081,9 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AD5" s="1"/>
-    </row>
-    <row r="6" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC5" s="1"/>
+    </row>
+    <row r="6" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B6" s="3">
         <v>1978</v>
       </c>
@@ -3159,10 +3110,9 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AD6" s="1"/>
-    </row>
-    <row r="7" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC6" s="1"/>
+    </row>
+    <row r="7" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B7" s="3">
         <v>1979</v>
       </c>
@@ -3189,10 +3139,9 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AD7" s="1"/>
-    </row>
-    <row r="8" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC7" s="1"/>
+    </row>
+    <row r="8" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B8" s="3">
         <v>1980</v>
       </c>
@@ -3220,13 +3169,12 @@
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3" t="s">
+      <c r="Y8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AD8" s="1"/>
-    </row>
-    <row r="9" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC8" s="1"/>
+    </row>
+    <row r="9" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B9" s="3">
         <v>1981</v>
       </c>
@@ -3253,10 +3201,9 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AD9" s="1"/>
-    </row>
-    <row r="10" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC9" s="1"/>
+    </row>
+    <row r="10" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B10" s="3">
         <v>1982</v>
       </c>
@@ -3283,10 +3230,9 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AD10" s="1"/>
-    </row>
-    <row r="11" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC10" s="1"/>
+    </row>
+    <row r="11" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B11" s="3">
         <v>1983</v>
       </c>
@@ -3313,10 +3259,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AD11" s="1"/>
-    </row>
-    <row r="12" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC11" s="1"/>
+    </row>
+    <row r="12" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B12" s="3">
         <v>1984</v>
       </c>
@@ -3343,10 +3288,9 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AD12" s="1"/>
-    </row>
-    <row r="13" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC12" s="1"/>
+    </row>
+    <row r="13" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B13" s="3">
         <v>1985</v>
       </c>
@@ -3371,14 +3315,13 @@
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3" t="s">
+      <c r="X13" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="Z13" s="3"/>
-      <c r="AD13" s="1"/>
-    </row>
-    <row r="14" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Y13" s="3"/>
+      <c r="AC13" s="1"/>
+    </row>
+    <row r="14" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B14" s="3">
         <v>1986</v>
       </c>
@@ -3405,16 +3348,15 @@
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
+      <c r="X14" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="Y14" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="AD14" s="1"/>
-    </row>
-    <row r="15" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC14" s="1"/>
+    </row>
+    <row r="15" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B15" s="3">
         <v>1987</v>
       </c>
@@ -3440,13 +3382,12 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3" t="s">
+      <c r="Y15" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="AD15" s="1"/>
-    </row>
-    <row r="16" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC15" s="1"/>
+    </row>
+    <row r="16" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B16" s="3">
         <v>1988</v>
       </c>
@@ -3477,10 +3418,9 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AD16" s="1"/>
-    </row>
-    <row r="17" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC16" s="1"/>
+    </row>
+    <row r="17" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B17" s="3">
         <v>1989</v>
       </c>
@@ -3505,16 +3445,15 @@
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
+      <c r="X17" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="Y17" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="AD17" s="1"/>
-    </row>
-    <row r="18" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC17" s="1"/>
+    </row>
+    <row r="18" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B18" s="3">
         <v>1990</v>
       </c>
@@ -3541,10 +3480,9 @@
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AD18" s="1"/>
-    </row>
-    <row r="19" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC18" s="1"/>
+    </row>
+    <row r="19" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B19" s="3">
         <v>1991</v>
       </c>
@@ -3571,10 +3509,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AD19" s="1"/>
-    </row>
-    <row r="20" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC19" s="1"/>
+    </row>
+    <row r="20" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B20" s="3">
         <v>1992</v>
       </c>
@@ -3601,10 +3538,9 @@
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-      <c r="AD20" s="1"/>
-    </row>
-    <row r="21" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC20" s="1"/>
+    </row>
+    <row r="21" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B21" s="3">
         <v>1993</v>
       </c>
@@ -3631,10 +3567,9 @@
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
-      <c r="AD21" s="1"/>
-    </row>
-    <row r="22" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC21" s="1"/>
+    </row>
+    <row r="22" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B22" s="3">
         <v>1994</v>
       </c>
@@ -3661,10 +3596,9 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
-      <c r="AD22" s="1"/>
-    </row>
-    <row r="23" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AC22" s="1"/>
+    </row>
+    <row r="23" spans="2:29" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B23" s="3">
         <v>1995</v>
       </c>
@@ -3691,16 +3625,15 @@
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
+      <c r="X23" s="3" t="s">
+        <v>183</v>
+      </c>
       <c r="Y23" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="Z23" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AD23" s="1"/>
-    </row>
-    <row r="24" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC23" s="1"/>
+    </row>
+    <row r="24" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B24" s="3">
         <v>1996</v>
       </c>
@@ -3726,13 +3659,12 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="AD24" s="1"/>
-    </row>
-    <row r="25" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Y24" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="AC24" s="1"/>
+    </row>
+    <row r="25" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B25" s="3">
         <v>1997</v>
       </c>
@@ -3760,13 +3692,12 @@
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="3" t="s">
+      <c r="Y25" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="AD25" s="1"/>
-    </row>
-    <row r="26" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC25" s="1"/>
+    </row>
+    <row r="26" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B26" s="3">
         <v>1998</v>
       </c>
@@ -3791,16 +3722,15 @@
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
+      <c r="X26" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="Y26" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z26" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AD26" s="1"/>
-    </row>
-    <row r="27" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC26" s="1"/>
+    </row>
+    <row r="27" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B27" s="3">
         <v>1999</v>
       </c>
@@ -3827,14 +3757,13 @@
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3" t="s">
+      <c r="X27" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="Z27" s="3"/>
-      <c r="AD27" s="1"/>
-    </row>
-    <row r="28" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="Y27" s="3"/>
+      <c r="AC27" s="1"/>
+    </row>
+    <row r="28" spans="2:29" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B28" s="3">
         <v>2000</v>
       </c>
@@ -3864,13 +3793,12 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="3" t="s">
+      <c r="Y28" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="AD28" s="1"/>
-    </row>
-    <row r="29" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC28" s="1"/>
+    </row>
+    <row r="29" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B29" s="3">
         <v>2001</v>
       </c>
@@ -3901,10 +3829,9 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
-      <c r="Z29" s="3"/>
-      <c r="AD29" s="1"/>
-    </row>
-    <row r="30" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AC29" s="1"/>
+    </row>
+    <row r="30" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B30" s="3">
         <v>2002</v>
       </c>
@@ -3929,14 +3856,13 @@
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
-      <c r="X30" s="3"/>
-      <c r="Y30" s="3" t="s">
+      <c r="X30" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="Z30" s="3"/>
-      <c r="AD30" s="1"/>
-    </row>
-    <row r="31" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Y30" s="3"/>
+      <c r="AC30" s="1"/>
+    </row>
+    <row r="31" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B31" s="3">
         <v>2003</v>
       </c>
@@ -3963,10 +3889,9 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
-      <c r="Z31" s="3"/>
-      <c r="AD31" s="1"/>
-    </row>
-    <row r="32" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AC31" s="1"/>
+    </row>
+    <row r="32" spans="2:29" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B32" s="3">
         <v>2004</v>
       </c>
@@ -3991,16 +3916,15 @@
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
+      <c r="X32" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="Y32" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z32" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="AD32" s="1"/>
-    </row>
-    <row r="33" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AC32" s="1"/>
+    </row>
+    <row r="33" spans="2:29" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B33" s="3">
         <v>2005</v>
       </c>
@@ -4027,14 +3951,13 @@
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="Z33" s="3"/>
-      <c r="AD33" s="1"/>
-    </row>
-    <row r="34" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
+      <c r="X33" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y33" s="3"/>
+      <c r="AC33" s="1"/>
+    </row>
+    <row r="34" spans="2:29" ht="66.7" x14ac:dyDescent="0.8">
       <c r="B34" s="3">
         <v>2006</v>
       </c>
@@ -4043,13 +3966,13 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>52</v>
@@ -4066,17 +3989,16 @@
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
-      <c r="W34" s="3"/>
-      <c r="X34" s="3" t="s">
+      <c r="W34" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="3" t="s">
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="AD34" s="1"/>
-    </row>
-    <row r="35" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+      <c r="AC34" s="1"/>
+    </row>
+    <row r="35" spans="2:29" ht="50" x14ac:dyDescent="0.8">
       <c r="B35" s="3">
         <v>2007</v>
       </c>
@@ -4100,28 +4022,27 @@
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
-      <c r="W35" s="3"/>
-      <c r="X35" s="3" t="s">
+      <c r="W35" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="AD35" s="1"/>
-    </row>
-    <row r="36" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="X35" s="3"/>
+      <c r="Y35" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="AC35" s="1"/>
+    </row>
+    <row r="36" spans="2:29" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B36" s="3">
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4138,17 +4059,16 @@
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
-      <c r="W36" s="3"/>
-      <c r="X36" s="3" t="s">
+      <c r="W36" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="AD36" s="1"/>
-    </row>
-    <row r="37" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="X36" s="3"/>
+      <c r="Y36" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="AC36" s="1"/>
+    </row>
+    <row r="37" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B37" s="3">
         <v>2009</v>
       </c>
@@ -4173,14 +4093,13 @@
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3" t="s">
+      <c r="X37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="Z37" s="3"/>
-      <c r="AD37" s="1"/>
-    </row>
-    <row r="38" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+      <c r="Y37" s="3"/>
+      <c r="AC37" s="1"/>
+    </row>
+    <row r="38" spans="2:29" ht="50" x14ac:dyDescent="0.8">
       <c r="B38" s="3">
         <v>2010</v>
       </c>
@@ -4209,19 +4128,18 @@
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3" t="s">
+      <c r="X38" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Z38" s="3"/>
-      <c r="AD38" s="1"/>
-    </row>
-    <row r="39" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="Y38" s="3"/>
+      <c r="AC38" s="1"/>
+    </row>
+    <row r="39" spans="2:29" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B39" s="3">
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4250,17 +4168,16 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3" t="s">
+      <c r="W39" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="AD39" s="1"/>
-    </row>
-    <row r="40" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC39" s="1"/>
+    </row>
+    <row r="40" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B40" s="3">
         <v>2012</v>
       </c>
@@ -4268,7 +4185,7 @@
         <v>139</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>41</v>
@@ -4297,14 +4214,13 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z40" s="3"/>
-      <c r="AD40" s="1"/>
-    </row>
-    <row r="41" spans="2:30" ht="100" x14ac:dyDescent="0.8">
+      <c r="X40" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y40" s="3"/>
+      <c r="AC40" s="1"/>
+    </row>
+    <row r="41" spans="2:29" ht="100" x14ac:dyDescent="0.8">
       <c r="B41" s="3">
         <v>2013</v>
       </c>
@@ -4313,17 +4229,17 @@
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4338,24 +4254,23 @@
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
-      <c r="W41" s="3"/>
+      <c r="W41" s="3" t="s">
+        <v>101</v>
+      </c>
       <c r="X41" s="3" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="Z41" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD41" s="1"/>
-    </row>
-    <row r="42" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+        <v>150</v>
+      </c>
+      <c r="AC41" s="1"/>
+    </row>
+    <row r="42" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B42" s="3">
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4379,21 +4294,20 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
+      <c r="X42" s="3" t="s">
+        <v>138</v>
+      </c>
       <c r="Y42" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="Z42" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="AD42" s="1"/>
-    </row>
-    <row r="43" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
+        <v>212</v>
+      </c>
+      <c r="AC42" s="1"/>
+    </row>
+    <row r="43" spans="2:29" ht="66.7" x14ac:dyDescent="0.8">
       <c r="B43" s="3">
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4418,22 +4332,21 @@
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
-      <c r="W43" s="3"/>
-      <c r="X43" s="3" t="s">
+      <c r="W43" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="Y43" s="3"/>
-      <c r="Z43" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="AD43" s="1"/>
-    </row>
-    <row r="44" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+      <c r="X43" s="3"/>
+      <c r="Y43" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AC43" s="1"/>
+    </row>
+    <row r="44" spans="2:29" ht="50" x14ac:dyDescent="0.8">
       <c r="B44" s="3">
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
@@ -4459,21 +4372,20 @@
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
+      <c r="X44" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="Y44" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z44" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="AD44" s="1"/>
-    </row>
-    <row r="45" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+        <v>208</v>
+      </c>
+      <c r="AC44" s="1"/>
+    </row>
+    <row r="45" spans="2:29" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B45" s="3">
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4496,7 +4408,7 @@
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
@@ -4506,30 +4418,29 @@
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
-      <c r="W45" s="3"/>
+      <c r="W45" s="3" t="s">
+        <v>112</v>
+      </c>
       <c r="X45" s="3" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="Z45" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AD45" s="1"/>
-    </row>
-    <row r="46" spans="2:30" ht="100" x14ac:dyDescent="0.8">
+      <c r="AC45" s="1"/>
+    </row>
+    <row r="46" spans="2:29" ht="100" x14ac:dyDescent="0.8">
       <c r="B46" s="3">
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>14</v>
@@ -4559,27 +4470,24 @@
         <v>126</v>
       </c>
       <c r="U46" s="3"/>
-      <c r="V46" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="W46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="X46" s="3" t="s">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="Z46" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="AD46" s="1"/>
-    </row>
-    <row r="47" spans="2:30" ht="83.35" x14ac:dyDescent="0.8">
+        <v>141</v>
+      </c>
+      <c r="AC46" s="1"/>
+    </row>
+    <row r="47" spans="2:29" ht="100" x14ac:dyDescent="0.8">
       <c r="B47" s="3">
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4593,7 +4501,7 @@
         <v>23</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>72</v>
@@ -4613,20 +4521,17 @@
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
-      <c r="V47" s="3" t="s">
-        <v>144</v>
-      </c>
+      <c r="V47" s="3"/>
       <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
+      <c r="X47" s="3" t="s">
+        <v>165</v>
+      </c>
       <c r="Y47" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="Z47" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="AD47" s="1"/>
-    </row>
-    <row r="48" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+        <v>224</v>
+      </c>
+      <c r="AC47" s="1"/>
+    </row>
+    <row r="48" spans="2:29" ht="50" x14ac:dyDescent="0.8">
       <c r="B48" s="3">
         <v>2020</v>
       </c>
@@ -4659,16 +4564,15 @@
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
-      <c r="X48" s="3"/>
+      <c r="X48" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="Y48" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="Z48" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="AD48" s="1"/>
-    </row>
-    <row r="49" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
+        <v>219</v>
+      </c>
+      <c r="AC48" s="1"/>
+    </row>
+    <row r="49" spans="2:29" ht="66.7" x14ac:dyDescent="0.8">
       <c r="B49" s="3">
         <v>2021</v>
       </c>
@@ -4676,7 +4580,7 @@
         <v>50</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>45</v>
@@ -4685,7 +4589,7 @@
         <v>11</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4709,35 +4613,34 @@
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
-      <c r="V49" s="3"/>
-      <c r="W49" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="X49" s="3"/>
-      <c r="Y49" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z49" s="3"/>
-      <c r="AD49" s="1"/>
-    </row>
-    <row r="50" spans="2:30" ht="133.35" x14ac:dyDescent="0.8">
+      <c r="V49" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="W49" s="3"/>
+      <c r="X49" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y49" s="3"/>
+      <c r="AC49" s="1"/>
+    </row>
+    <row r="50" spans="2:29" ht="133.35" x14ac:dyDescent="0.8">
       <c r="B50" s="3">
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>22</v>
@@ -4749,13 +4652,13 @@
         <v>73</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4763,20 +4666,19 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
-      <c r="V50" s="3"/>
-      <c r="W50" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="X50" s="3"/>
+      <c r="V50" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="W50" s="3"/>
+      <c r="X50" s="3" t="s">
+        <v>159</v>
+      </c>
       <c r="Y50" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="Z50" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="AD50" s="1"/>
-    </row>
-    <row r="51" spans="2:30" ht="100" x14ac:dyDescent="0.8">
+        <v>187</v>
+      </c>
+      <c r="AC50" s="1"/>
+    </row>
+    <row r="51" spans="2:29" ht="100" x14ac:dyDescent="0.8">
       <c r="B51" s="3">
         <v>2023</v>
       </c>
@@ -4784,16 +4686,16 @@
         <v>25</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>111</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>116</v>
@@ -4806,7 +4708,7 @@
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
@@ -4818,7 +4720,7 @@
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
@@ -4826,21 +4728,18 @@
         <v>135</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="W51" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="X51" s="3"/>
+        <v>162</v>
+      </c>
+      <c r="W51" s="3"/>
+      <c r="X51" s="3" t="s">
+        <v>226</v>
+      </c>
       <c r="Y51" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="Z51" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="AD51" s="1"/>
-    </row>
-    <row r="52" spans="2:30" ht="100" x14ac:dyDescent="0.8">
+        <v>146</v>
+      </c>
+      <c r="AC51" s="1"/>
+    </row>
+    <row r="52" spans="2:29" ht="100" x14ac:dyDescent="0.8">
       <c r="B52" s="3">
         <v>2024</v>
       </c>
@@ -4857,10 +4756,10 @@
         <v>137</v>
       </c>
       <c r="G52" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H52" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>78</v>
@@ -4869,7 +4768,7 @@
         <v>75</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="L52" s="3"/>
       <c r="M52" s="3" t="s">
@@ -4879,7 +4778,7 @@
         <v>113</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
@@ -4895,25 +4794,24 @@
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
-      <c r="X52" s="3"/>
-      <c r="Y52" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z52" s="3"/>
-      <c r="AD52" s="1"/>
-    </row>
-    <row r="53" spans="2:30" ht="100" x14ac:dyDescent="0.8">
+      <c r="X52" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y52" s="3"/>
+      <c r="AC52" s="1"/>
+    </row>
+    <row r="53" spans="2:29" ht="116.7" x14ac:dyDescent="0.8">
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>110</v>
@@ -4922,26 +4820,26 @@
         <v>102</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
@@ -4952,26 +4850,23 @@
         <v>136</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="W53" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="X53" s="3"/>
-      <c r="Y53" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="Z53" s="3"/>
-      <c r="AD53" s="1"/>
-    </row>
-    <row r="54" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+        <v>193</v>
+      </c>
+      <c r="W53" s="3"/>
+      <c r="X53" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="Y53" s="3"/>
+      <c r="AC53" s="1"/>
+    </row>
+    <row r="54" spans="2:29" ht="50" x14ac:dyDescent="0.8">
       <c r="B54" s="3">
         <v>2026</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
@@ -4979,7 +4874,7 @@
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
@@ -4987,7 +4882,7 @@
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4995,42 +4890,41 @@
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
-      <c r="X54" s="3"/>
-      <c r="Y54" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="Z54" s="3"/>
-      <c r="AD54" s="1"/>
-    </row>
-    <row r="55" spans="2:30" ht="83.35" x14ac:dyDescent="0.8">
+      <c r="X54" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="Y54" s="3"/>
+      <c r="AC54" s="1"/>
+    </row>
+    <row r="55" spans="2:29" ht="83.35" x14ac:dyDescent="0.8">
       <c r="B55" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -5039,14 +4933,13 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-      <c r="X55" s="3"/>
-      <c r="Y55" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z55" s="3"/>
-      <c r="AD55" s="1"/>
-    </row>
-    <row r="56" spans="2:30" x14ac:dyDescent="0.8">
+      <c r="X55" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="Y55" s="3"/>
+      <c r="AC55" s="1"/>
+    </row>
+    <row r="56" spans="2:29" x14ac:dyDescent="0.8">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -5071,7 +4964,6 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-      <c r="Z56" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2405F96C-40D8-42CB-B937-1E3C5749AA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14EA735-A386-45A6-BE70-580606A74179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6453" yWindow="213" windowWidth="19020" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1441,16 +1441,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>梨央
-弥福かな
-ゴんべ
-摩利乃</t>
-    <rPh sb="0" eb="2">
-      <t>リオ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>稲葉ともか</t>
     <rPh sb="0" eb="2">
       <t>イナバ</t>
@@ -1502,17 +1492,6 @@
 儛島エマ
 古沢稀杏
 フワちゃん</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;小谷さつき&gt;
-&lt;松﨑紗弥&gt;
-&lt;山根百合&gt;
-&lt;桃羽もえは&gt;
-&lt;確変むぎ&gt;</t>
-    <rPh sb="31" eb="33">
-      <t>カクヘン</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1744,6 +1723,33 @@
     </rPh>
     <rPh sb="33" eb="35">
       <t>ジョシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>梨央
+弥福かな
+ゴんべ
+西村摩利乃</t>
+    <rPh sb="0" eb="2">
+      <t>リオ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニシムラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;小谷さつき&gt;
+&lt;松﨑紗弥&gt;
+&lt;山根百合&gt;
+&lt;桃羽もえは&gt;
+&lt;確変むぎ&gt;(4.5デビュー予定)</t>
+    <rPh sb="31" eb="33">
+      <t>カクヘン</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3006,7 +3012,7 @@
         <v>57</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>51</v>
@@ -4042,7 +4048,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4064,7 +4070,7 @@
       </c>
       <c r="X36" s="3"/>
       <c r="Y36" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AC36" s="1"/>
     </row>
@@ -4139,7 +4145,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4215,7 +4221,7 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Y40" s="3"/>
       <c r="AC40" s="1"/>
@@ -4298,7 +4304,7 @@
         <v>138</v>
       </c>
       <c r="Y42" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AC42" s="1"/>
     </row>
@@ -4307,7 +4313,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4346,7 +4352,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
@@ -4376,7 +4382,7 @@
         <v>122</v>
       </c>
       <c r="Y44" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AC44" s="1"/>
     </row>
@@ -4385,7 +4391,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4408,7 +4414,7 @@
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
@@ -4475,7 +4481,7 @@
         <v>100</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>141</v>
@@ -4501,7 +4507,7 @@
         <v>23</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>72</v>
@@ -4527,7 +4533,7 @@
         <v>165</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AC47" s="1"/>
     </row>
@@ -4565,10 +4571,10 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Y48" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AC48" s="1"/>
     </row>
@@ -4580,7 +4586,7 @@
         <v>50</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>45</v>
@@ -4628,7 +4634,7 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>156</v>
@@ -4692,7 +4698,7 @@
         <v>111</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>194</v>
@@ -4732,7 +4738,7 @@
       </c>
       <c r="W51" s="3"/>
       <c r="X51" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="Y51" s="3" t="s">
         <v>146</v>
@@ -4805,10 +4811,10 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>178</v>
@@ -4836,7 +4842,7 @@
         <v>189</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>174</v>
@@ -4854,7 +4860,7 @@
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="Y53" s="3"/>
       <c r="AC53" s="1"/>
@@ -4866,7 +4872,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
@@ -4874,7 +4880,7 @@
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
@@ -4882,7 +4888,7 @@
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4891,21 +4897,21 @@
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
       <c r="X54" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Y54" s="3"/>
       <c r="AC54" s="1"/>
     </row>
-    <row r="55" spans="2:29" ht="83.35" x14ac:dyDescent="0.8">
+    <row r="55" spans="2:29" ht="116.7" x14ac:dyDescent="0.8">
       <c r="B55" s="3" t="s">
         <v>179</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
@@ -4915,7 +4921,7 @@
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -4934,7 +4940,7 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Y55" s="3"/>
       <c r="AC55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14EA735-A386-45A6-BE70-580606A74179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C30299-9061-42E8-B7D2-0CB2FF1FCA37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6453" yWindow="213" windowWidth="19020" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="31627" yWindow="327" windowWidth="19020" windowHeight="13466" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -1742,13 +1742,13 @@
   <si>
     <t>&lt;小谷さつき&gt;
 &lt;松﨑紗弥&gt;
-&lt;山根百合&gt;
+&lt;山根百合&gt;(4.5デビュー予定)
 &lt;桃羽もえは&gt;
 &lt;確変むぎ&gt;(4.5デビュー予定)</t>
-    <rPh sb="31" eb="33">
+    <rPh sb="42" eb="44">
       <t>カクヘン</t>
     </rPh>
-    <rPh sb="44" eb="46">
+    <rPh sb="55" eb="57">
       <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -2732,7 +2732,7 @@
     <col min="1" max="1" width="1.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.38671875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="20.27734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.94140625" style="1" bestFit="1" customWidth="1"/>
@@ -4902,7 +4902,7 @@
       <c r="Y54" s="3"/>
       <c r="AC54" s="1"/>
     </row>
-    <row r="55" spans="2:29" ht="116.7" x14ac:dyDescent="0.8">
+    <row r="55" spans="2:29" ht="83.35" x14ac:dyDescent="0.8">
       <c r="B55" s="3" t="s">
         <v>179</v>
       </c>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C30299-9061-42E8-B7D2-0CB2FF1FCA37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B73DF8F-EED2-4715-A2F1-FE248CEC062B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31627" yWindow="327" windowWidth="19020" windowHeight="13466" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="2440" yWindow="1407" windowWidth="19020" windowHeight="13466" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="229">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1749,6 +1749,13 @@
       <t>カクヘン</t>
     </rPh>
     <rPh sb="55" eb="57">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI(3.14デビュー予定)</t>
+    <rPh sb="11" eb="13">
       <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -2780,7 +2787,7 @@
     <row r="2" spans="1:29" ht="16" x14ac:dyDescent="0.8">
       <c r="B2" s="1">
         <f>SUM(C2:RY2)</f>
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2812,7 +2819,7 @@
      LEN(F5:F1001) - LEN(SUBSTITUTE(F5:F1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" cm="1">
         <f t="array" ref="G2">SUMPRODUCT(
@@ -4913,7 +4920,9 @@
       <c r="E55" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="F55" s="3"/>
+      <c r="F55" s="3" t="s">
+        <v>228</v>
+      </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B73DF8F-EED2-4715-A2F1-FE248CEC062B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233343A0-A2E7-4BE4-A4E5-3A9CF68339CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2440" yWindow="1407" windowWidth="19020" windowHeight="13466" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="1193" yWindow="107" windowWidth="18500" windowHeight="13466" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -1626,31 +1626,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;七世真理子&gt;(Rose)
-&lt;星野 さやか&gt;(九州女子プロレス)
-&lt;今野結菜&gt;(伊藤道場)仮合格
-&lt;未愛&gt;(Pure-J)(2.23デビュー予定)</t>
-    <rPh sb="23" eb="27">
-      <t>キュウシュウジョシ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>イトウ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ドウジョウ</t>
-    </rPh>
-    <rPh sb="45" eb="46">
-      <t>カリ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>ゴウカク</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>バニー及川
 マドレーヌ
 ウナギ・サヤカ
@@ -1754,8 +1729,37 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>AI(3.14デビュー予定)</t>
-    <rPh sb="11" eb="13">
+    <t>&lt;AI&gt;(3.14デビュー予定)</t>
+    <rPh sb="13" eb="15">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;七世真理子&gt;(Rose)
+&lt;星野 さやか&gt;(九州女子プロレス)
+&lt;今野結菜&gt;(伊藤道場)仮合格
+&lt;未愛&gt;(Pure-J)(2.23デビュー予定)
+&lt;鰻マスクウーマン&gt;(DDT?)(4.19デビュー予定)</t>
+    <rPh sb="23" eb="27">
+      <t>キュウシュウジョシ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>イトウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ドウジョウ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ゴウカク</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
       <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -2787,7 +2791,7 @@
     <row r="2" spans="1:29" ht="16" x14ac:dyDescent="0.8">
       <c r="B2" s="1">
         <f>SUM(C2:RY2)</f>
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2963,7 +2967,7 @@
      LEN(X5:X1001) - LEN(SUBSTITUTE(X5:X1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y2" s="1" cm="1">
         <f t="array" ref="Y2">SUMPRODUCT(
@@ -4488,7 +4492,7 @@
         <v>100</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>141</v>
@@ -4540,7 +4544,7 @@
         <v>165</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AC47" s="1"/>
     </row>
@@ -4745,7 +4749,7 @@
       </c>
       <c r="W51" s="3"/>
       <c r="X51" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Y51" s="3" t="s">
         <v>146</v>
@@ -4821,7 +4825,7 @@
         <v>204</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>178</v>
@@ -4867,7 +4871,7 @@
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y53" s="3"/>
       <c r="AC53" s="1"/>
@@ -4909,19 +4913,19 @@
       <c r="Y54" s="3"/>
       <c r="AC54" s="1"/>
     </row>
-    <row r="55" spans="2:29" ht="83.35" x14ac:dyDescent="0.8">
+    <row r="55" spans="2:29" ht="100" x14ac:dyDescent="0.8">
       <c r="B55" s="3" t="s">
         <v>179</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>200</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
@@ -4949,7 +4953,7 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="Y55" s="3"/>
       <c r="AC55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233343A0-A2E7-4BE4-A4E5-3A9CF68339CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE926B79-F78D-484E-9B7D-D28C4B191F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1193" yWindow="107" windowWidth="18500" windowHeight="13466" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="230">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1739,7 +1739,6 @@
     <t>&lt;七世真理子&gt;(Rose)
 &lt;星野 さやか&gt;(九州女子プロレス)
 &lt;今野結菜&gt;(伊藤道場)仮合格
-&lt;未愛&gt;(Pure-J)(2.23デビュー予定)
 &lt;鰻マスクウーマン&gt;(DDT?)(4.19デビュー予定)</t>
     <rPh sb="23" eb="27">
       <t>キュウシュウジョシ</t>
@@ -1756,12 +1755,13 @@
     <rPh sb="46" eb="48">
       <t>ゴウカク</t>
     </rPh>
-    <rPh sb="70" eb="72">
+    <rPh sb="74" eb="76">
       <t>ヨテイ</t>
     </rPh>
-    <rPh sb="99" eb="101">
-      <t>ヨテイ</t>
-    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未愛</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1847,6 +1847,26 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="26">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Noto Serif JP SemiBold"/>
+        <family val="1"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1989,26 +2009,6 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2401,20 +2401,20 @@
     <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="16"/>
     <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="15"/>
     <tableColumn id="8" xr3:uid="{0D2ABC96-F0CF-44E9-912A-CA35E8452616}" name="Venus" dataDxfId="14"/>
+    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="0"/>
     <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="13"/>
-    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="12"/>
-    <tableColumn id="21" xr3:uid="{ACF43FBE-31D7-4ED6-A997-E4AF4BF0B9D4}" name="マーベラス" dataDxfId="11"/>
-    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="10"/>
-    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="9"/>
-    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="8"/>
-    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{3CAB629B-BA9F-4560-89E7-0980EE2B0905}" name="エボリューション" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="3"/>
-    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="0"/>
+    <tableColumn id="21" xr3:uid="{ACF43FBE-31D7-4ED6-A997-E4AF4BF0B9D4}" name="マーベラス" dataDxfId="12"/>
+    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="11"/>
+    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="10"/>
+    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="9"/>
+    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{3CAB629B-BA9F-4560-89E7-0980EE2B0905}" name="エボリューション" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="4"/>
+    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2737,7 +2737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4F8F56-06F6-4E1D-8D81-5A485042419D}">
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AD56"/>
   <sheetFormatPr defaultColWidth="27.33203125" defaultRowHeight="18" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="1.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -2750,27 +2750,27 @@
     <col min="9" max="9" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.609375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.38671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.609375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.0546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.27734375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.94140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.27734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="30.27734375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="30.0546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="27.33203125" style="1"/>
-    <col min="30" max="16384" width="27.33203125" style="1"/>
+    <col min="12" max="12" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.609375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.0546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.27734375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.94140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.27734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="30.27734375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="30.0546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="27.33203125" style="1"/>
+    <col min="31" max="16384" width="27.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:30" ht="16" x14ac:dyDescent="0.8">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
@@ -2780,18 +2780,19 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="Q1" s="1"/>
+      <c r="P1" s="1"/>
       <c r="R1" s="1"/>
-      <c r="V1" s="1"/>
+      <c r="S1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="AC1" s="1"/>
-    </row>
-    <row r="2" spans="1:29" ht="16" x14ac:dyDescent="0.8">
+      <c r="Z1" s="1"/>
+      <c r="AD1" s="1"/>
+    </row>
+    <row r="2" spans="1:30" ht="16" x14ac:dyDescent="0.8">
       <c r="B2" s="1">
         <f>SUM(C2:RY2)</f>
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2871,7 +2872,7 @@
      LEN(L5:L1001) - LEN(SUBSTITUTE(L5:L1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M2" s="1" cm="1">
         <f t="array" ref="M2">SUMPRODUCT(
@@ -2907,94 +2908,96 @@
       </c>
       <c r="Q2" s="1" cm="1">
         <f t="array" ref="Q2">SUMPRODUCT(
-  IF(LEN(Q5:Q1001)=0, 0,
-     LEN(Q5:Q1001) - LEN(SUBSTITUTE(Q5:Q1001, CHAR(10), "")) + 1
-  )
-)</f>
-        <v>6</v>
-      </c>
-      <c r="R2" s="1" cm="1">
-        <f t="array" ref="R2">SUMPRODUCT(
   IF(LEN(R5:R1001)=0, 0,
      LEN(R5:R1001) - LEN(SUBSTITUTE(R5:R1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="S2" s="1" cm="1">
-        <f t="array" ref="S2">SUMPRODUCT(
+      <c r="R2" s="1" cm="1">
+        <f t="array" ref="R2">SUMPRODUCT(
   IF(LEN(S5:S1001)=0, 0,
      LEN(S5:S1001) - LEN(SUBSTITUTE(S5:S1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="T2" s="1" cm="1">
-        <f t="array" ref="T2">SUMPRODUCT(
+      <c r="S2" s="1" cm="1">
+        <f t="array" ref="S2">SUMPRODUCT(
   IF(LEN(T5:T1001)=0, 0,
      LEN(T5:T1001) - LEN(SUBSTITUTE(T5:T1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="U2" s="1" cm="1">
-        <f t="array" ref="U2">SUMPRODUCT(
+      <c r="T2" s="1" cm="1">
+        <f t="array" ref="T2">SUMPRODUCT(
   IF(LEN(U5:U1001)=0, 0,
      LEN(U5:U1001) - LEN(SUBSTITUTE(U5:U1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="V2" s="1" cm="1">
-        <f t="array" ref="V2">SUMPRODUCT(
+      <c r="U2" s="1" cm="1">
+        <f t="array" ref="U2">SUMPRODUCT(
   IF(LEN(V5:V1001)=0, 0,
      LEN(V5:V1001) - LEN(SUBSTITUTE(V5:V1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="W2" s="1" cm="1">
-        <f t="array" ref="W2">SUMPRODUCT(
+      <c r="V2" s="1" cm="1">
+        <f t="array" ref="V2">SUMPRODUCT(
   IF(LEN(W5:W1001)=0, 0,
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>8</v>
       </c>
-      <c r="X2" s="1" cm="1">
-        <f t="array" ref="X2">SUMPRODUCT(
+      <c r="W2" s="1" cm="1">
+        <f t="array" ref="W2">SUMPRODUCT(
   IF(LEN(X5:X1001)=0, 0,
      LEN(X5:X1001) - LEN(SUBSTITUTE(X5:X1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>52</v>
-      </c>
-      <c r="Y2" s="1" cm="1">
-        <f t="array" ref="Y2">SUMPRODUCT(
+        <v>51</v>
+      </c>
+      <c r="X2" s="1" cm="1">
+        <f t="array" ref="X2">SUMPRODUCT(
   IF(LEN(Y5:Y1001)=0, 0,
      LEN(Y5:Y1001) - LEN(SUBSTITUTE(Y5:Y1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>50</v>
       </c>
-      <c r="AC2" s="1"/>
-    </row>
-    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.8">
+      <c r="Y2" s="1" cm="1">
+        <f t="array" ref="Y2">SUMPRODUCT(
+  IF(LEN(Z5:Z1001)=0, 0,
+     LEN(Z5:Z1001) - LEN(SUBSTITUTE(Z5:Z1001, CHAR(10), "")) + 1
+  )
+)</f>
+        <v>0</v>
+      </c>
+      <c r="Z2" s="1"/>
+      <c r="AD2" s="1"/>
+    </row>
+    <row r="3" spans="1:30" ht="16" x14ac:dyDescent="0.8">
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="Q3" s="1"/>
+      <c r="P3" s="1"/>
       <c r="R3" s="1"/>
-      <c r="V3" s="1"/>
+      <c r="S3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
-      <c r="AC3" s="1"/>
-    </row>
-    <row r="4" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z3" s="1"/>
+      <c r="AD3" s="1"/>
+    </row>
+    <row r="4" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
@@ -3026,10 +3029,10 @@
         <v>197</v>
       </c>
       <c r="L4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>8</v>
@@ -3067,9 +3070,10 @@
       <c r="Y4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AC4" s="1"/>
-    </row>
-    <row r="5" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z4" s="1"/>
+      <c r="AD4" s="1"/>
+    </row>
+    <row r="5" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B5" s="3">
         <v>1977</v>
       </c>
@@ -3098,9 +3102,10 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
-      <c r="AC5" s="1"/>
-    </row>
-    <row r="6" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z5" s="1"/>
+      <c r="AD5" s="1"/>
+    </row>
+    <row r="6" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B6" s="3">
         <v>1978</v>
       </c>
@@ -3127,9 +3132,10 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
-      <c r="AC6" s="1"/>
-    </row>
-    <row r="7" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z6" s="1"/>
+      <c r="AD6" s="1"/>
+    </row>
+    <row r="7" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B7" s="3">
         <v>1979</v>
       </c>
@@ -3156,9 +3162,10 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
-      <c r="AC7" s="1"/>
-    </row>
-    <row r="8" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z7" s="1"/>
+      <c r="AD7" s="1"/>
+    </row>
+    <row r="8" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B8" s="3">
         <v>1980</v>
       </c>
@@ -3189,9 +3196,10 @@
       <c r="Y8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AC8" s="1"/>
-    </row>
-    <row r="9" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z8" s="1"/>
+      <c r="AD8" s="1"/>
+    </row>
+    <row r="9" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B9" s="3">
         <v>1981</v>
       </c>
@@ -3218,9 +3226,10 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
-      <c r="AC9" s="1"/>
-    </row>
-    <row r="10" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z9" s="1"/>
+      <c r="AD9" s="1"/>
+    </row>
+    <row r="10" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B10" s="3">
         <v>1982</v>
       </c>
@@ -3247,9 +3256,10 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
-      <c r="AC10" s="1"/>
-    </row>
-    <row r="11" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z10" s="1"/>
+      <c r="AD10" s="1"/>
+    </row>
+    <row r="11" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B11" s="3">
         <v>1983</v>
       </c>
@@ -3276,9 +3286,10 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-      <c r="AC11" s="1"/>
-    </row>
-    <row r="12" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z11" s="1"/>
+      <c r="AD11" s="1"/>
+    </row>
+    <row r="12" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B12" s="3">
         <v>1984</v>
       </c>
@@ -3305,9 +3316,10 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
-      <c r="AC12" s="1"/>
-    </row>
-    <row r="13" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z12" s="1"/>
+      <c r="AD12" s="1"/>
+    </row>
+    <row r="13" spans="1:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B13" s="3">
         <v>1985</v>
       </c>
@@ -3336,9 +3348,10 @@
         <v>123</v>
       </c>
       <c r="Y13" s="3"/>
-      <c r="AC13" s="1"/>
-    </row>
-    <row r="14" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z13" s="1"/>
+      <c r="AD13" s="1"/>
+    </row>
+    <row r="14" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B14" s="3">
         <v>1986</v>
       </c>
@@ -3371,9 +3384,10 @@
       <c r="Y14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="AC14" s="1"/>
-    </row>
-    <row r="15" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z14" s="1"/>
+      <c r="AD14" s="1"/>
+    </row>
+    <row r="15" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B15" s="3">
         <v>1987</v>
       </c>
@@ -3402,9 +3416,10 @@
       <c r="Y15" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="AC15" s="1"/>
-    </row>
-    <row r="16" spans="1:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z15" s="1"/>
+      <c r="AD15" s="1"/>
+    </row>
+    <row r="16" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B16" s="3">
         <v>1988</v>
       </c>
@@ -3435,9 +3450,10 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-      <c r="AC16" s="1"/>
-    </row>
-    <row r="17" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z16" s="1"/>
+      <c r="AD16" s="1"/>
+    </row>
+    <row r="17" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B17" s="3">
         <v>1989</v>
       </c>
@@ -3468,9 +3484,10 @@
       <c r="Y17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="AC17" s="1"/>
-    </row>
-    <row r="18" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z17" s="1"/>
+      <c r="AD17" s="1"/>
+    </row>
+    <row r="18" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B18" s="3">
         <v>1990</v>
       </c>
@@ -3497,9 +3514,10 @@
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
-      <c r="AC18" s="1"/>
-    </row>
-    <row r="19" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z18" s="1"/>
+      <c r="AD18" s="1"/>
+    </row>
+    <row r="19" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B19" s="3">
         <v>1991</v>
       </c>
@@ -3526,9 +3544,10 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-      <c r="AC19" s="1"/>
-    </row>
-    <row r="20" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z19" s="1"/>
+      <c r="AD19" s="1"/>
+    </row>
+    <row r="20" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B20" s="3">
         <v>1992</v>
       </c>
@@ -3555,9 +3574,10 @@
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
-      <c r="AC20" s="1"/>
-    </row>
-    <row r="21" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z20" s="1"/>
+      <c r="AD20" s="1"/>
+    </row>
+    <row r="21" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B21" s="3">
         <v>1993</v>
       </c>
@@ -3584,9 +3604,10 @@
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
-      <c r="AC21" s="1"/>
-    </row>
-    <row r="22" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z21" s="1"/>
+      <c r="AD21" s="1"/>
+    </row>
+    <row r="22" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B22" s="3">
         <v>1994</v>
       </c>
@@ -3613,9 +3634,10 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
-      <c r="AC22" s="1"/>
-    </row>
-    <row r="23" spans="2:29" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="Z22" s="1"/>
+      <c r="AD22" s="1"/>
+    </row>
+    <row r="23" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B23" s="3">
         <v>1995</v>
       </c>
@@ -3648,9 +3670,10 @@
       <c r="Y23" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AC23" s="1"/>
-    </row>
-    <row r="24" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z23" s="1"/>
+      <c r="AD23" s="1"/>
+    </row>
+    <row r="24" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B24" s="3">
         <v>1996</v>
       </c>
@@ -3679,9 +3702,10 @@
       <c r="Y24" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="AC24" s="1"/>
-    </row>
-    <row r="25" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z24" s="1"/>
+      <c r="AD24" s="1"/>
+    </row>
+    <row r="25" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B25" s="3">
         <v>1997</v>
       </c>
@@ -3694,10 +3718,10 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3" t="s">
+      <c r="L25" s="3" t="s">
         <v>90</v>
       </c>
+      <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -3712,9 +3736,10 @@
       <c r="Y25" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="AC25" s="1"/>
-    </row>
-    <row r="26" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z25" s="1"/>
+      <c r="AD25" s="1"/>
+    </row>
+    <row r="26" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B26" s="3">
         <v>1998</v>
       </c>
@@ -3745,9 +3770,10 @@
       <c r="Y26" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AC26" s="1"/>
-    </row>
-    <row r="27" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z26" s="1"/>
+      <c r="AD26" s="1"/>
+    </row>
+    <row r="27" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B27" s="3">
         <v>1999</v>
       </c>
@@ -3778,9 +3804,10 @@
         <v>81</v>
       </c>
       <c r="Y27" s="3"/>
-      <c r="AC27" s="1"/>
-    </row>
-    <row r="28" spans="2:29" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="Z27" s="1"/>
+      <c r="AD27" s="1"/>
+    </row>
+    <row r="28" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B28" s="3">
         <v>2000</v>
       </c>
@@ -3795,10 +3822,10 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3" t="s">
+      <c r="L28" s="3" t="s">
         <v>91</v>
       </c>
+      <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
@@ -3813,9 +3840,10 @@
       <c r="Y28" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="AC28" s="1"/>
-    </row>
-    <row r="29" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z28" s="1"/>
+      <c r="AD28" s="1"/>
+    </row>
+    <row r="29" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B29" s="3">
         <v>2001</v>
       </c>
@@ -3846,9 +3874,10 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
-      <c r="AC29" s="1"/>
-    </row>
-    <row r="30" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z29" s="1"/>
+      <c r="AD29" s="1"/>
+    </row>
+    <row r="30" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B30" s="3">
         <v>2002</v>
       </c>
@@ -3877,9 +3906,10 @@
         <v>84</v>
       </c>
       <c r="Y30" s="3"/>
-      <c r="AC30" s="1"/>
-    </row>
-    <row r="31" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z30" s="1"/>
+      <c r="AD30" s="1"/>
+    </row>
+    <row r="31" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B31" s="3">
         <v>2003</v>
       </c>
@@ -3906,9 +3936,10 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
-      <c r="AC31" s="1"/>
-    </row>
-    <row r="32" spans="2:29" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="Z31" s="1"/>
+      <c r="AD31" s="1"/>
+    </row>
+    <row r="32" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B32" s="3">
         <v>2004</v>
       </c>
@@ -3939,9 +3970,10 @@
       <c r="Y32" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="AC32" s="1"/>
-    </row>
-    <row r="33" spans="2:29" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="Z32" s="1"/>
+      <c r="AD32" s="1"/>
+    </row>
+    <row r="33" spans="2:30" ht="50" x14ac:dyDescent="0.8">
       <c r="B33" s="3">
         <v>2005</v>
       </c>
@@ -3972,9 +4004,10 @@
         <v>142</v>
       </c>
       <c r="Y33" s="3"/>
-      <c r="AC33" s="1"/>
-    </row>
-    <row r="34" spans="2:29" ht="66.7" x14ac:dyDescent="0.8">
+      <c r="Z33" s="1"/>
+      <c r="AD33" s="1"/>
+    </row>
+    <row r="34" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
       <c r="B34" s="3">
         <v>2006</v>
       </c>
@@ -3992,10 +4025,10 @@
         <v>170</v>
       </c>
       <c r="L34" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="M34" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
@@ -4013,9 +4046,10 @@
       <c r="Y34" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="AC34" s="1"/>
-    </row>
-    <row r="35" spans="2:29" ht="50" x14ac:dyDescent="0.8">
+      <c r="Z34" s="1"/>
+      <c r="AD34" s="1"/>
+    </row>
+    <row r="35" spans="2:30" ht="50" x14ac:dyDescent="0.8">
       <c r="B35" s="3">
         <v>2007</v>
       </c>
@@ -4046,9 +4080,10 @@
       <c r="Y35" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="AC35" s="1"/>
-    </row>
-    <row r="36" spans="2:29" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="Z35" s="1"/>
+      <c r="AD35" s="1"/>
+    </row>
+    <row r="36" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B36" s="3">
         <v>2008</v>
       </c>
@@ -4083,9 +4118,10 @@
       <c r="Y36" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="AC36" s="1"/>
-    </row>
-    <row r="37" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z36" s="1"/>
+      <c r="AD36" s="1"/>
+    </row>
+    <row r="37" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B37" s="3">
         <v>2009</v>
       </c>
@@ -4114,9 +4150,10 @@
         <v>59</v>
       </c>
       <c r="Y37" s="3"/>
-      <c r="AC37" s="1"/>
-    </row>
-    <row r="38" spans="2:29" ht="50" x14ac:dyDescent="0.8">
+      <c r="Z37" s="1"/>
+      <c r="AD37" s="1"/>
+    </row>
+    <row r="38" spans="2:30" ht="50" x14ac:dyDescent="0.8">
       <c r="B38" s="3">
         <v>2010</v>
       </c>
@@ -4149,9 +4186,10 @@
         <v>86</v>
       </c>
       <c r="Y38" s="3"/>
-      <c r="AC38" s="1"/>
-    </row>
-    <row r="39" spans="2:29" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="Z38" s="1"/>
+      <c r="AD38" s="1"/>
+    </row>
+    <row r="39" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B39" s="3">
         <v>2011</v>
       </c>
@@ -4170,10 +4208,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-      <c r="L39" s="3" t="s">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
@@ -4192,9 +4230,10 @@
       <c r="Y39" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="AC39" s="1"/>
-    </row>
-    <row r="40" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z39" s="1"/>
+      <c r="AD39" s="1"/>
+    </row>
+    <row r="40" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B40" s="3">
         <v>2012</v>
       </c>
@@ -4215,10 +4254,10 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3" t="s">
+      <c r="L40" s="3" t="s">
         <v>93</v>
       </c>
+      <c r="M40" s="3"/>
       <c r="N40" s="3" t="s">
         <v>1</v>
       </c>
@@ -4235,9 +4274,10 @@
         <v>209</v>
       </c>
       <c r="Y40" s="3"/>
-      <c r="AC40" s="1"/>
-    </row>
-    <row r="41" spans="2:29" ht="100" x14ac:dyDescent="0.8">
+      <c r="Z40" s="1"/>
+      <c r="AD40" s="1"/>
+    </row>
+    <row r="41" spans="2:30" ht="100" x14ac:dyDescent="0.8">
       <c r="B41" s="3">
         <v>2013</v>
       </c>
@@ -4280,9 +4320,10 @@
       <c r="Y41" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="AC41" s="1"/>
-    </row>
-    <row r="42" spans="2:29" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="Z41" s="1"/>
+      <c r="AD41" s="1"/>
+    </row>
+    <row r="42" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B42" s="3">
         <v>2014</v>
       </c>
@@ -4317,9 +4358,10 @@
       <c r="Y42" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="AC42" s="1"/>
-    </row>
-    <row r="43" spans="2:29" ht="66.7" x14ac:dyDescent="0.8">
+      <c r="Z42" s="1"/>
+      <c r="AD42" s="1"/>
+    </row>
+    <row r="43" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
       <c r="B43" s="3">
         <v>2015</v>
       </c>
@@ -4336,10 +4378,10 @@
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
-      <c r="L43" s="3" t="s">
+      <c r="L43" s="3"/>
+      <c r="M43" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="M43" s="3"/>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
@@ -4356,9 +4398,10 @@
       <c r="Y43" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="AC43" s="1"/>
-    </row>
-    <row r="44" spans="2:29" ht="50" x14ac:dyDescent="0.8">
+      <c r="Z43" s="1"/>
+      <c r="AD43" s="1"/>
+    </row>
+    <row r="44" spans="2:30" ht="50" x14ac:dyDescent="0.8">
       <c r="B44" s="3">
         <v>2016</v>
       </c>
@@ -4395,9 +4438,10 @@
       <c r="Y44" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="AC44" s="1"/>
-    </row>
-    <row r="45" spans="2:29" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="Z44" s="1"/>
+      <c r="AD44" s="1"/>
+    </row>
+    <row r="45" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B45" s="3">
         <v>2017</v>
       </c>
@@ -4418,10 +4462,10 @@
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
-      <c r="L45" s="3" t="s">
+      <c r="L45" s="3"/>
+      <c r="M45" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
@@ -4444,9 +4488,10 @@
       <c r="Y45" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AC45" s="1"/>
-    </row>
-    <row r="46" spans="2:29" ht="100" x14ac:dyDescent="0.8">
+      <c r="Z45" s="1"/>
+      <c r="AD45" s="1"/>
+    </row>
+    <row r="46" spans="2:30" ht="200" x14ac:dyDescent="0.8">
       <c r="B46" s="3">
         <v>2018</v>
       </c>
@@ -4469,10 +4514,10 @@
         <v>71</v>
       </c>
       <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3" t="s">
+      <c r="L46" s="3" t="s">
         <v>94</v>
       </c>
+      <c r="M46" s="3"/>
       <c r="N46" s="3" t="s">
         <v>29</v>
       </c>
@@ -4497,9 +4542,10 @@
       <c r="Y46" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="AC46" s="1"/>
-    </row>
-    <row r="47" spans="2:29" ht="100" x14ac:dyDescent="0.8">
+      <c r="Z46" s="1"/>
+      <c r="AD46" s="1"/>
+    </row>
+    <row r="47" spans="2:30" ht="100" x14ac:dyDescent="0.8">
       <c r="B47" s="3">
         <v>2019</v>
       </c>
@@ -4525,10 +4571,10 @@
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="M47" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -4546,9 +4592,10 @@
       <c r="Y47" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="AC47" s="1"/>
-    </row>
-    <row r="48" spans="2:29" ht="50" x14ac:dyDescent="0.8">
+      <c r="Z47" s="1"/>
+      <c r="AD47" s="1"/>
+    </row>
+    <row r="48" spans="2:30" ht="50" x14ac:dyDescent="0.8">
       <c r="B48" s="3">
         <v>2020</v>
       </c>
@@ -4565,10 +4612,10 @@
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3" t="s">
+      <c r="L48" s="3" t="s">
         <v>95</v>
       </c>
+      <c r="M48" s="3"/>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
       <c r="P48" s="3"/>
@@ -4587,9 +4634,10 @@
       <c r="Y48" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="AC48" s="1"/>
-    </row>
-    <row r="49" spans="2:29" ht="66.7" x14ac:dyDescent="0.8">
+      <c r="Z48" s="1"/>
+      <c r="AD48" s="1"/>
+    </row>
+    <row r="49" spans="2:30" ht="100" x14ac:dyDescent="0.8">
       <c r="B49" s="3">
         <v>2021</v>
       </c>
@@ -4638,9 +4686,10 @@
         <v>158</v>
       </c>
       <c r="Y49" s="3"/>
-      <c r="AC49" s="1"/>
-    </row>
-    <row r="50" spans="2:29" ht="133.35" x14ac:dyDescent="0.8">
+      <c r="Z49" s="1"/>
+      <c r="AD49" s="1"/>
+    </row>
+    <row r="50" spans="2:30" ht="133.35" x14ac:dyDescent="0.8">
       <c r="B50" s="3">
         <v>2022</v>
       </c>
@@ -4693,9 +4742,10 @@
       <c r="Y50" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="AC50" s="1"/>
-    </row>
-    <row r="51" spans="2:29" ht="100" x14ac:dyDescent="0.8">
+      <c r="Z50" s="1"/>
+      <c r="AD50" s="1"/>
+    </row>
+    <row r="51" spans="2:30" ht="100" x14ac:dyDescent="0.8">
       <c r="B51" s="3">
         <v>2023</v>
       </c>
@@ -4724,10 +4774,10 @@
         <v>74</v>
       </c>
       <c r="K51" s="3"/>
-      <c r="L51" s="3" t="s">
+      <c r="L51" s="3"/>
+      <c r="M51" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="M51" s="3"/>
       <c r="N51" s="3"/>
       <c r="O51" s="3" t="s">
         <v>117</v>
@@ -4754,9 +4804,10 @@
       <c r="Y51" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="AC51" s="1"/>
-    </row>
-    <row r="52" spans="2:29" ht="100" x14ac:dyDescent="0.8">
+      <c r="Z51" s="1"/>
+      <c r="AD51" s="1"/>
+    </row>
+    <row r="52" spans="2:30" ht="100" x14ac:dyDescent="0.8">
       <c r="B52" s="3">
         <v>2024</v>
       </c>
@@ -4787,10 +4838,10 @@
       <c r="K52" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3" t="s">
+      <c r="L52" s="3" t="s">
         <v>114</v>
       </c>
+      <c r="M52" s="3"/>
       <c r="N52" s="3" t="s">
         <v>113</v>
       </c>
@@ -4815,9 +4866,10 @@
         <v>147</v>
       </c>
       <c r="Y52" s="3"/>
-      <c r="AC52" s="1"/>
-    </row>
-    <row r="53" spans="2:29" ht="116.7" x14ac:dyDescent="0.8">
+      <c r="Z52" s="1"/>
+      <c r="AD52" s="1"/>
+    </row>
+    <row r="53" spans="2:30" ht="183.35" x14ac:dyDescent="0.8">
       <c r="B53" s="3">
         <v>2025</v>
       </c>
@@ -4874,9 +4926,10 @@
         <v>224</v>
       </c>
       <c r="Y53" s="3"/>
-      <c r="AC53" s="1"/>
-    </row>
-    <row r="54" spans="2:29" ht="50" x14ac:dyDescent="0.8">
+      <c r="Z53" s="1"/>
+      <c r="AD53" s="1"/>
+    </row>
+    <row r="54" spans="2:30" ht="50" x14ac:dyDescent="0.8">
       <c r="B54" s="3">
         <v>2026</v>
       </c>
@@ -4893,7 +4946,9 @@
       <c r="K54" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="L54" s="3"/>
+      <c r="L54" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
@@ -4911,9 +4966,10 @@
         <v>219</v>
       </c>
       <c r="Y54" s="3"/>
-      <c r="AC54" s="1"/>
-    </row>
-    <row r="55" spans="2:29" ht="100" x14ac:dyDescent="0.8">
+      <c r="Z54" s="1"/>
+      <c r="AD54" s="1"/>
+    </row>
+    <row r="55" spans="2:30" ht="150" x14ac:dyDescent="0.8">
       <c r="B55" s="3" t="s">
         <v>179</v>
       </c>
@@ -4956,9 +5012,10 @@
         <v>228</v>
       </c>
       <c r="Y55" s="3"/>
-      <c r="AC55" s="1"/>
-    </row>
-    <row r="56" spans="2:29" x14ac:dyDescent="0.8">
+      <c r="Z55" s="1"/>
+      <c r="AD55" s="1"/>
+    </row>
+    <row r="56" spans="2:30" x14ac:dyDescent="0.8">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -4983,6 +5040,9 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
+      <c r="Z56" s="1"/>
+      <c r="AC56"/>
+      <c r="AD56" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE926B79-F78D-484E-9B7D-D28C4B191F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC3073A-3A1E-46D5-9B88-6C628A71276B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1193" yWindow="107" windowWidth="18500" windowHeight="13466" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1729,13 +1729,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;AI&gt;(3.14デビュー予定)</t>
-    <rPh sb="13" eb="15">
-      <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>&lt;七世真理子&gt;(Rose)
 &lt;星野 さやか&gt;(九州女子プロレス)
 &lt;今野結菜&gt;(伊藤道場)仮合格
@@ -1762,6 +1755,10 @@
   </si>
   <si>
     <t>未愛</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ザ・レディAI</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1847,26 +1844,6 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="26">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2009,6 +1986,26 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Noto Serif JP SemiBold"/>
+        <family val="1"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2401,20 +2398,20 @@
     <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="16"/>
     <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="15"/>
     <tableColumn id="8" xr3:uid="{0D2ABC96-F0CF-44E9-912A-CA35E8452616}" name="Venus" dataDxfId="14"/>
-    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="0"/>
-    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="13"/>
-    <tableColumn id="21" xr3:uid="{ACF43FBE-31D7-4ED6-A997-E4AF4BF0B9D4}" name="マーベラス" dataDxfId="12"/>
-    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="11"/>
-    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="10"/>
-    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="9"/>
-    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{3CAB629B-BA9F-4560-89E7-0980EE2B0905}" name="エボリューション" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="4"/>
-    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="1"/>
+    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="13"/>
+    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="12"/>
+    <tableColumn id="21" xr3:uid="{ACF43FBE-31D7-4ED6-A997-E4AF4BF0B9D4}" name="マーベラス" dataDxfId="11"/>
+    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="10"/>
+    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="9"/>
+    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="8"/>
+    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{3CAB629B-BA9F-4560-89E7-0980EE2B0905}" name="エボリューション" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="3"/>
+    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4938,7 +4935,9 @@
       <c r="E54" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="F54" s="3"/>
+      <c r="F54" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
@@ -4947,7 +4946,7 @@
         <v>198</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
@@ -4980,9 +4979,7 @@
       <c r="E55" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>227</v>
-      </c>
+      <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
@@ -5009,7 +5006,7 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y55" s="3"/>
       <c r="Z55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC3073A-3A1E-46D5-9B88-6C628A71276B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25278F4B-4F45-44D7-AA2C-42835FE272D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1193" yWindow="107" windowWidth="18500" windowHeight="13466" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -514,12 +514,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>コグマ
-葉月
-AZM</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>梨杏
 浜辺纏</t>
     <phoneticPr fontId="1"/>
@@ -1051,36 +1045,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>山下りな
-日向小陽(休)
-夏 すみれ
-藤田あかね
-小林香萌
-弓李</t>
-    <rPh sb="0" eb="2">
-      <t>ヤマシタ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヒナタ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>コハル</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>フジタ</t>
-    </rPh>
-    <rPh sb="25" eb="29">
-      <t>コバヤシカホ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>キュウリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>山下実優
 中島翔子
 上福ゆき</t>
@@ -1282,21 +1246,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ホルスタイン・エンジュ
-ラブリカ・ヒナーノ
-枢夜 佐季</t>
-    <rPh sb="22" eb="23">
-      <t>クルル</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>サキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>&lt;Y&gt;</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1455,20 +1404,6 @@
     <t>髙橋光咲
 伊田惟吹
 当麻煌</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ひな
-希咲みなみ
-直江ミう</t>
-    <rPh sb="9" eb="11">
-      <t>ナオエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;アンリ&gt;仮
-&lt;ユウカ&gt;仮</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1729,9 +1664,46 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>未愛</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ザ・レディAI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;ひな&gt;
+&lt;希咲みなみ&gt;
+&lt;直江ミう&gt;</t>
+    <rPh sb="14" eb="16">
+      <t>ナオエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;アンリ&gt;(仮)
+&lt;ユウカ&gt;(仮)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホルスタイン・エンジュ
+ラブリカ・ヒナーノ
+枢夜佐季</t>
+    <rPh sb="22" eb="23">
+      <t>クルル</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>サキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>&lt;七世真理子&gt;(Rose)
 &lt;星野 さやか&gt;(九州女子プロレス)
-&lt;今野結菜&gt;(伊藤道場)仮合格
+&lt;今野結菜&gt;(伊藤道場)(仮合格)
 &lt;鰻マスクウーマン&gt;(DDT?)(4.19デビュー予定)</t>
     <rPh sb="23" eb="27">
       <t>キュウシュウジョシ</t>
@@ -1742,23 +1714,51 @@
     <rPh sb="42" eb="44">
       <t>ドウジョウ</t>
     </rPh>
-    <rPh sb="45" eb="46">
+    <rPh sb="46" eb="47">
       <t>カリ</t>
     </rPh>
-    <rPh sb="46" eb="48">
+    <rPh sb="47" eb="49">
       <t>ゴウカク</t>
     </rPh>
-    <rPh sb="74" eb="76">
+    <rPh sb="76" eb="78">
       <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>未愛</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ザ・レディAI</t>
+    <t>山下りな
+日向小陽(休)
+夏すみれ
+藤田あかね
+小林香萌
+弓李</t>
+    <rPh sb="0" eb="2">
+      <t>ヤマシタ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒナタ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コハル</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>フジタ</t>
+    </rPh>
+    <rPh sb="24" eb="28">
+      <t>コバヤシカホ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>キュウリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コグマ(休)
+葉月
+AZM</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2758,7 +2758,7 @@
     <col min="21" max="21" width="10.27734375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="19.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="41.0546875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="30.27734375" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="30.0546875" style="1" bestFit="1" customWidth="1"/>
@@ -2769,7 +2769,7 @@
   <sheetData>
     <row r="1" spans="1:30" ht="16" x14ac:dyDescent="0.8">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3011,7 +3011,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>17</v>
@@ -3023,10 +3023,10 @@
         <v>57</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>51</v>
@@ -3035,7 +3035,7 @@
         <v>8</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>19</v>
@@ -3050,16 +3050,16 @@
         <v>7</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>35</v>
@@ -3342,7 +3342,7 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
       <c r="X13" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y13" s="3"/>
       <c r="Z13" s="1"/>
@@ -3411,7 +3411,7 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z15" s="1"/>
       <c r="AD15" s="1"/>
@@ -3476,10 +3476,10 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
       <c r="X17" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y17" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Z17" s="1"/>
       <c r="AD17" s="1"/>
@@ -3662,7 +3662,7 @@
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
       <c r="X23" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>64</v>
@@ -3697,7 +3697,7 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AD24" s="1"/>
@@ -3716,7 +3716,7 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -3731,7 +3731,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z25" s="1"/>
       <c r="AD25" s="1"/>
@@ -3762,7 +3762,7 @@
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>32</v>
@@ -3798,7 +3798,7 @@
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
       <c r="X27" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Y27" s="3"/>
       <c r="Z27" s="1"/>
@@ -3820,7 +3820,7 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -3835,7 +3835,7 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z28" s="1"/>
       <c r="AD28" s="1"/>
@@ -3900,7 +3900,7 @@
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y30" s="3"/>
       <c r="Z30" s="1"/>
@@ -3965,7 +3965,7 @@
         <v>60</v>
       </c>
       <c r="Y32" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Z32" s="1"/>
       <c r="AD32" s="1"/>
@@ -3991,14 +3991,14 @@
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
       <c r="X33" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Y33" s="3"/>
       <c r="Z33" s="1"/>
@@ -4013,16 +4013,16 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M34" s="3" t="s">
         <v>52</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="X34" s="3"/>
       <c r="Y34" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z34" s="1"/>
       <c r="AD34" s="1"/>
@@ -4071,11 +4071,11 @@
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X35" s="3"/>
       <c r="Y35" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Z35" s="1"/>
       <c r="AD35" s="1"/>
@@ -4085,13 +4085,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="X36" s="3"/>
       <c r="Y36" s="3" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AD36" s="1"/>
@@ -4162,7 +4162,7 @@
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
@@ -4180,7 +4180,7 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Y38" s="3"/>
       <c r="Z38" s="1"/>
@@ -4191,15 +4191,15 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -4207,7 +4207,7 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
@@ -4221,11 +4221,11 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="X39" s="3"/>
       <c r="Y39" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Z39" s="1"/>
       <c r="AD39" s="1"/>
@@ -4235,16 +4235,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4252,7 +4252,7 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3" t="s">
@@ -4268,7 +4268,7 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="Y40" s="3"/>
       <c r="Z40" s="1"/>
@@ -4279,21 +4279,21 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>68</v>
+        <v>229</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4309,23 +4309,23 @@
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>150</v>
+        <v>228</v>
       </c>
       <c r="Z41" s="1"/>
       <c r="AD41" s="1"/>
     </row>
-    <row r="42" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+    <row r="42" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B42" s="3">
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4350,10 +4350,10 @@
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Y42" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AD42" s="1"/>
@@ -4363,7 +4363,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4389,11 +4389,11 @@
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="X43" s="3"/>
       <c r="Y43" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Z43" s="1"/>
       <c r="AD43" s="1"/>
@@ -4403,7 +4403,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
@@ -4430,10 +4430,10 @@
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
       <c r="X44" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Y44" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="Z44" s="1"/>
       <c r="AD44" s="1"/>
@@ -4443,7 +4443,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4451,39 +4451,39 @@
         <v>12</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z45" s="1"/>
       <c r="AD45" s="1"/>
@@ -4493,13 +4493,13 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>14</v>
@@ -4508,11 +4508,11 @@
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M46" s="3"/>
       <c r="N46" s="3" t="s">
@@ -4526,18 +4526,18 @@
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Z46" s="1"/>
       <c r="AD46" s="1"/>
@@ -4547,7 +4547,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4555,20 +4555,20 @@
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>54</v>
@@ -4584,10 +4584,10 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
       <c r="X47" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="Z47" s="1"/>
       <c r="AD47" s="1"/>
@@ -4610,7 +4610,7 @@
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -4619,17 +4619,17 @@
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
       <c r="S48" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="Y48" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AD48" s="1"/>
@@ -4642,7 +4642,7 @@
         <v>50</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>45</v>
@@ -4651,11 +4651,11 @@
         <v>11</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
@@ -4676,11 +4676,11 @@
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="W49" s="3"/>
       <c r="X49" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Y49" s="3"/>
       <c r="Z49" s="1"/>
@@ -4691,37 +4691,37 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4730,14 +4730,14 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="W50" s="3"/>
       <c r="X50" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Y50" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="Z50" s="1"/>
       <c r="AD50" s="1"/>
@@ -4750,56 +4750,56 @@
         <v>25</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>49</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="W51" s="3"/>
       <c r="X51" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="Y51" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Z51" s="1"/>
       <c r="AD51" s="1"/>
@@ -4809,7 +4809,7 @@
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>34</v>
@@ -4818,32 +4818,32 @@
         <v>44</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M52" s="3"/>
       <c r="N52" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
@@ -4852,15 +4852,15 @@
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Y52" s="3"/>
       <c r="Z52" s="1"/>
@@ -4871,56 +4871,56 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>175</v>
+        <v>226</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="Y53" s="3"/>
       <c r="Z53" s="1"/>
@@ -4933,27 +4933,27 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4962,41 +4962,41 @@
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
       <c r="X54" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="Y54" s="3"/>
       <c r="Z54" s="1"/>
       <c r="AD54" s="1"/>
     </row>
-    <row r="55" spans="2:30" ht="150" x14ac:dyDescent="0.8">
+    <row r="55" spans="2:30" ht="83.35" x14ac:dyDescent="0.8">
       <c r="B55" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25278F4B-4F45-44D7-AA2C-42835FE272D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66DABC1-8AB3-405E-98B7-10B221300BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1193" yWindow="107" windowWidth="18500" windowHeight="13466" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="5627" yWindow="653" windowWidth="18500" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -356,21 +356,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>遠藤有栖
-鳥喰かや
-荒井優希</t>
-    <rPh sb="0" eb="4">
-      <t>エンドウアリス</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>トリバミ</t>
-    </rPh>
-    <rPh sb="10" eb="14">
-      <t>アライユキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>フキゲンです</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1759,6 +1744,21 @@
     <t>コグマ(休)
 葉月
 AZM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遠藤有栖
+ハットリ桜
+荒井優希</t>
+    <rPh sb="0" eb="4">
+      <t>エンドウアリス</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ザクラ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>アライユキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2769,7 +2769,7 @@
   <sheetData>
     <row r="1" spans="1:30" ht="16" x14ac:dyDescent="0.8">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3011,31 +3011,31 @@
         <v>3</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>19</v>
@@ -3050,16 +3050,16 @@
         <v>7</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>35</v>
@@ -3316,7 +3316,7 @@
       <c r="Z12" s="1"/>
       <c r="AD12" s="1"/>
     </row>
-    <row r="13" spans="1:30" ht="33.35" x14ac:dyDescent="0.8">
+    <row r="13" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B13" s="3">
         <v>1985</v>
       </c>
@@ -3342,7 +3342,7 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
       <c r="X13" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Y13" s="3"/>
       <c r="Z13" s="1"/>
@@ -3376,7 +3376,7 @@
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>15</v>
@@ -3411,7 +3411,7 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Z15" s="1"/>
       <c r="AD15" s="1"/>
@@ -3476,10 +3476,10 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
       <c r="X17" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y17" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Z17" s="1"/>
       <c r="AD17" s="1"/>
@@ -3646,7 +3646,7 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
@@ -3662,10 +3662,10 @@
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
       <c r="X23" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y23" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Z23" s="1"/>
       <c r="AD23" s="1"/>
@@ -3697,7 +3697,7 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AD24" s="1"/>
@@ -3716,7 +3716,7 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -3731,7 +3731,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Z25" s="1"/>
       <c r="AD25" s="1"/>
@@ -3762,7 +3762,7 @@
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>32</v>
@@ -3770,12 +3770,12 @@
       <c r="Z26" s="1"/>
       <c r="AD26" s="1"/>
     </row>
-    <row r="27" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+    <row r="27" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B27" s="3">
         <v>1999</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -3798,7 +3798,7 @@
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
       <c r="X27" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y27" s="3"/>
       <c r="Z27" s="1"/>
@@ -3820,7 +3820,7 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -3835,7 +3835,7 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z28" s="1"/>
       <c r="AD28" s="1"/>
@@ -3862,7 +3862,7 @@
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
@@ -3874,7 +3874,7 @@
       <c r="Z29" s="1"/>
       <c r="AD29" s="1"/>
     </row>
-    <row r="30" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+    <row r="30" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B30" s="3">
         <v>2002</v>
       </c>
@@ -3900,7 +3900,7 @@
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y30" s="3"/>
       <c r="Z30" s="1"/>
@@ -3962,15 +3962,15 @@
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
       <c r="X32" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Y32" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Z32" s="1"/>
       <c r="AD32" s="1"/>
     </row>
-    <row r="33" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+    <row r="33" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B33" s="3">
         <v>2005</v>
       </c>
@@ -3991,14 +3991,14 @@
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
       <c r="X33" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Y33" s="3"/>
       <c r="Z33" s="1"/>
@@ -4013,19 +4013,19 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
@@ -4037,11 +4037,11 @@
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="X34" s="3"/>
       <c r="Y34" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z34" s="1"/>
       <c r="AD34" s="1"/>
@@ -4071,11 +4071,11 @@
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X35" s="3"/>
       <c r="Y35" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Z35" s="1"/>
       <c r="AD35" s="1"/>
@@ -4085,13 +4085,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4109,11 +4109,11 @@
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X36" s="3"/>
       <c r="Y36" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AD36" s="1"/>
@@ -4144,7 +4144,7 @@
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
       <c r="X37" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Y37" s="3"/>
       <c r="Z37" s="1"/>
@@ -4162,7 +4162,7 @@
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
@@ -4180,7 +4180,7 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y38" s="3"/>
       <c r="Z38" s="1"/>
@@ -4191,15 +4191,15 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -4207,7 +4207,7 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
@@ -4221,11 +4221,11 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X39" s="3"/>
       <c r="Y39" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Z39" s="1"/>
       <c r="AD39" s="1"/>
@@ -4235,16 +4235,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4252,7 +4252,7 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3" t="s">
@@ -4268,7 +4268,7 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Y40" s="3"/>
       <c r="Z40" s="1"/>
@@ -4279,21 +4279,21 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4309,13 +4309,13 @@
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Z41" s="1"/>
       <c r="AD41" s="1"/>
@@ -4325,7 +4325,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4350,10 +4350,10 @@
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y42" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AD42" s="1"/>
@@ -4363,7 +4363,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4377,7 +4377,7 @@
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
@@ -4389,11 +4389,11 @@
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="X43" s="3"/>
       <c r="Y43" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Z43" s="1"/>
       <c r="AD43" s="1"/>
@@ -4403,7 +4403,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
@@ -4430,10 +4430,10 @@
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
       <c r="X44" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Y44" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Z44" s="1"/>
       <c r="AD44" s="1"/>
@@ -4443,7 +4443,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4451,55 +4451,55 @@
         <v>12</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z45" s="1"/>
       <c r="AD45" s="1"/>
     </row>
-    <row r="46" spans="2:30" ht="200" x14ac:dyDescent="0.8">
+    <row r="46" spans="2:30" ht="100" x14ac:dyDescent="0.8">
       <c r="B46" s="3">
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>14</v>
@@ -4508,11 +4508,11 @@
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M46" s="3"/>
       <c r="N46" s="3" t="s">
@@ -4522,22 +4522,22 @@
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Z46" s="1"/>
       <c r="AD46" s="1"/>
@@ -4547,7 +4547,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4555,23 +4555,23 @@
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -4584,10 +4584,10 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
       <c r="X47" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Z47" s="1"/>
       <c r="AD47" s="1"/>
@@ -4597,7 +4597,7 @@
         <v>2020</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -4610,7 +4610,7 @@
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -4619,43 +4619,43 @@
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
       <c r="S48" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y48" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AD48" s="1"/>
     </row>
-    <row r="49" spans="2:30" ht="100" x14ac:dyDescent="0.8">
+    <row r="49" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
       <c r="B49" s="3">
         <v>2021</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>45</v>
+        <v>229</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
@@ -4667,20 +4667,20 @@
       <c r="O49" s="3"/>
       <c r="P49" s="3"/>
       <c r="Q49" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="W49" s="3"/>
       <c r="X49" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Y49" s="3"/>
       <c r="Z49" s="1"/>
@@ -4691,37 +4691,37 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4730,14 +4730,14 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="W50" s="3"/>
       <c r="X50" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y50" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Z50" s="1"/>
       <c r="AD50" s="1"/>
@@ -4750,56 +4750,56 @@
         <v>25</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="W51" s="3"/>
       <c r="X51" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y51" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Z51" s="1"/>
       <c r="AD51" s="1"/>
@@ -4809,7 +4809,7 @@
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>34</v>
@@ -4818,109 +4818,109 @@
         <v>44</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G52" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K52" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="L52" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M52" s="3"/>
       <c r="N52" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y52" s="3"/>
       <c r="Z52" s="1"/>
       <c r="AD52" s="1"/>
     </row>
-    <row r="53" spans="2:30" ht="183.35" x14ac:dyDescent="0.8">
+    <row r="53" spans="2:30" ht="116.7" x14ac:dyDescent="0.8">
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Y53" s="3"/>
       <c r="Z53" s="1"/>
@@ -4933,27 +4933,27 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4962,7 +4962,7 @@
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
       <c r="X54" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y54" s="3"/>
       <c r="Z54" s="1"/>
@@ -4970,33 +4970,33 @@
     </row>
     <row r="55" spans="2:30" ht="83.35" x14ac:dyDescent="0.8">
       <c r="B55" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -5006,7 +5006,7 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y55" s="3"/>
       <c r="Z55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66DABC1-8AB3-405E-98B7-10B221300BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B71F00-9539-4A08-8C1A-ABF9657E1BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5627" yWindow="653" windowWidth="18500" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="1167" yWindow="2687" windowWidth="18500" windowHeight="13466" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -628,10 +628,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>谷もも</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>大空ちえ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1758,6 +1754,13 @@
     </rPh>
     <rPh sb="11" eb="15">
       <t>アライユキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>谷もも(休)</t>
+    <rPh sb="4" eb="5">
+      <t>キュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2769,7 +2772,7 @@
   <sheetData>
     <row r="1" spans="1:30" ht="16" x14ac:dyDescent="0.8">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3023,7 +3026,7 @@
         <v>56</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>87</v>
@@ -3035,7 +3038,7 @@
         <v>8</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>19</v>
@@ -3050,16 +3053,16 @@
         <v>7</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>35</v>
@@ -3342,7 +3345,7 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
       <c r="X13" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Y13" s="3"/>
       <c r="Z13" s="1"/>
@@ -3411,7 +3414,7 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Z15" s="1"/>
       <c r="AD15" s="1"/>
@@ -3476,10 +3479,10 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
       <c r="X17" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y17" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Z17" s="1"/>
       <c r="AD17" s="1"/>
@@ -3662,7 +3665,7 @@
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
       <c r="X23" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>63</v>
@@ -3697,7 +3700,7 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AD24" s="1"/>
@@ -3998,7 +4001,7 @@
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
       <c r="X33" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y33" s="3"/>
       <c r="Z33" s="1"/>
@@ -4013,13 +4016,13 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>90</v>
@@ -4041,7 +4044,7 @@
       </c>
       <c r="X34" s="3"/>
       <c r="Y34" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Z34" s="1"/>
       <c r="AD34" s="1"/>
@@ -4071,11 +4074,11 @@
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X35" s="3"/>
       <c r="Y35" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Z35" s="1"/>
       <c r="AD35" s="1"/>
@@ -4085,13 +4088,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4113,7 +4116,7 @@
       </c>
       <c r="X36" s="3"/>
       <c r="Y36" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AD36" s="1"/>
@@ -4191,15 +4194,15 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -4207,7 +4210,7 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
@@ -4221,11 +4224,11 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X39" s="3"/>
       <c r="Y39" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Z39" s="1"/>
       <c r="AD39" s="1"/>
@@ -4235,16 +4238,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4268,7 +4271,7 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y40" s="3"/>
       <c r="Z40" s="1"/>
@@ -4279,21 +4282,21 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4309,13 +4312,13 @@
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z41" s="1"/>
       <c r="AD41" s="1"/>
@@ -4325,7 +4328,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4350,10 +4353,10 @@
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Y42" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AD42" s="1"/>
@@ -4363,7 +4366,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4389,11 +4392,11 @@
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X43" s="3"/>
       <c r="Y43" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Z43" s="1"/>
       <c r="AD43" s="1"/>
@@ -4403,7 +4406,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
@@ -4430,10 +4433,10 @@
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
       <c r="X44" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Y44" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Z44" s="1"/>
       <c r="AD44" s="1"/>
@@ -4443,7 +4446,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4451,39 +4454,39 @@
         <v>12</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z45" s="1"/>
       <c r="AD45" s="1"/>
@@ -4493,13 +4496,13 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>14</v>
@@ -4512,7 +4515,7 @@
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>92</v>
+        <v>229</v>
       </c>
       <c r="M46" s="3"/>
       <c r="N46" s="3" t="s">
@@ -4526,18 +4529,18 @@
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Z46" s="1"/>
       <c r="AD46" s="1"/>
@@ -4547,7 +4550,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4555,20 +4558,20 @@
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>70</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>53</v>
@@ -4584,10 +4587,10 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
       <c r="X47" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Z47" s="1"/>
       <c r="AD47" s="1"/>
@@ -4610,7 +4613,7 @@
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -4626,10 +4629,10 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y48" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AD48" s="1"/>
@@ -4642,16 +4645,16 @@
         <v>49</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4676,11 +4679,11 @@
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="W49" s="3"/>
       <c r="X49" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Y49" s="3"/>
       <c r="Z49" s="1"/>
@@ -4691,19 +4694,19 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>22</v>
@@ -4715,13 +4718,13 @@
         <v>71</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4730,14 +4733,14 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="W50" s="3"/>
       <c r="X50" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Y50" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Z50" s="1"/>
       <c r="AD50" s="1"/>
@@ -4750,19 +4753,19 @@
         <v>25</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>48</v>
@@ -4773,33 +4776,33 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="W51" s="3"/>
       <c r="X51" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Y51" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Z51" s="1"/>
       <c r="AD51" s="1"/>
@@ -4818,13 +4821,13 @@
         <v>44</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>76</v>
@@ -4833,17 +4836,17 @@
         <v>73</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M52" s="3"/>
       <c r="N52" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
@@ -4852,15 +4855,15 @@
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Y52" s="3"/>
       <c r="Z52" s="1"/>
@@ -4871,56 +4874,56 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y53" s="3"/>
       <c r="Z53" s="1"/>
@@ -4933,27 +4936,27 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4962,7 +4965,7 @@
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
       <c r="X54" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y54" s="3"/>
       <c r="Z54" s="1"/>
@@ -4970,33 +4973,33 @@
     </row>
     <row r="55" spans="2:30" ht="83.35" x14ac:dyDescent="0.8">
       <c r="B55" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -5006,7 +5009,7 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Y55" s="3"/>
       <c r="Z55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B71F00-9539-4A08-8C1A-ABF9657E1BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122D2B10-DC25-4C3E-90F0-600A36B14E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1167" yWindow="2687" windowWidth="18500" windowHeight="13466" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="-67" yWindow="-67" windowWidth="25734" windowHeight="13814" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="230">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1249,13 +1249,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;根本楓花&gt;(プロテスト合格)</t>
-    <rPh sb="12" eb="14">
-      <t>ゴウカク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>シン・広田・葛飾さくら</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1761,6 +1754,18 @@
     <t>谷もも(休)</t>
     <rPh sb="4" eb="5">
       <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;根本楓花&gt;(5.5デビュー予定)
+&lt;生田目真紘&gt;(5.5デビュー予定)
+&lt;西村香矢&gt;(プロテスト合格)</t>
+    <rPh sb="14" eb="16">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ゴウカク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1847,6 +1852,46 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="26">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Noto Serif JP SemiBold"/>
+        <family val="1"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Noto Serif JP SemiBold"/>
+        <family val="1"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1989,46 +2034,6 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2398,23 +2403,23 @@
     <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリゴ" dataDxfId="19"/>
     <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ" dataDxfId="18"/>
     <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="17"/>
-    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="16"/>
-    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{0D2ABC96-F0CF-44E9-912A-CA35E8452616}" name="Venus" dataDxfId="14"/>
-    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="13"/>
-    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="12"/>
-    <tableColumn id="21" xr3:uid="{ACF43FBE-31D7-4ED6-A997-E4AF4BF0B9D4}" name="マーベラス" dataDxfId="11"/>
-    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="10"/>
-    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="9"/>
-    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="8"/>
-    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{3CAB629B-BA9F-4560-89E7-0980EE2B0905}" name="エボリューション" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="3"/>
-    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="0"/>
+    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="1"/>
+    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{0D2ABC96-F0CF-44E9-912A-CA35E8452616}" name="Venus" dataDxfId="15"/>
+    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="14"/>
+    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="13"/>
+    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="12"/>
+    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="11"/>
+    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="10"/>
+    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{3CAB629B-BA9F-4560-89E7-0980EE2B0905}" name="エボリューション" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="5"/>
+    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2747,11 +2752,12 @@
     <col min="5" max="5" width="13.38671875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="20.27734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.94140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.609375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.38671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.609375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.38671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.609375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="26.33203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12.0546875" style="1" bestFit="1" customWidth="1"/>
@@ -2776,7 +2782,7 @@
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="L1" s="1"/>
+      <c r="I1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -2792,7 +2798,7 @@
     <row r="2" spans="1:30" ht="16" x14ac:dyDescent="0.8">
       <c r="B2" s="1">
         <f>SUM(C2:RY2)</f>
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2848,7 +2854,7 @@
      LEN(I5:I1001) - LEN(SUBSTITUTE(I5:I1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" cm="1">
         <f t="array" ref="J2">SUMPRODUCT(
@@ -2872,7 +2878,7 @@
      LEN(L5:L1001) - LEN(SUBSTITUTE(L5:L1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M2" s="1" cm="1">
         <f t="array" ref="M2">SUMPRODUCT(
@@ -2880,7 +2886,7 @@
      LEN(M5:M1001) - LEN(SUBSTITUTE(M5:M1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N2" s="1" cm="1">
         <f t="array" ref="N2">SUMPRODUCT(
@@ -2908,51 +2914,51 @@
       </c>
       <c r="Q2" s="1" cm="1">
         <f t="array" ref="Q2">SUMPRODUCT(
+  IF(LEN(Q5:Q1001)=0, 0,
+     LEN(Q5:Q1001) - LEN(SUBSTITUTE(Q5:Q1001, CHAR(10), "")) + 1
+  )
+)</f>
+        <v>6</v>
+      </c>
+      <c r="R2" s="1" cm="1">
+        <f t="array" ref="R2">SUMPRODUCT(
   IF(LEN(R5:R1001)=0, 0,
      LEN(R5:R1001) - LEN(SUBSTITUTE(R5:R1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="R2" s="1" cm="1">
-        <f t="array" ref="R2">SUMPRODUCT(
+      <c r="S2" s="1" cm="1">
+        <f t="array" ref="S2">SUMPRODUCT(
   IF(LEN(S5:S1001)=0, 0,
      LEN(S5:S1001) - LEN(SUBSTITUTE(S5:S1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="S2" s="1" cm="1">
-        <f t="array" ref="S2">SUMPRODUCT(
+      <c r="T2" s="1" cm="1">
+        <f t="array" ref="T2">SUMPRODUCT(
   IF(LEN(T5:T1001)=0, 0,
      LEN(T5:T1001) - LEN(SUBSTITUTE(T5:T1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="T2" s="1" cm="1">
-        <f t="array" ref="T2">SUMPRODUCT(
+      <c r="U2" s="1" cm="1">
+        <f t="array" ref="U2">SUMPRODUCT(
   IF(LEN(U5:U1001)=0, 0,
      LEN(U5:U1001) - LEN(SUBSTITUTE(U5:U1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="U2" s="1" cm="1">
-        <f t="array" ref="U2">SUMPRODUCT(
+      <c r="V2" s="1" cm="1">
+        <f t="array" ref="V2">SUMPRODUCT(
   IF(LEN(V5:V1001)=0, 0,
      LEN(V5:V1001) - LEN(SUBSTITUTE(V5:V1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
-      </c>
-      <c r="V2" s="1" cm="1">
-        <f t="array" ref="V2">SUMPRODUCT(
-  IF(LEN(W5:W1001)=0, 0,
-     LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
-  )
-)</f>
-        <v>8</v>
       </c>
       <c r="W2" s="1" cm="1">
         <f t="array" ref="W2">SUMPRODUCT(
@@ -2984,7 +2990,7 @@
     <row r="3" spans="1:30" ht="16" x14ac:dyDescent="0.8">
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="L3" s="1"/>
+      <c r="I3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -3020,25 +3026,25 @@
         <v>17</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="L4" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="O4" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>19</v>
@@ -3175,14 +3181,14 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="I8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
@@ -3648,10 +3654,10 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-      <c r="J23" s="3" t="s">
+      <c r="J23" s="3"/>
+      <c r="K23" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
@@ -3665,7 +3671,7 @@
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
       <c r="X23" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>63</v>
@@ -3700,7 +3706,7 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AD24" s="1"/>
@@ -3718,10 +3724,10 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="L25" s="3" t="s">
+      <c r="L25" s="3"/>
+      <c r="M25" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -3822,10 +3828,10 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
-      <c r="L28" s="3" t="s">
+      <c r="L28" s="3"/>
+      <c r="M28" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
@@ -4021,16 +4027,16 @@
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="3" t="s">
+      <c r="K34" s="3"/>
+      <c r="L34" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="L34" s="3" t="s">
+      <c r="M34" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="M34" s="3" t="s">
+      <c r="N34" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="N34" s="3"/>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
@@ -4094,7 +4100,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4116,7 +4122,7 @@
       </c>
       <c r="X36" s="3"/>
       <c r="Y36" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AD36" s="1"/>
@@ -4164,10 +4170,10 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="3" t="s">
+      <c r="J38" s="3"/>
+      <c r="K38" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
@@ -4194,7 +4200,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4209,10 +4215,10 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-      <c r="M39" s="3" t="s">
+      <c r="M39" s="3"/>
+      <c r="N39" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
@@ -4251,16 +4257,16 @@
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
+      <c r="I40" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-      <c r="L40" s="3" t="s">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
@@ -4271,7 +4277,7 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Y40" s="3"/>
       <c r="Z40" s="1"/>
@@ -4282,7 +4288,7 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
@@ -4290,15 +4296,15 @@
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="L41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3" t="s">
+        <v>178</v>
+      </c>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
@@ -4318,7 +4324,7 @@
         <v>145</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z41" s="1"/>
       <c r="AD41" s="1"/>
@@ -4356,7 +4362,7 @@
         <v>135</v>
       </c>
       <c r="Y42" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AD42" s="1"/>
@@ -4366,7 +4372,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4379,10 +4385,10 @@
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
-      <c r="M43" s="3" t="s">
+      <c r="M43" s="3"/>
+      <c r="N43" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
@@ -4406,7 +4412,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
@@ -4415,14 +4421,14 @@
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
+      <c r="I44" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
-      <c r="N44" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="N44" s="3"/>
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
@@ -4436,7 +4442,7 @@
         <v>119</v>
       </c>
       <c r="Y44" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Z44" s="1"/>
       <c r="AD44" s="1"/>
@@ -4446,7 +4452,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4463,13 +4469,13 @@
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
-      <c r="M45" s="3" t="s">
+      <c r="M45" s="3"/>
+      <c r="N45" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
@@ -4496,7 +4502,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>159</v>
@@ -4509,18 +4515,18 @@
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3" t="s">
+      <c r="I46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
@@ -4537,7 +4543,7 @@
         <v>97</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>138</v>
@@ -4550,7 +4556,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4563,20 +4569,20 @@
       <c r="H47" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>191</v>
-      </c>
+      <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K47" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3" t="s">
+      <c r="L47" s="3"/>
+      <c r="M47" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="M47" s="3" t="s">
+      <c r="N47" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="N47" s="3"/>
       <c r="O47" s="3"/>
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
@@ -4590,7 +4596,7 @@
         <v>161</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Z47" s="1"/>
       <c r="AD47" s="1"/>
@@ -4612,10 +4618,10 @@
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
-      <c r="L48" s="3" t="s">
+      <c r="L48" s="3"/>
+      <c r="M48" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="M48" s="3"/>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
       <c r="P48" s="3"/>
@@ -4629,10 +4635,10 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Y48" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AD48" s="1"/>
@@ -4645,10 +4651,10 @@
         <v>49</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>11</v>
@@ -4658,15 +4664,15 @@
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J49" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
-      <c r="N49" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="3"/>
       <c r="Q49" s="3" t="s">
@@ -4694,7 +4700,7 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>152</v>
@@ -4711,20 +4717,20 @@
       <c r="H50" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I50" s="3" t="s">
+      <c r="I50" s="3"/>
+      <c r="J50" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="J50" s="3" t="s">
+      <c r="K50" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="K50" s="3" t="s">
+      <c r="L50" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4740,7 +4746,7 @@
         <v>155</v>
       </c>
       <c r="Y50" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Z50" s="1"/>
       <c r="AD50" s="1"/>
@@ -4753,32 +4759,32 @@
         <v>25</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>108</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="I51" s="3" t="s">
+      <c r="I51" s="3"/>
+      <c r="J51" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="K51" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="K51" s="3"/>
       <c r="L51" s="3"/>
-      <c r="M51" s="3" t="s">
+      <c r="M51" s="3"/>
+      <c r="N51" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="N51" s="3"/>
       <c r="O51" s="3" t="s">
         <v>114</v>
       </c>
@@ -4799,7 +4805,7 @@
       </c>
       <c r="W51" s="3"/>
       <c r="X51" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Y51" s="3" t="s">
         <v>143</v>
@@ -4830,23 +4836,23 @@
         <v>168</v>
       </c>
       <c r="I52" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J52" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="K52" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="K52" s="3" t="s">
+      <c r="L52" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="L52" s="3" t="s">
+      <c r="M52" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3" t="s">
-        <v>110</v>
-      </c>
+      <c r="N52" s="3"/>
       <c r="O52" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
@@ -4874,10 +4880,10 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>173</v>
@@ -4891,21 +4897,21 @@
       <c r="H53" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="I53" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="L53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3" t="s">
+        <v>185</v>
+      </c>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>170</v>
@@ -4919,11 +4925,11 @@
         <v>133</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Y53" s="3"/>
       <c r="Z53" s="1"/>
@@ -4936,27 +4942,27 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
-      <c r="K54" s="3" t="s">
-        <v>193</v>
-      </c>
+      <c r="K54" s="3"/>
       <c r="L54" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="M54" s="3"/>
+        <v>192</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4965,7 +4971,7 @@
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
       <c r="X54" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y54" s="3"/>
       <c r="Z54" s="1"/>
@@ -4977,26 +4983,26 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="J55" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="L55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3" t="s">
+        <v>221</v>
+      </c>
       <c r="M55" s="3"/>
-      <c r="N55" s="3" t="s">
-        <v>176</v>
-      </c>
+      <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
         <v>172</v>
@@ -5009,7 +5015,7 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y55" s="3"/>
       <c r="Z55" s="1"/>
@@ -5023,7 +5029,9 @@
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
+      <c r="I56" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122D2B10-DC25-4C3E-90F0-600A36B14E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382E312D-F58F-4BD5-98DE-2CE34D9A6611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-67" yWindow="-67" windowWidth="25734" windowHeight="13814" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="1167" yWindow="213" windowWidth="18500" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -532,12 +532,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>奏衣エリー
-谷綿ヒヨリ
-広海カホ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>HisokA</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1767,6 +1761,11 @@
     <rPh sb="49" eb="51">
       <t>ゴウカク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奏衣エリー
+広海カホ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1852,26 +1851,6 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="26">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2034,6 +2013,26 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Noto Serif JP SemiBold"/>
+        <family val="1"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2403,23 +2402,23 @@
     <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリゴ" dataDxfId="19"/>
     <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ" dataDxfId="18"/>
     <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="0"/>
-    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="1"/>
-    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{0D2ABC96-F0CF-44E9-912A-CA35E8452616}" name="Venus" dataDxfId="15"/>
-    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="14"/>
-    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="13"/>
-    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="12"/>
-    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="11"/>
-    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="10"/>
-    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{3CAB629B-BA9F-4560-89E7-0980EE2B0905}" name="エボリューション" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="5"/>
-    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="16"/>
+    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{0D2ABC96-F0CF-44E9-912A-CA35E8452616}" name="Venus" dataDxfId="14"/>
+    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="0"/>
+    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="13"/>
+    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="12"/>
+    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="11"/>
+    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="10"/>
+    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="9"/>
+    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{3CAB629B-BA9F-4560-89E7-0980EE2B0905}" name="エボリューション" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="4"/>
+    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2742,7 +2741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4F8F56-06F6-4E1D-8D81-5A485042419D}">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A1:AE56"/>
   <sheetFormatPr defaultColWidth="27.33203125" defaultRowHeight="18" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="1.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -2752,53 +2751,54 @@
     <col min="5" max="5" width="13.38671875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="20.27734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.94140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.609375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.38671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.609375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.0546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.27734375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.94140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.27734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="41.0546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="30.27734375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="30.0546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="27.33203125" style="1"/>
-    <col min="31" max="16384" width="27.33203125" style="1"/>
+    <col min="9" max="9" width="27.71875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.0546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.38671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.609375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.609375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.0546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.27734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.94140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.27734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="41.0546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="30.27734375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="30.0546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="27.33203125" style="1"/>
+    <col min="32" max="16384" width="27.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="16" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:31" ht="16" x14ac:dyDescent="0.8">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="K1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="Q1" s="1"/>
       <c r="S1" s="1"/>
-      <c r="W1" s="1"/>
+      <c r="T1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
-      <c r="AD1" s="1"/>
-    </row>
-    <row r="2" spans="1:30" ht="16" x14ac:dyDescent="0.8">
+      <c r="AA1" s="1"/>
+      <c r="AE1" s="1"/>
+    </row>
+    <row r="2" spans="1:31" ht="16" x14ac:dyDescent="0.8">
       <c r="B2" s="1">
         <f>SUM(C2:RY2)</f>
-        <v>366</v>
+        <v>313</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2878,7 +2878,7 @@
      LEN(L5:L1001) - LEN(SUBSTITUTE(L5:L1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M2" s="1" cm="1">
         <f t="array" ref="M2">SUMPRODUCT(
@@ -2890,120 +2890,122 @@
       </c>
       <c r="N2" s="1" cm="1">
         <f t="array" ref="N2">SUMPRODUCT(
-  IF(LEN(N5:N1001)=0, 0,
-     LEN(N5:N1001) - LEN(SUBSTITUTE(N5:N1001, CHAR(10), "")) + 1
-  )
-)</f>
-        <v>9</v>
-      </c>
-      <c r="O2" s="1" cm="1">
-        <f t="array" ref="O2">SUMPRODUCT(
   IF(LEN(O5:O1001)=0, 0,
      LEN(O5:O1001) - LEN(SUBSTITUTE(O5:O1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>9</v>
       </c>
-      <c r="P2" s="1" cm="1">
-        <f t="array" ref="P2">SUMPRODUCT(
+      <c r="O2" s="1" cm="1">
+        <f t="array" ref="O2">SUMPRODUCT(
   IF(LEN(P5:P1001)=0, 0,
      LEN(P5:P1001) - LEN(SUBSTITUTE(P5:P1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>7</v>
       </c>
-      <c r="Q2" s="1" cm="1">
-        <f t="array" ref="Q2">SUMPRODUCT(
+      <c r="P2" s="1" cm="1">
+        <f t="array" ref="P2">SUMPRODUCT(
   IF(LEN(Q5:Q1001)=0, 0,
      LEN(Q5:Q1001) - LEN(SUBSTITUTE(Q5:Q1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>6</v>
       </c>
-      <c r="R2" s="1" cm="1">
-        <f t="array" ref="R2">SUMPRODUCT(
+      <c r="Q2" s="1" cm="1">
+        <f t="array" ref="Q2">SUMPRODUCT(
   IF(LEN(R5:R1001)=0, 0,
      LEN(R5:R1001) - LEN(SUBSTITUTE(R5:R1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="S2" s="1" cm="1">
-        <f t="array" ref="S2">SUMPRODUCT(
+      <c r="R2" s="1" cm="1">
+        <f t="array" ref="R2">SUMPRODUCT(
   IF(LEN(S5:S1001)=0, 0,
      LEN(S5:S1001) - LEN(SUBSTITUTE(S5:S1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="T2" s="1" cm="1">
-        <f t="array" ref="T2">SUMPRODUCT(
+      <c r="S2" s="1" cm="1">
+        <f t="array" ref="S2">SUMPRODUCT(
   IF(LEN(T5:T1001)=0, 0,
      LEN(T5:T1001) - LEN(SUBSTITUTE(T5:T1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="U2" s="1" cm="1">
-        <f t="array" ref="U2">SUMPRODUCT(
+      <c r="T2" s="1" cm="1">
+        <f t="array" ref="T2">SUMPRODUCT(
   IF(LEN(U5:U1001)=0, 0,
      LEN(U5:U1001) - LEN(SUBSTITUTE(U5:U1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="V2" s="1" cm="1">
-        <f t="array" ref="V2">SUMPRODUCT(
+      <c r="U2" s="1" cm="1">
+        <f t="array" ref="U2">SUMPRODUCT(
   IF(LEN(V5:V1001)=0, 0,
      LEN(V5:V1001) - LEN(SUBSTITUTE(V5:V1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
+      <c r="V2" s="1" cm="1">
+        <f t="array" ref="V2">SUMPRODUCT(
+  IF(LEN(W5:W1001)=0, 0,
+     LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
+  )
+)</f>
+        <v>8</v>
+      </c>
       <c r="W2" s="1" cm="1">
         <f t="array" ref="W2">SUMPRODUCT(
-  IF(LEN(X5:X1001)=0, 0,
-     LEN(X5:X1001) - LEN(SUBSTITUTE(X5:X1001, CHAR(10), "")) + 1
-  )
-)</f>
-        <v>51</v>
-      </c>
-      <c r="X2" s="1" cm="1">
-        <f t="array" ref="X2">SUMPRODUCT(
   IF(LEN(Y5:Y1001)=0, 0,
      LEN(Y5:Y1001) - LEN(SUBSTITUTE(Y5:Y1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>50</v>
       </c>
-      <c r="Y2" s="1" cm="1">
-        <f t="array" ref="Y2">SUMPRODUCT(
+      <c r="X2" s="1" cm="1">
+        <f t="array" ref="X2">SUMPRODUCT(
   IF(LEN(Z5:Z1001)=0, 0,
      LEN(Z5:Z1001) - LEN(SUBSTITUTE(Z5:Z1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>0</v>
       </c>
+      <c r="Y2" s="1" cm="1">
+        <f t="array" ref="Y2">SUMPRODUCT(
+  IF(LEN(AA5:AA1001)=0, 0,
+     LEN(AA5:AA1001) - LEN(SUBSTITUTE(AA5:AA1001, CHAR(10), "")) + 1
+  )
+)</f>
+        <v>0</v>
+      </c>
       <c r="Z2" s="1"/>
-      <c r="AD2" s="1"/>
-    </row>
-    <row r="3" spans="1:30" ht="16" x14ac:dyDescent="0.8">
+      <c r="AA2" s="1"/>
+      <c r="AE2" s="1"/>
+    </row>
+    <row r="3" spans="1:31" ht="16" x14ac:dyDescent="0.8">
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="K3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
-      <c r="R3" s="1"/>
+      <c r="Q3" s="1"/>
       <c r="S3" s="1"/>
-      <c r="W3" s="1"/>
+      <c r="T3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
-      <c r="AD3" s="1"/>
-    </row>
-    <row r="4" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA3" s="1"/>
+      <c r="AE3" s="1"/>
+    </row>
+    <row r="4" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
@@ -3020,7 +3022,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>17</v>
@@ -3032,19 +3034,19 @@
         <v>47</v>
       </c>
       <c r="K4" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="M4" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>50</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>19</v>
@@ -3059,16 +3061,16 @@
         <v>7</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>35</v>
@@ -3077,9 +3079,10 @@
         <v>10</v>
       </c>
       <c r="Z4" s="1"/>
-      <c r="AD4" s="1"/>
-    </row>
-    <row r="5" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA4" s="1"/>
+      <c r="AE4" s="1"/>
+    </row>
+    <row r="5" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B5" s="3">
         <v>1977</v>
       </c>
@@ -3109,9 +3112,10 @@
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="1"/>
-      <c r="AD5" s="1"/>
-    </row>
-    <row r="6" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA5" s="1"/>
+      <c r="AE5" s="1"/>
+    </row>
+    <row r="6" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B6" s="3">
         <v>1978</v>
       </c>
@@ -3139,9 +3143,10 @@
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="1"/>
-      <c r="AD6" s="1"/>
-    </row>
-    <row r="7" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA6" s="1"/>
+      <c r="AE6" s="1"/>
+    </row>
+    <row r="7" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B7" s="3">
         <v>1979</v>
       </c>
@@ -3169,9 +3174,10 @@
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="1"/>
-      <c r="AD7" s="1"/>
-    </row>
-    <row r="8" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA7" s="1"/>
+      <c r="AE7" s="1"/>
+    </row>
+    <row r="8" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B8" s="3">
         <v>1980</v>
       </c>
@@ -3203,9 +3209,10 @@
         <v>30</v>
       </c>
       <c r="Z8" s="1"/>
-      <c r="AD8" s="1"/>
-    </row>
-    <row r="9" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA8" s="1"/>
+      <c r="AE8" s="1"/>
+    </row>
+    <row r="9" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B9" s="3">
         <v>1981</v>
       </c>
@@ -3233,9 +3240,10 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="1"/>
-      <c r="AD9" s="1"/>
-    </row>
-    <row r="10" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA9" s="1"/>
+      <c r="AE9" s="1"/>
+    </row>
+    <row r="10" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B10" s="3">
         <v>1982</v>
       </c>
@@ -3263,9 +3271,10 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="1"/>
-      <c r="AD10" s="1"/>
-    </row>
-    <row r="11" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA10" s="1"/>
+      <c r="AE10" s="1"/>
+    </row>
+    <row r="11" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B11" s="3">
         <v>1983</v>
       </c>
@@ -3293,9 +3302,10 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="1"/>
-      <c r="AD11" s="1"/>
-    </row>
-    <row r="12" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA11" s="1"/>
+      <c r="AE11" s="1"/>
+    </row>
+    <row r="12" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B12" s="3">
         <v>1984</v>
       </c>
@@ -3323,9 +3333,10 @@
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="1"/>
-      <c r="AD12" s="1"/>
-    </row>
-    <row r="13" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA12" s="1"/>
+      <c r="AE12" s="1"/>
+    </row>
+    <row r="13" spans="1:31" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B13" s="3">
         <v>1985</v>
       </c>
@@ -3351,13 +3362,14 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
       <c r="X13" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Y13" s="3"/>
       <c r="Z13" s="1"/>
-      <c r="AD13" s="1"/>
-    </row>
-    <row r="14" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA13" s="1"/>
+      <c r="AE13" s="1"/>
+    </row>
+    <row r="14" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B14" s="3">
         <v>1986</v>
       </c>
@@ -3391,9 +3403,10 @@
         <v>15</v>
       </c>
       <c r="Z14" s="1"/>
-      <c r="AD14" s="1"/>
-    </row>
-    <row r="15" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA14" s="1"/>
+      <c r="AE14" s="1"/>
+    </row>
+    <row r="15" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B15" s="3">
         <v>1987</v>
       </c>
@@ -3420,12 +3433,13 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Z15" s="1"/>
-      <c r="AD15" s="1"/>
-    </row>
-    <row r="16" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA15" s="1"/>
+      <c r="AE15" s="1"/>
+    </row>
+    <row r="16" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B16" s="3">
         <v>1988</v>
       </c>
@@ -3457,9 +3471,10 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="1"/>
-      <c r="AD16" s="1"/>
-    </row>
-    <row r="17" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA16" s="1"/>
+      <c r="AE16" s="1"/>
+    </row>
+    <row r="17" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B17" s="3">
         <v>1989</v>
       </c>
@@ -3485,15 +3500,16 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
       <c r="X17" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y17" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Z17" s="1"/>
-      <c r="AD17" s="1"/>
-    </row>
-    <row r="18" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA17" s="1"/>
+      <c r="AE17" s="1"/>
+    </row>
+    <row r="18" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B18" s="3">
         <v>1990</v>
       </c>
@@ -3521,9 +3537,10 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="1"/>
-      <c r="AD18" s="1"/>
-    </row>
-    <row r="19" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA18" s="1"/>
+      <c r="AE18" s="1"/>
+    </row>
+    <row r="19" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B19" s="3">
         <v>1991</v>
       </c>
@@ -3551,9 +3568,10 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="1"/>
-      <c r="AD19" s="1"/>
-    </row>
-    <row r="20" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA19" s="1"/>
+      <c r="AE19" s="1"/>
+    </row>
+    <row r="20" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B20" s="3">
         <v>1992</v>
       </c>
@@ -3581,9 +3599,10 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="1"/>
-      <c r="AD20" s="1"/>
-    </row>
-    <row r="21" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA20" s="1"/>
+      <c r="AE20" s="1"/>
+    </row>
+    <row r="21" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B21" s="3">
         <v>1993</v>
       </c>
@@ -3611,9 +3630,10 @@
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
       <c r="Z21" s="1"/>
-      <c r="AD21" s="1"/>
-    </row>
-    <row r="22" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA21" s="1"/>
+      <c r="AE21" s="1"/>
+    </row>
+    <row r="22" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B22" s="3">
         <v>1994</v>
       </c>
@@ -3641,9 +3661,10 @@
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="1"/>
-      <c r="AD22" s="1"/>
-    </row>
-    <row r="23" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AA22" s="1"/>
+      <c r="AE22" s="1"/>
+    </row>
+    <row r="23" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B23" s="3">
         <v>1995</v>
       </c>
@@ -3655,10 +3676,10 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="3" t="s">
+      <c r="K23" s="3"/>
+      <c r="L23" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -3671,15 +3692,16 @@
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
       <c r="X23" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>63</v>
       </c>
       <c r="Z23" s="1"/>
-      <c r="AD23" s="1"/>
-    </row>
-    <row r="24" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA23" s="1"/>
+      <c r="AE23" s="1"/>
+    </row>
+    <row r="24" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B24" s="3">
         <v>1996</v>
       </c>
@@ -3706,12 +3728,13 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Z24" s="1"/>
-      <c r="AD24" s="1"/>
-    </row>
-    <row r="25" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA24" s="1"/>
+      <c r="AE24" s="1"/>
+    </row>
+    <row r="25" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B25" s="3">
         <v>1997</v>
       </c>
@@ -3726,7 +3749,7 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -3740,12 +3763,13 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Z25" s="1"/>
-      <c r="AD25" s="1"/>
-    </row>
-    <row r="26" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA25" s="1"/>
+      <c r="AE25" s="1"/>
+    </row>
+    <row r="26" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B26" s="3">
         <v>1998</v>
       </c>
@@ -3771,15 +3795,16 @@
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="Z26" s="1"/>
-      <c r="AD26" s="1"/>
-    </row>
-    <row r="27" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA26" s="1"/>
+      <c r="AE26" s="1"/>
+    </row>
+    <row r="27" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B27" s="3">
         <v>1999</v>
       </c>
@@ -3807,13 +3832,14 @@
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
       <c r="X27" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y27" s="3"/>
       <c r="Z27" s="1"/>
-      <c r="AD27" s="1"/>
-    </row>
-    <row r="28" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AA27" s="1"/>
+      <c r="AE27" s="1"/>
+    </row>
+    <row r="28" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B28" s="3">
         <v>2000</v>
       </c>
@@ -3830,7 +3856,7 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -3844,12 +3870,13 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z28" s="1"/>
-      <c r="AD28" s="1"/>
-    </row>
-    <row r="29" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA28" s="1"/>
+      <c r="AE28" s="1"/>
+    </row>
+    <row r="29" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B29" s="3">
         <v>2001</v>
       </c>
@@ -3881,9 +3908,10 @@
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
       <c r="Z29" s="1"/>
-      <c r="AD29" s="1"/>
-    </row>
-    <row r="30" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA29" s="1"/>
+      <c r="AE29" s="1"/>
+    </row>
+    <row r="30" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B30" s="3">
         <v>2002</v>
       </c>
@@ -3909,13 +3937,14 @@
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y30" s="3"/>
       <c r="Z30" s="1"/>
-      <c r="AD30" s="1"/>
-    </row>
-    <row r="31" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA30" s="1"/>
+      <c r="AE30" s="1"/>
+    </row>
+    <row r="31" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B31" s="3">
         <v>2003</v>
       </c>
@@ -3943,9 +3972,10 @@
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
       <c r="Z31" s="1"/>
-      <c r="AD31" s="1"/>
-    </row>
-    <row r="32" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AA31" s="1"/>
+      <c r="AE31" s="1"/>
+    </row>
+    <row r="32" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B32" s="3">
         <v>2004</v>
       </c>
@@ -3974,12 +4004,13 @@
         <v>59</v>
       </c>
       <c r="Y32" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z32" s="1"/>
-      <c r="AD32" s="1"/>
-    </row>
-    <row r="33" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AA32" s="1"/>
+      <c r="AE32" s="1"/>
+    </row>
+    <row r="33" spans="2:31" ht="50" x14ac:dyDescent="0.8">
       <c r="B33" s="3">
         <v>2005</v>
       </c>
@@ -4000,20 +4031,21 @@
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
       <c r="X33" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Y33" s="3"/>
       <c r="Z33" s="1"/>
-      <c r="AD33" s="1"/>
-    </row>
-    <row r="34" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
+      <c r="AA33" s="1"/>
+      <c r="AE33" s="1"/>
+    </row>
+    <row r="34" spans="2:31" ht="66.7" x14ac:dyDescent="0.8">
       <c r="B34" s="3">
         <v>2006</v>
       </c>
@@ -4022,17 +4054,17 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3" t="s">
-        <v>166</v>
-      </c>
+      <c r="K34" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>51</v>
@@ -4050,12 +4082,13 @@
       </c>
       <c r="X34" s="3"/>
       <c r="Y34" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Z34" s="1"/>
-      <c r="AD34" s="1"/>
-    </row>
-    <row r="35" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+      <c r="AA34" s="1"/>
+      <c r="AE34" s="1"/>
+    </row>
+    <row r="35" spans="2:31" ht="50" x14ac:dyDescent="0.8">
       <c r="B35" s="3">
         <v>2007</v>
       </c>
@@ -4080,27 +4113,28 @@
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X35" s="3"/>
       <c r="Y35" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Z35" s="1"/>
-      <c r="AD35" s="1"/>
-    </row>
-    <row r="36" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AA35" s="1"/>
+      <c r="AE35" s="1"/>
+    </row>
+    <row r="36" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B36" s="3">
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4122,12 +4156,13 @@
       </c>
       <c r="X36" s="3"/>
       <c r="Y36" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Z36" s="1"/>
-      <c r="AD36" s="1"/>
-    </row>
-    <row r="37" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA36" s="1"/>
+      <c r="AE36" s="1"/>
+    </row>
+    <row r="37" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B37" s="3">
         <v>2009</v>
       </c>
@@ -4157,9 +4192,10 @@
       </c>
       <c r="Y37" s="3"/>
       <c r="Z37" s="1"/>
-      <c r="AD37" s="1"/>
-    </row>
-    <row r="38" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+      <c r="AA37" s="1"/>
+      <c r="AE37" s="1"/>
+    </row>
+    <row r="38" spans="2:31" ht="50" x14ac:dyDescent="0.8">
       <c r="B38" s="3">
         <v>2010</v>
       </c>
@@ -4171,10 +4207,10 @@
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="3" t="s">
+      <c r="K38" s="3"/>
+      <c r="L38" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="L38" s="3"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
@@ -4189,26 +4225,27 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y38" s="3"/>
       <c r="Z38" s="1"/>
-      <c r="AD38" s="1"/>
-    </row>
-    <row r="39" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AA38" s="1"/>
+      <c r="AE38" s="1"/>
+    </row>
+    <row r="39" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B39" s="3">
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -4217,7 +4254,7 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
@@ -4230,30 +4267,31 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X39" s="3"/>
       <c r="Y39" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Z39" s="1"/>
-      <c r="AD39" s="1"/>
-    </row>
-    <row r="40" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA39" s="1"/>
+      <c r="AE39" s="1"/>
+    </row>
+    <row r="40" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B40" s="3">
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4264,7 +4302,7 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
@@ -4277,34 +4315,35 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Y40" s="3"/>
       <c r="Z40" s="1"/>
-      <c r="AD40" s="1"/>
-    </row>
-    <row r="41" spans="2:30" ht="100" x14ac:dyDescent="0.8">
+      <c r="AA40" s="1"/>
+      <c r="AE40" s="1"/>
+    </row>
+    <row r="41" spans="2:31" ht="100" x14ac:dyDescent="0.8">
       <c r="B41" s="3">
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3" t="s">
-        <v>178</v>
-      </c>
+      <c r="K41" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
@@ -4318,23 +4357,24 @@
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z41" s="1"/>
-      <c r="AD41" s="1"/>
-    </row>
-    <row r="42" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AA41" s="1"/>
+      <c r="AE41" s="1"/>
+    </row>
+    <row r="42" spans="2:31" ht="50" x14ac:dyDescent="0.8">
       <c r="B42" s="3">
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4359,20 +4399,21 @@
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y42" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Z42" s="1"/>
-      <c r="AD42" s="1"/>
-    </row>
-    <row r="43" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
+      <c r="AA42" s="1"/>
+      <c r="AE42" s="1"/>
+    </row>
+    <row r="43" spans="2:31" ht="66.7" x14ac:dyDescent="0.8">
       <c r="B43" s="3">
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4398,21 +4439,22 @@
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X43" s="3"/>
       <c r="Y43" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Z43" s="1"/>
-      <c r="AD43" s="1"/>
-    </row>
-    <row r="44" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+      <c r="AA43" s="1"/>
+      <c r="AE43" s="1"/>
+    </row>
+    <row r="44" spans="2:31" ht="50" x14ac:dyDescent="0.8">
       <c r="B44" s="3">
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
@@ -4439,20 +4481,21 @@
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
       <c r="X44" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y44" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Z44" s="1"/>
-      <c r="AD44" s="1"/>
-    </row>
-    <row r="45" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AA44" s="1"/>
+      <c r="AE44" s="1"/>
+    </row>
+    <row r="45" spans="2:31" ht="66.7" x14ac:dyDescent="0.8">
       <c r="B45" s="3">
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4460,10 +4503,10 @@
         <v>12</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -4471,44 +4514,45 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Z45" s="1"/>
-      <c r="AD45" s="1"/>
-    </row>
-    <row r="46" spans="2:30" ht="100" x14ac:dyDescent="0.8">
+      <c r="AA45" s="1"/>
+      <c r="AE45" s="1"/>
+    </row>
+    <row r="46" spans="2:31" ht="200" x14ac:dyDescent="0.8">
       <c r="B46" s="3">
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>14</v>
@@ -4519,12 +4563,12 @@
         <v>29</v>
       </c>
       <c r="J46" s="3"/>
-      <c r="K46" s="3" t="s">
+      <c r="K46" s="3"/>
+      <c r="L46" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -4535,28 +4579,29 @@
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Z46" s="1"/>
-      <c r="AD46" s="1"/>
-    </row>
-    <row r="47" spans="2:30" ht="100" x14ac:dyDescent="0.8">
+      <c r="AA46" s="1"/>
+      <c r="AE46" s="1"/>
+    </row>
+    <row r="47" spans="2:31" ht="100" x14ac:dyDescent="0.8">
       <c r="B47" s="3">
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4564,21 +4609,21 @@
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="K47" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>53</v>
@@ -4593,15 +4638,16 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
       <c r="X47" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Z47" s="1"/>
-      <c r="AD47" s="1"/>
-    </row>
-    <row r="48" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+      <c r="AA47" s="1"/>
+      <c r="AE47" s="1"/>
+    </row>
+    <row r="48" spans="2:31" ht="66.7" x14ac:dyDescent="0.8">
       <c r="B48" s="3">
         <v>2020</v>
       </c>
@@ -4620,7 +4666,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
@@ -4628,22 +4674,23 @@
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
       <c r="S48" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y48" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Z48" s="1"/>
-      <c r="AD48" s="1"/>
-    </row>
-    <row r="49" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
+      <c r="AA48" s="1"/>
+      <c r="AE48" s="1"/>
+    </row>
+    <row r="49" spans="2:31" ht="116.7" x14ac:dyDescent="0.8">
       <c r="B49" s="3">
         <v>2021</v>
       </c>
@@ -4651,23 +4698,23 @@
         <v>49</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
         <v>28</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
@@ -4685,52 +4732,53 @@
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="W49" s="3"/>
       <c r="X49" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Y49" s="3"/>
       <c r="Z49" s="1"/>
-      <c r="AD49" s="1"/>
-    </row>
-    <row r="50" spans="2:30" ht="133.35" x14ac:dyDescent="0.8">
+      <c r="AA49" s="1"/>
+      <c r="AE49" s="1"/>
+    </row>
+    <row r="50" spans="2:31" ht="133.35" x14ac:dyDescent="0.8">
       <c r="B50" s="3">
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K50" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="L50" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4739,19 +4787,20 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="W50" s="3"/>
       <c r="X50" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Y50" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Z50" s="1"/>
-      <c r="AD50" s="1"/>
-    </row>
-    <row r="51" spans="2:30" ht="100" x14ac:dyDescent="0.8">
+      <c r="AA50" s="1"/>
+      <c r="AE50" s="1"/>
+    </row>
+    <row r="51" spans="2:31" ht="100" x14ac:dyDescent="0.8">
       <c r="B51" s="3">
         <v>2023</v>
       </c>
@@ -4759,61 +4808,62 @@
         <v>25</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="K51" s="3" t="s">
+      <c r="K51" s="3"/>
+      <c r="L51" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="W51" s="3"/>
       <c r="X51" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Y51" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Z51" s="1"/>
-      <c r="AD51" s="1"/>
-    </row>
-    <row r="52" spans="2:30" ht="100" x14ac:dyDescent="0.8">
+      <c r="AA51" s="1"/>
+      <c r="AE51" s="1"/>
+    </row>
+    <row r="52" spans="2:31" ht="100" x14ac:dyDescent="0.8">
       <c r="B52" s="3">
         <v>2024</v>
       </c>
@@ -4827,32 +4877,32 @@
         <v>44</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G52" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="K52" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="I52" s="3" t="s">
+      <c r="L52" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="M52" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
@@ -4861,108 +4911,110 @@
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Y52" s="3"/>
       <c r="Z52" s="1"/>
-      <c r="AD52" s="1"/>
-    </row>
-    <row r="53" spans="2:30" ht="116.7" x14ac:dyDescent="0.8">
+      <c r="AA52" s="1"/>
+      <c r="AE52" s="1"/>
+    </row>
+    <row r="53" spans="2:31" ht="250" x14ac:dyDescent="0.8">
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3" t="s">
-        <v>185</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Y53" s="3"/>
       <c r="Z53" s="1"/>
-      <c r="AD53" s="1"/>
-    </row>
-    <row r="54" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+      <c r="AA53" s="1"/>
+      <c r="AE53" s="1"/>
+    </row>
+    <row r="54" spans="2:31" ht="50" x14ac:dyDescent="0.8">
       <c r="B54" s="3">
         <v>2026</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3" t="s">
-        <v>192</v>
-      </c>
+      <c r="K54" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4971,41 +5023,42 @@
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
       <c r="X54" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Y54" s="3"/>
       <c r="Z54" s="1"/>
-      <c r="AD54" s="1"/>
-    </row>
-    <row r="55" spans="2:30" ht="83.35" x14ac:dyDescent="0.8">
+      <c r="AA54" s="1"/>
+      <c r="AE54" s="1"/>
+    </row>
+    <row r="55" spans="2:31" ht="200" x14ac:dyDescent="0.8">
       <c r="B55" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3" t="s">
-        <v>221</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -5015,13 +5068,14 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Y55" s="3"/>
       <c r="Z55" s="1"/>
-      <c r="AD55" s="1"/>
-    </row>
-    <row r="56" spans="2:30" x14ac:dyDescent="0.8">
+      <c r="AA55" s="1"/>
+      <c r="AE55" s="1"/>
+    </row>
+    <row r="56" spans="2:31" x14ac:dyDescent="0.8">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -5030,7 +5084,7 @@
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
@@ -5049,8 +5103,9 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="1"/>
+      <c r="AA56" s="1"/>
       <c r="AC56"/>
-      <c r="AD56" s="1"/>
+      <c r="AE56" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382E312D-F58F-4BD5-98DE-2CE34D9A6611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57F0F26-B8EC-47C9-B3A9-471A18CD14D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1167" yWindow="213" windowWidth="18500" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="1173" yWindow="213" windowWidth="18500" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -1752,20 +1752,47 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;根本楓花&gt;(5.5デビュー予定)
-&lt;生田目真紘&gt;(5.5デビュー予定)
-&lt;西村香矢&gt;(プロテスト合格)</t>
-    <rPh sb="14" eb="16">
-      <t>ヨテイ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ゴウカク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>奏衣エリー
 広海カホ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;天羽瑠迦&gt;(あまはねるか, 5.5デビュー予定)
+&lt;早乙女聖&gt;(さおとめひじり, 5.5デビュー予定)
+&lt;州王叶多&gt;(すおうかなた, プロテスト合格)</t>
+    <rPh sb="1" eb="2">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ハネ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>サオトメ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ヒジリ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>カナタ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ゴウカク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1851,26 +1878,6 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="26">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2013,6 +2020,26 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Noto Serif JP SemiBold"/>
+        <family val="1"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2405,20 +2432,20 @@
     <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="16"/>
     <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="15"/>
     <tableColumn id="8" xr3:uid="{0D2ABC96-F0CF-44E9-912A-CA35E8452616}" name="Venus" dataDxfId="14"/>
-    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="0"/>
-    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="13"/>
-    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="12"/>
-    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="11"/>
-    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="10"/>
-    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="9"/>
-    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{3CAB629B-BA9F-4560-89E7-0980EE2B0905}" name="エボリューション" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="4"/>
-    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="1"/>
+    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="13"/>
+    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="11"/>
+    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="10"/>
+    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="9"/>
+    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="8"/>
+    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{3CAB629B-BA9F-4560-89E7-0980EE2B0905}" name="エボリューション" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="3"/>
+    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4895,7 +4922,7 @@
         <v>162</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>110</v>
@@ -5045,7 +5072,7 @@
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>170</v>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57F0F26-B8EC-47C9-B3A9-471A18CD14D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBFA6C0-2606-42DB-99F2-529801122462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1173" yWindow="213" windowWidth="18500" windowHeight="13467" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="-67" yWindow="-67" windowWidth="25734" windowHeight="13814" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -1006,20 +1006,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>松下楓歩(IR)
-キク(HCC)(2026/3引退予定)</t>
-    <rPh sb="0" eb="4">
-      <t>マツシタカホ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>インタイ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>山下実優
 中島翔子
 上福ゆき</t>
@@ -1792,6 +1778,13 @@
     </rPh>
     <rPh sb="73" eb="75">
       <t>ゴウカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>松下楓歩(IR)</t>
+    <rPh sb="0" eb="4">
+      <t>マツシタカホ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2825,7 +2818,7 @@
     <row r="2" spans="1:31" ht="16" x14ac:dyDescent="0.8">
       <c r="B2" s="1">
         <f>SUM(C2:RY2)</f>
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2865,7 +2858,7 @@
      LEN(G5:G1001) - LEN(SUBSTITUTE(G5:G1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H2" s="1" cm="1">
         <f t="array" ref="H2">SUMPRODUCT(
@@ -3061,7 +3054,7 @@
         <v>47</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>56</v>
@@ -3073,7 +3066,7 @@
         <v>50</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>19</v>
@@ -3094,7 +3087,7 @@
         <v>129</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>92</v>
@@ -3719,7 +3712,7 @@
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
       <c r="X23" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>63</v>
@@ -3755,7 +3748,7 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
@@ -4081,13 +4074,13 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
@@ -4155,13 +4148,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4183,7 +4176,7 @@
       </c>
       <c r="X36" s="3"/>
       <c r="Y36" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
@@ -4264,7 +4257,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4312,7 +4305,7 @@
         <v>135</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>41</v>
@@ -4342,7 +4335,7 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y40" s="3"/>
       <c r="Z40" s="1"/>
@@ -4354,21 +4347,21 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4390,7 +4383,7 @@
         <v>144</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
@@ -4401,7 +4394,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4429,7 +4422,7 @@
         <v>134</v>
       </c>
       <c r="Y42" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
@@ -4440,7 +4433,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4470,7 +4463,7 @@
       </c>
       <c r="X43" s="3"/>
       <c r="Y43" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
@@ -4481,7 +4474,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
@@ -4511,7 +4504,7 @@
         <v>118</v>
       </c>
       <c r="Y44" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
@@ -4522,7 +4515,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4545,7 +4538,7 @@
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
@@ -4573,13 +4566,13 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>14</v>
@@ -4595,7 +4588,7 @@
         <v>69</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -4614,7 +4607,7 @@
         <v>96</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>137</v>
@@ -4628,7 +4621,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4643,7 +4636,7 @@
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4665,10 +4658,10 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
       <c r="X47" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
@@ -4708,10 +4701,10 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y48" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
@@ -4725,16 +4718,16 @@
         <v>49</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>145</v>
+        <v>229</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4759,11 +4752,11 @@
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="W49" s="3"/>
       <c r="X49" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Y49" s="3"/>
       <c r="Z49" s="1"/>
@@ -4775,19 +4768,19 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>22</v>
@@ -4797,7 +4790,7 @@
         <v>73</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>71</v>
@@ -4805,7 +4798,7 @@
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4814,14 +4807,14 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="W50" s="3"/>
       <c r="X50" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Y50" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
@@ -4835,16 +4828,16 @@
         <v>25</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>107</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>112</v>
@@ -4859,7 +4852,7 @@
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O51" s="3" t="s">
         <v>113</v>
@@ -4877,11 +4870,11 @@
         <v>131</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="W51" s="3"/>
       <c r="X51" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y51" s="3" t="s">
         <v>142</v>
@@ -4907,10 +4900,10 @@
         <v>133</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>109</v>
@@ -4919,17 +4912,17 @@
         <v>75</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>110</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
@@ -4958,13 +4951,13 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>106</v>
@@ -4973,26 +4966,26 @@
         <v>98</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
@@ -5003,11 +4996,11 @@
         <v>132</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Y53" s="3"/>
       <c r="Z53" s="1"/>
@@ -5021,27 +5014,27 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -5050,7 +5043,7 @@
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
       <c r="X54" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y54" s="3"/>
       <c r="Z54" s="1"/>
@@ -5059,33 +5052,33 @@
     </row>
     <row r="55" spans="2:31" ht="200" x14ac:dyDescent="0.8">
       <c r="B55" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -5095,7 +5088,7 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y55" s="3"/>
       <c r="Z55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBFA6C0-2606-42DB-99F2-529801122462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01A2142-0922-4C89-B36E-51E608182D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-67" yWindow="-67" windowWidth="25734" windowHeight="13814" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -4286,9 +4286,7 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-      <c r="W39" s="3" t="s">
-        <v>94</v>
-      </c>
+      <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3" t="s">
         <v>141</v>
@@ -4333,7 +4331,9 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
+      <c r="W40" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="X40" s="3" t="s">
         <v>199</v>
       </c>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01A2142-0922-4C89-B36E-51E608182D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2836D590-C605-4F1E-96DB-E2C1F80106A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-67" yWindow="-67" windowWidth="25734" windowHeight="13814" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="226">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -873,23 +873,6 @@
   </si>
   <si>
     <t>キャサリン.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エボリューション</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ソイ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Chi Chi
-ZONES</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CHIKA</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -992,15 +975,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>郷田明日香(休)
-ブランキー真帆</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>浦幌ちほ(北都)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>YAKO(アルマリブレ)
 神田愛実(北都)</t>
     <phoneticPr fontId="1"/>
@@ -1575,22 +1549,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>苺畑ひより(666)
-横井真菜(REINA)
-タギリヒメ真夢(九州女子プロレス)
-彩月悠叶(2AW)
-さいとう(アップタウン)
-しおの(アップタウン)
-小久保アリサ(BBJ)</t>
-    <rPh sb="31" eb="33">
-      <t>キュウシュウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ジョシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>梨央
 弥福かな
 ゴんべ
@@ -1786,6 +1744,35 @@
     <rPh sb="0" eb="4">
       <t>マツシタカホ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>郷田明日香(休)
+ブランキー真帆
+Chi Chi
+ZONES</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>苺畑ひより(666)
+横井真菜(REINA)
+タギリヒメ真夢(九州女子プロレス)
+彩月悠叶(2AW)
+さいとう(アップタウン)
+しおの(アップタウン)
+小久保アリサ(BBJ)
+CHIKA(EVO)</t>
+    <rPh sb="31" eb="33">
+      <t>キュウシュウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジョシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>浦幌ちほ(北都)
+ソイ(EVO)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1870,7 +1857,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="25">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1891,26 +1878,6 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2412,29 +2379,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}" name="テーブル1" displayName="テーブル1" ref="B4:Y56" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
-  <autoFilter ref="B4:Y56" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}"/>
-  <tableColumns count="24">
-    <tableColumn id="1" xr3:uid="{C5BCADDE-F600-4480-BD2B-E93168A1BF7F}" name="デビュー年" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{7319872F-B1DE-47E8-ADFA-F5962E445AE2}" name="Stardom" dataDxfId="22"/>
-    <tableColumn id="18" xr3:uid="{6DD05DFF-D195-4CF5-BFC5-531553A9ADC5}" name="AWG" dataDxfId="21"/>
-    <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリゴ" dataDxfId="19"/>
-    <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ" dataDxfId="18"/>
-    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="16"/>
-    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{0D2ABC96-F0CF-44E9-912A-CA35E8452616}" name="Venus" dataDxfId="14"/>
-    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="13"/>
-    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="12"/>
-    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="11"/>
-    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="10"/>
-    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="9"/>
-    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="8"/>
-    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{3CAB629B-BA9F-4560-89E7-0980EE2B0905}" name="エボリューション" dataDxfId="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}" name="テーブル1" displayName="テーブル1" ref="B4:X56" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+  <autoFilter ref="B4:X56" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}"/>
+  <tableColumns count="23">
+    <tableColumn id="1" xr3:uid="{C5BCADDE-F600-4480-BD2B-E93168A1BF7F}" name="デビュー年" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{7319872F-B1DE-47E8-ADFA-F5962E445AE2}" name="Stardom" dataDxfId="21"/>
+    <tableColumn id="18" xr3:uid="{6DD05DFF-D195-4CF5-BFC5-531553A9ADC5}" name="AWG" dataDxfId="20"/>
+    <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリゴ" dataDxfId="18"/>
+    <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ" dataDxfId="17"/>
+    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="15"/>
+    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{0D2ABC96-F0CF-44E9-912A-CA35E8452616}" name="Venus" dataDxfId="13"/>
+    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="12"/>
+    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="11"/>
+    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="10"/>
+    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="9"/>
+    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="8"/>
+    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="7"/>
+    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="4"/>
     <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="3"/>
     <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="2"/>
     <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="1"/>
@@ -2761,7 +2727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4F8F56-06F6-4E1D-8D81-5A485042419D}">
-  <dimension ref="A1:AE56"/>
+  <dimension ref="A1:AD56"/>
   <sheetFormatPr defaultColWidth="27.33203125" defaultRowHeight="18" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="1.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -2778,24 +2744,23 @@
     <col min="13" max="13" width="13.5" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.609375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.0546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.27734375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.94140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.27734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="41.0546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="30.27734375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="30.0546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="27.33203125" style="1"/>
-    <col min="32" max="16384" width="27.33203125" style="1"/>
+    <col min="17" max="17" width="10.27734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.94140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.27734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="41.0546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="30.27734375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="30.0546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="27.33203125" style="1"/>
+    <col min="31" max="16384" width="27.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="16" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:30" ht="16" x14ac:dyDescent="0.8">
       <c r="A1" s="1" t="s">
         <v>102</v>
       </c>
@@ -2809,16 +2774,16 @@
       <c r="Q1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
+      <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AE1" s="1"/>
-    </row>
-    <row r="2" spans="1:31" ht="16" x14ac:dyDescent="0.8">
+      <c r="AD1" s="1"/>
+    </row>
+    <row r="2" spans="1:30" ht="16" x14ac:dyDescent="0.8">
       <c r="B2" s="1">
-        <f>SUM(C2:RY2)</f>
-        <v>312</v>
+        <f>SUM(C2:RX2)</f>
+        <v>372</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2910,105 +2875,97 @@
       </c>
       <c r="N2" s="1" cm="1">
         <f t="array" ref="N2">SUMPRODUCT(
+  IF(LEN(N5:N1001)=0, 0,
+     LEN(N5:N1001) - LEN(SUBSTITUTE(N5:N1001, CHAR(10), "")) + 1
+  )
+)</f>
+        <v>9</v>
+      </c>
+      <c r="O2" s="1" cm="1">
+        <f t="array" ref="O2">SUMPRODUCT(
   IF(LEN(O5:O1001)=0, 0,
      LEN(O5:O1001) - LEN(SUBSTITUTE(O5:O1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>9</v>
       </c>
-      <c r="O2" s="1" cm="1">
-        <f t="array" ref="O2">SUMPRODUCT(
+      <c r="P2" s="1" cm="1">
+        <f t="array" ref="P2">SUMPRODUCT(
   IF(LEN(P5:P1001)=0, 0,
      LEN(P5:P1001) - LEN(SUBSTITUTE(P5:P1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>7</v>
       </c>
-      <c r="P2" s="1" cm="1">
-        <f t="array" ref="P2">SUMPRODUCT(
+      <c r="Q2" s="1" cm="1">
+        <f t="array" ref="Q2">SUMPRODUCT(
   IF(LEN(Q5:Q1001)=0, 0,
      LEN(Q5:Q1001) - LEN(SUBSTITUTE(Q5:Q1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>6</v>
       </c>
-      <c r="Q2" s="1" cm="1">
-        <f t="array" ref="Q2">SUMPRODUCT(
+      <c r="R2" s="1" cm="1">
+        <f t="array" ref="R2">SUMPRODUCT(
   IF(LEN(R5:R1001)=0, 0,
      LEN(R5:R1001) - LEN(SUBSTITUTE(R5:R1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="R2" s="1" cm="1">
-        <f t="array" ref="R2">SUMPRODUCT(
+      <c r="S2" s="1" cm="1">
+        <f t="array" ref="S2">SUMPRODUCT(
   IF(LEN(S5:S1001)=0, 0,
      LEN(S5:S1001) - LEN(SUBSTITUTE(S5:S1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="S2" s="1" cm="1">
-        <f t="array" ref="S2">SUMPRODUCT(
+      <c r="T2" s="1" cm="1">
+        <f t="array" ref="T2">SUMPRODUCT(
   IF(LEN(T5:T1001)=0, 0,
      LEN(T5:T1001) - LEN(SUBSTITUTE(T5:T1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="T2" s="1" cm="1">
-        <f t="array" ref="T2">SUMPRODUCT(
+      <c r="U2" s="1" cm="1">
+        <f t="array" ref="U2">SUMPRODUCT(
   IF(LEN(U5:U1001)=0, 0,
      LEN(U5:U1001) - LEN(SUBSTITUTE(U5:U1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="U2" s="1" cm="1">
-        <f t="array" ref="U2">SUMPRODUCT(
+      <c r="V2" s="1" cm="1">
+        <f t="array" ref="V2">SUMPRODUCT(
   IF(LEN(V5:V1001)=0, 0,
      LEN(V5:V1001) - LEN(SUBSTITUTE(V5:V1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>4</v>
-      </c>
-      <c r="V2" s="1" cm="1">
-        <f t="array" ref="V2">SUMPRODUCT(
+        <v>8</v>
+      </c>
+      <c r="W2" s="1" cm="1">
+        <f t="array" ref="W2">SUMPRODUCT(
   IF(LEN(W5:W1001)=0, 0,
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>8</v>
-      </c>
-      <c r="W2" s="1" cm="1">
-        <f t="array" ref="W2">SUMPRODUCT(
-  IF(LEN(Y5:Y1001)=0, 0,
-     LEN(Y5:Y1001) - LEN(SUBSTITUTE(Y5:Y1001, CHAR(10), "")) + 1
+        <v>53</v>
+      </c>
+      <c r="X2" s="1" cm="1">
+        <f t="array" ref="X2">SUMPRODUCT(
+  IF(LEN(X5:X1001)=0, 0,
+     LEN(X5:X1001) - LEN(SUBSTITUTE(X5:X1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>50</v>
-      </c>
-      <c r="X2" s="1" cm="1">
-        <f t="array" ref="X2">SUMPRODUCT(
-  IF(LEN(Z5:Z1001)=0, 0,
-     LEN(Z5:Z1001) - LEN(SUBSTITUTE(Z5:Z1001, CHAR(10), "")) + 1
-  )
-)</f>
-        <v>0</v>
-      </c>
-      <c r="Y2" s="1" cm="1">
-        <f t="array" ref="Y2">SUMPRODUCT(
-  IF(LEN(AA5:AA1001)=0, 0,
-     LEN(AA5:AA1001) - LEN(SUBSTITUTE(AA5:AA1001, CHAR(10), "")) + 1
-  )
-)</f>
-        <v>0</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AE2" s="1"/>
-    </row>
-    <row r="3" spans="1:31" ht="16" x14ac:dyDescent="0.8">
+      <c r="AD2" s="1"/>
+    </row>
+    <row r="3" spans="1:30" ht="16" x14ac:dyDescent="0.8">
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
@@ -3019,13 +2976,13 @@
       <c r="Q3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
+      <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AE3" s="1"/>
-    </row>
-    <row r="4" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD3" s="1"/>
+    </row>
+    <row r="4" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
@@ -3054,7 +3011,7 @@
         <v>47</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>56</v>
@@ -3066,7 +3023,7 @@
         <v>50</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>19</v>
@@ -3084,25 +3041,22 @@
         <v>120</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y4" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AE4" s="1"/>
-    </row>
-    <row r="5" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD4" s="1"/>
+    </row>
+    <row r="5" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B5" s="3">
         <v>1977</v>
       </c>
@@ -3130,12 +3084,11 @@
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
+      <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AE5" s="1"/>
-    </row>
-    <row r="6" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD5" s="1"/>
+    </row>
+    <row r="6" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B6" s="3">
         <v>1978</v>
       </c>
@@ -3161,12 +3114,11 @@
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
+      <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AE6" s="1"/>
-    </row>
-    <row r="7" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD6" s="1"/>
+    </row>
+    <row r="7" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B7" s="3">
         <v>1979</v>
       </c>
@@ -3192,12 +3144,11 @@
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
+      <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-      <c r="AE7" s="1"/>
-    </row>
-    <row r="8" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD7" s="1"/>
+    </row>
+    <row r="8" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B8" s="3">
         <v>1980</v>
       </c>
@@ -3224,15 +3175,14 @@
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3" t="s">
+      <c r="X8" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-      <c r="AE8" s="1"/>
-    </row>
-    <row r="9" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD8" s="1"/>
+    </row>
+    <row r="9" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B9" s="3">
         <v>1981</v>
       </c>
@@ -3258,12 +3208,11 @@
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
+      <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
-      <c r="AE9" s="1"/>
-    </row>
-    <row r="10" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD9" s="1"/>
+    </row>
+    <row r="10" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B10" s="3">
         <v>1982</v>
       </c>
@@ -3289,12 +3238,11 @@
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
+      <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
-      <c r="AA10" s="1"/>
-      <c r="AE10" s="1"/>
-    </row>
-    <row r="11" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD10" s="1"/>
+    </row>
+    <row r="11" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B11" s="3">
         <v>1983</v>
       </c>
@@ -3320,12 +3268,11 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
+      <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
-      <c r="AA11" s="1"/>
-      <c r="AE11" s="1"/>
-    </row>
-    <row r="12" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD11" s="1"/>
+    </row>
+    <row r="12" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B12" s="3">
         <v>1984</v>
       </c>
@@ -3351,12 +3298,11 @@
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
+      <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
-      <c r="AA12" s="1"/>
-      <c r="AE12" s="1"/>
-    </row>
-    <row r="13" spans="1:31" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AD12" s="1"/>
+    </row>
+    <row r="13" spans="1:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B13" s="3">
         <v>1985</v>
       </c>
@@ -3380,16 +3326,15 @@
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3" t="s">
+      <c r="W13" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="Y13" s="3"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
-      <c r="AA13" s="1"/>
-      <c r="AE13" s="1"/>
-    </row>
-    <row r="14" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD13" s="1"/>
+    </row>
+    <row r="14" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B14" s="3">
         <v>1986</v>
       </c>
@@ -3415,18 +3360,17 @@
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
+      <c r="W14" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="X14" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y14" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
-      <c r="AA14" s="1"/>
-      <c r="AE14" s="1"/>
-    </row>
-    <row r="15" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD14" s="1"/>
+    </row>
+    <row r="15" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B15" s="3">
         <v>1987</v>
       </c>
@@ -3451,15 +3395,14 @@
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3" t="s">
+      <c r="X15" s="3" t="s">
         <v>104</v>
       </c>
+      <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
-      <c r="AA15" s="1"/>
-      <c r="AE15" s="1"/>
-    </row>
-    <row r="16" spans="1:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD15" s="1"/>
+    </row>
+    <row r="16" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B16" s="3">
         <v>1988</v>
       </c>
@@ -3489,12 +3432,11 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
+      <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
-      <c r="AA16" s="1"/>
-      <c r="AE16" s="1"/>
-    </row>
-    <row r="17" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AD16" s="1"/>
+    </row>
+    <row r="17" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B17" s="3">
         <v>1989</v>
       </c>
@@ -3518,18 +3460,17 @@
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
+      <c r="W17" s="3" t="s">
+        <v>127</v>
+      </c>
       <c r="X17" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y17" s="3" t="s">
         <v>126</v>
       </c>
+      <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
-      <c r="AA17" s="1"/>
-      <c r="AE17" s="1"/>
-    </row>
-    <row r="18" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD17" s="1"/>
+    </row>
+    <row r="18" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B18" s="3">
         <v>1990</v>
       </c>
@@ -3555,12 +3496,11 @@
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
+      <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
-      <c r="AA18" s="1"/>
-      <c r="AE18" s="1"/>
-    </row>
-    <row r="19" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD18" s="1"/>
+    </row>
+    <row r="19" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B19" s="3">
         <v>1991</v>
       </c>
@@ -3586,12 +3526,11 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
+      <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
-      <c r="AA19" s="1"/>
-      <c r="AE19" s="1"/>
-    </row>
-    <row r="20" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD19" s="1"/>
+    </row>
+    <row r="20" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B20" s="3">
         <v>1992</v>
       </c>
@@ -3617,12 +3556,11 @@
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
+      <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
-      <c r="AA20" s="1"/>
-      <c r="AE20" s="1"/>
-    </row>
-    <row r="21" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD20" s="1"/>
+    </row>
+    <row r="21" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B21" s="3">
         <v>1993</v>
       </c>
@@ -3648,12 +3586,11 @@
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
+      <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
-      <c r="AA21" s="1"/>
-      <c r="AE21" s="1"/>
-    </row>
-    <row r="22" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD21" s="1"/>
+    </row>
+    <row r="22" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B22" s="3">
         <v>1994</v>
       </c>
@@ -3679,12 +3616,11 @@
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
+      <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
-      <c r="AA22" s="1"/>
-      <c r="AE22" s="1"/>
-    </row>
-    <row r="23" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AD22" s="1"/>
+    </row>
+    <row r="23" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B23" s="3">
         <v>1995</v>
       </c>
@@ -3710,18 +3646,17 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
-      <c r="W23" s="3"/>
+      <c r="W23" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="X23" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y23" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
-      <c r="AA23" s="1"/>
-      <c r="AE23" s="1"/>
-    </row>
-    <row r="24" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD23" s="1"/>
+    </row>
+    <row r="24" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B24" s="3">
         <v>1996</v>
       </c>
@@ -3746,15 +3681,14 @@
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3" t="s">
-        <v>174</v>
-      </c>
+      <c r="X24" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
-      <c r="AA24" s="1"/>
-      <c r="AE24" s="1"/>
-    </row>
-    <row r="25" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD24" s="1"/>
+    </row>
+    <row r="25" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B25" s="3">
         <v>1997</v>
       </c>
@@ -3781,15 +3715,14 @@
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3" t="s">
+      <c r="X25" s="3" t="s">
         <v>80</v>
       </c>
+      <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
-      <c r="AA25" s="1"/>
-      <c r="AE25" s="1"/>
-    </row>
-    <row r="26" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD25" s="1"/>
+    </row>
+    <row r="26" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B26" s="3">
         <v>1998</v>
       </c>
@@ -3813,18 +3746,17 @@
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
+      <c r="W26" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="X26" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y26" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
-      <c r="AA26" s="1"/>
-      <c r="AE26" s="1"/>
-    </row>
-    <row r="27" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AD26" s="1"/>
+    </row>
+    <row r="27" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B27" s="3">
         <v>1999</v>
       </c>
@@ -3850,16 +3782,15 @@
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3" t="s">
+      <c r="W27" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="Y27" s="3"/>
+      <c r="X27" s="3"/>
+      <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
-      <c r="AA27" s="1"/>
-      <c r="AE27" s="1"/>
-    </row>
-    <row r="28" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AD27" s="1"/>
+    </row>
+    <row r="28" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B28" s="3">
         <v>2000</v>
       </c>
@@ -3888,15 +3819,14 @@
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3" t="s">
+      <c r="X28" s="3" t="s">
         <v>82</v>
       </c>
+      <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
-      <c r="AA28" s="1"/>
-      <c r="AE28" s="1"/>
-    </row>
-    <row r="29" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD28" s="1"/>
+    </row>
+    <row r="29" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B29" s="3">
         <v>2001</v>
       </c>
@@ -3926,12 +3856,11 @@
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
+      <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
-      <c r="AA29" s="1"/>
-      <c r="AE29" s="1"/>
-    </row>
-    <row r="30" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AD29" s="1"/>
+    </row>
+    <row r="30" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B30" s="3">
         <v>2002</v>
       </c>
@@ -3955,16 +3884,15 @@
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
-      <c r="W30" s="3"/>
-      <c r="X30" s="3" t="s">
+      <c r="W30" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="Y30" s="3"/>
+      <c r="X30" s="3"/>
+      <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
-      <c r="AA30" s="1"/>
-      <c r="AE30" s="1"/>
-    </row>
-    <row r="31" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD30" s="1"/>
+    </row>
+    <row r="31" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B31" s="3">
         <v>2003</v>
       </c>
@@ -3990,12 +3918,11 @@
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
-      <c r="Y31" s="3"/>
+      <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
-      <c r="AA31" s="1"/>
-      <c r="AE31" s="1"/>
-    </row>
-    <row r="32" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AD31" s="1"/>
+    </row>
+    <row r="32" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B32" s="3">
         <v>2004</v>
       </c>
@@ -4019,18 +3946,17 @@
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
-      <c r="W32" s="3"/>
+      <c r="W32" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="X32" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y32" s="3" t="s">
         <v>79</v>
       </c>
+      <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
-      <c r="AA32" s="1"/>
-      <c r="AE32" s="1"/>
-    </row>
-    <row r="33" spans="2:31" ht="50" x14ac:dyDescent="0.8">
+      <c r="AD32" s="1"/>
+    </row>
+    <row r="33" spans="2:30" ht="50" x14ac:dyDescent="0.8">
       <c r="B33" s="3">
         <v>2005</v>
       </c>
@@ -4056,16 +3982,15 @@
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
-      <c r="W33" s="3"/>
-      <c r="X33" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y33" s="3"/>
+      <c r="W33" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="X33" s="3"/>
+      <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
-      <c r="AA33" s="1"/>
-      <c r="AE33" s="1"/>
-    </row>
-    <row r="34" spans="2:31" ht="66.7" x14ac:dyDescent="0.8">
+      <c r="AD33" s="1"/>
+    </row>
+    <row r="34" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
       <c r="B34" s="3">
         <v>2006</v>
       </c>
@@ -4074,13 +3999,13 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
@@ -4096,19 +4021,18 @@
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
-      <c r="W34" s="3" t="s">
+      <c r="V34" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3" t="s">
+      <c r="W34" s="3"/>
+      <c r="X34" s="3" t="s">
         <v>105</v>
       </c>
+      <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
-      <c r="AA34" s="1"/>
-      <c r="AE34" s="1"/>
-    </row>
-    <row r="35" spans="2:31" ht="50" x14ac:dyDescent="0.8">
+      <c r="AD34" s="1"/>
+    </row>
+    <row r="35" spans="2:30" ht="50" x14ac:dyDescent="0.8">
       <c r="B35" s="3">
         <v>2007</v>
       </c>
@@ -4131,30 +4055,29 @@
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
-      <c r="W35" s="3" t="s">
+      <c r="V35" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3" t="s">
-        <v>139</v>
-      </c>
+      <c r="W35" s="3"/>
+      <c r="X35" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
-      <c r="AA35" s="1"/>
-      <c r="AE35" s="1"/>
-    </row>
-    <row r="36" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AD35" s="1"/>
+    </row>
+    <row r="36" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B36" s="3">
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4170,19 +4093,18 @@
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
-      <c r="W36" s="3" t="s">
+      <c r="V36" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3" t="s">
-        <v>206</v>
-      </c>
+      <c r="W36" s="3"/>
+      <c r="X36" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
-      <c r="AA36" s="1"/>
-      <c r="AE36" s="1"/>
-    </row>
-    <row r="37" spans="2:31" ht="16.7" x14ac:dyDescent="0.8">
+      <c r="AD36" s="1"/>
+    </row>
+    <row r="37" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
       <c r="B37" s="3">
         <v>2009</v>
       </c>
@@ -4206,16 +4128,15 @@
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
-      <c r="W37" s="3"/>
-      <c r="X37" s="3" t="s">
+      <c r="W37" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Y37" s="3"/>
+      <c r="X37" s="3"/>
+      <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
-      <c r="AA37" s="1"/>
-      <c r="AE37" s="1"/>
-    </row>
-    <row r="38" spans="2:31" ht="50" x14ac:dyDescent="0.8">
+      <c r="AD37" s="1"/>
+    </row>
+    <row r="38" spans="2:30" ht="50" x14ac:dyDescent="0.8">
       <c r="B38" s="3">
         <v>2010</v>
       </c>
@@ -4243,21 +4164,20 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
-      <c r="W38" s="3"/>
-      <c r="X38" s="3" t="s">
+      <c r="W38" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="Y38" s="3"/>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
-      <c r="AA38" s="1"/>
-      <c r="AE38" s="1"/>
-    </row>
-    <row r="39" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AD38" s="1"/>
+    </row>
+    <row r="39" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B39" s="3">
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4287,23 +4207,22 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3" t="s">
-        <v>141</v>
-      </c>
+      <c r="X39" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
-      <c r="AA39" s="1"/>
-      <c r="AE39" s="1"/>
-    </row>
-    <row r="40" spans="2:31" ht="33.35" x14ac:dyDescent="0.8">
+      <c r="AD39" s="1"/>
+    </row>
+    <row r="40" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
       <c r="B40" s="3">
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>41</v>
@@ -4330,38 +4249,37 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
+      <c r="V40" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="W40" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="X40" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="Y40" s="3"/>
+        <v>193</v>
+      </c>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
-      <c r="AA40" s="1"/>
-      <c r="AE40" s="1"/>
-    </row>
-    <row r="41" spans="2:31" ht="100" x14ac:dyDescent="0.8">
+      <c r="AD40" s="1"/>
+    </row>
+    <row r="41" spans="2:30" ht="100" x14ac:dyDescent="0.8">
       <c r="B41" s="3">
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4375,26 +4293,25 @@
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
+      <c r="V41" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="W41" s="3" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y41" s="3" t="s">
-        <v>223</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
-      <c r="AA41" s="1"/>
-      <c r="AE41" s="1"/>
-    </row>
-    <row r="42" spans="2:31" ht="50" x14ac:dyDescent="0.8">
+      <c r="AD41" s="1"/>
+    </row>
+    <row r="42" spans="2:30" ht="50" x14ac:dyDescent="0.8">
       <c r="B42" s="3">
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4417,23 +4334,22 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
-      <c r="W42" s="3"/>
+      <c r="W42" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="X42" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y42" s="3" t="s">
-        <v>200</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
-      <c r="AA42" s="1"/>
-      <c r="AE42" s="1"/>
-    </row>
-    <row r="43" spans="2:31" ht="66.7" x14ac:dyDescent="0.8">
+      <c r="AD42" s="1"/>
+    </row>
+    <row r="43" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
       <c r="B43" s="3">
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4457,24 +4373,23 @@
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
-      <c r="V43" s="3"/>
-      <c r="W43" s="3" t="s">
+      <c r="V43" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="X43" s="3"/>
-      <c r="Y43" s="3" t="s">
-        <v>149</v>
-      </c>
+      <c r="W43" s="3"/>
+      <c r="X43" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
-      <c r="AA43" s="1"/>
-      <c r="AE43" s="1"/>
-    </row>
-    <row r="44" spans="2:31" ht="50" x14ac:dyDescent="0.8">
+      <c r="AD43" s="1"/>
+    </row>
+    <row r="44" spans="2:30" ht="50" x14ac:dyDescent="0.8">
       <c r="B44" s="3">
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
@@ -4499,23 +4414,22 @@
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
-      <c r="W44" s="3"/>
+      <c r="W44" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="X44" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y44" s="3" t="s">
-        <v>196</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
-      <c r="AA44" s="1"/>
-      <c r="AE44" s="1"/>
-    </row>
-    <row r="45" spans="2:31" ht="66.7" x14ac:dyDescent="0.8">
+      <c r="AD44" s="1"/>
+    </row>
+    <row r="45" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
       <c r="B45" s="3">
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4538,7 +4452,7 @@
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
@@ -4547,32 +4461,31 @@
         <v>121</v>
       </c>
       <c r="U45" s="3"/>
-      <c r="V45" s="3"/>
+      <c r="V45" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="W45" s="3" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="Y45" s="3" t="s">
         <v>116</v>
       </c>
+      <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
-      <c r="AA45" s="1"/>
-      <c r="AE45" s="1"/>
-    </row>
-    <row r="46" spans="2:31" ht="200" x14ac:dyDescent="0.8">
+      <c r="AD45" s="1"/>
+    </row>
+    <row r="46" spans="2:30" ht="200" x14ac:dyDescent="0.8">
       <c r="B46" s="3">
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>14</v>
@@ -4588,7 +4501,7 @@
         <v>69</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -4602,26 +4515,25 @@
         <v>122</v>
       </c>
       <c r="U46" s="3"/>
-      <c r="V46" s="3"/>
+      <c r="V46" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="W46" s="3" t="s">
-        <v>96</v>
+        <v>206</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="Y46" s="3" t="s">
-        <v>137</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
-      <c r="AA46" s="1"/>
-      <c r="AE46" s="1"/>
-    </row>
-    <row r="47" spans="2:31" ht="100" x14ac:dyDescent="0.8">
+      <c r="AD46" s="1"/>
+    </row>
+    <row r="47" spans="2:30" ht="100" x14ac:dyDescent="0.8">
       <c r="B47" s="3">
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4636,7 +4548,7 @@
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4656,18 +4568,17 @@
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
-      <c r="W47" s="3"/>
+      <c r="W47" s="3" t="s">
+        <v>153</v>
+      </c>
       <c r="X47" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y47" s="3" t="s">
-        <v>211</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
-      <c r="AA47" s="1"/>
-      <c r="AE47" s="1"/>
-    </row>
-    <row r="48" spans="2:31" ht="66.7" x14ac:dyDescent="0.8">
+      <c r="AD47" s="1"/>
+    </row>
+    <row r="48" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
       <c r="B48" s="3">
         <v>2020</v>
       </c>
@@ -4699,18 +4610,17 @@
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
-      <c r="W48" s="3"/>
+      <c r="W48" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="X48" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Y48" s="3" t="s">
-        <v>207</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
-      <c r="AA48" s="1"/>
-      <c r="AE48" s="1"/>
-    </row>
-    <row r="49" spans="2:31" ht="116.7" x14ac:dyDescent="0.8">
+      <c r="AD48" s="1"/>
+    </row>
+    <row r="49" spans="2:30" ht="116.7" x14ac:dyDescent="0.8">
       <c r="B49" s="3">
         <v>2021</v>
       </c>
@@ -4718,16 +4628,16 @@
         <v>49</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4750,37 +4660,36 @@
       </c>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
-      <c r="U49" s="3"/>
-      <c r="V49" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="W49" s="3"/>
-      <c r="X49" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y49" s="3"/>
+      <c r="U49" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="V49" s="3"/>
+      <c r="W49" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="X49" s="3"/>
+      <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
-      <c r="AA49" s="1"/>
-      <c r="AE49" s="1"/>
-    </row>
-    <row r="50" spans="2:31" ht="133.35" x14ac:dyDescent="0.8">
+      <c r="AD49" s="1"/>
+    </row>
+    <row r="50" spans="2:30" ht="133.35" x14ac:dyDescent="0.8">
       <c r="B50" s="3">
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>22</v>
@@ -4790,7 +4699,7 @@
         <v>73</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>71</v>
@@ -4798,29 +4707,28 @@
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
-      <c r="U50" s="3"/>
-      <c r="V50" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="W50" s="3"/>
+      <c r="U50" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="V50" s="3"/>
+      <c r="W50" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="X50" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="Y50" s="3" t="s">
-        <v>179</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
-      <c r="AA50" s="1"/>
-      <c r="AE50" s="1"/>
-    </row>
-    <row r="51" spans="2:31" ht="100" x14ac:dyDescent="0.8">
+      <c r="AD50" s="1"/>
+    </row>
+    <row r="51" spans="2:30" ht="100" x14ac:dyDescent="0.8">
       <c r="B51" s="3">
         <v>2023</v>
       </c>
@@ -4828,16 +4736,16 @@
         <v>25</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>107</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>112</v>
@@ -4852,7 +4760,7 @@
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="O51" s="3" t="s">
         <v>113</v>
@@ -4862,28 +4770,25 @@
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="V51" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="W51" s="3"/>
+        <v>150</v>
+      </c>
+      <c r="V51" s="3"/>
+      <c r="W51" s="3" t="s">
+        <v>207</v>
+      </c>
       <c r="X51" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="Y51" s="3" t="s">
-        <v>142</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
-      <c r="AA51" s="1"/>
-      <c r="AE51" s="1"/>
-    </row>
-    <row r="52" spans="2:31" ht="100" x14ac:dyDescent="0.8">
+      <c r="AD51" s="1"/>
+    </row>
+    <row r="52" spans="2:30" ht="100" x14ac:dyDescent="0.8">
       <c r="B52" s="3">
         <v>2024</v>
       </c>
@@ -4897,13 +4802,13 @@
         <v>44</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G52" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H52" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>109</v>
@@ -4912,17 +4817,17 @@
         <v>75</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>110</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
@@ -4933,31 +4838,28 @@
       <c r="T52" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>130</v>
-      </c>
+      <c r="U52" s="3"/>
       <c r="V52" s="3"/>
-      <c r="W52" s="3"/>
-      <c r="X52" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y52" s="3"/>
+      <c r="W52" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="X52" s="3"/>
+      <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
-      <c r="AA52" s="1"/>
-      <c r="AE52" s="1"/>
-    </row>
-    <row r="53" spans="2:31" ht="250" x14ac:dyDescent="0.8">
+      <c r="AD52" s="1"/>
+    </row>
+    <row r="53" spans="2:30" ht="266.7" x14ac:dyDescent="0.8">
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>106</v>
@@ -4966,26 +4868,26 @@
         <v>98</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
@@ -4993,92 +4895,88 @@
         <v>123</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="V53" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="W53" s="3"/>
-      <c r="X53" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="Y53" s="3"/>
+        <v>179</v>
+      </c>
+      <c r="V53" s="3"/>
+      <c r="W53" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="X53" s="3"/>
+      <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
-      <c r="AA53" s="1"/>
-      <c r="AE53" s="1"/>
-    </row>
-    <row r="54" spans="2:31" ht="50" x14ac:dyDescent="0.8">
+      <c r="AD53" s="1"/>
+    </row>
+    <row r="54" spans="2:30" ht="50" x14ac:dyDescent="0.8">
       <c r="B54" s="3">
         <v>2026</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
-      <c r="W54" s="3"/>
-      <c r="X54" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="Y54" s="3"/>
+      <c r="W54" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="X54" s="3"/>
+      <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
-      <c r="AA54" s="1"/>
-      <c r="AE54" s="1"/>
-    </row>
-    <row r="55" spans="2:31" ht="200" x14ac:dyDescent="0.8">
+      <c r="AD54" s="1"/>
+    </row>
+    <row r="55" spans="2:30" ht="200" x14ac:dyDescent="0.8">
       <c r="B55" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -5086,16 +4984,15 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-      <c r="W55" s="3"/>
-      <c r="X55" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="Y55" s="3"/>
+      <c r="W55" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="X55" s="3"/>
+      <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
-      <c r="AA55" s="1"/>
-      <c r="AE55" s="1"/>
-    </row>
-    <row r="56" spans="2:31" x14ac:dyDescent="0.8">
+      <c r="AD55" s="1"/>
+    </row>
+    <row r="56" spans="2:30" x14ac:dyDescent="0.8">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -5121,11 +5018,10 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-      <c r="Y56" s="3"/>
+      <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
-      <c r="AA56" s="1"/>
-      <c r="AC56"/>
-      <c r="AE56" s="1"/>
+      <c r="AB56"/>
+      <c r="AD56" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2836D590-C605-4F1E-96DB-E2C1F80106A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7690C10-DD07-4A9B-BD41-E3381F4ECE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-67" yWindow="-67" windowWidth="25734" windowHeight="13814" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="-68" yWindow="-68" windowWidth="28936" windowHeight="15616" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="228">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -564,11 +564,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>チェリー
-水波綾</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>藪下めぐみ</t>
     <rPh sb="0" eb="2">
       <t>ヤブシタ</t>
@@ -735,33 +730,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>風城ハル
-芦田美歩
-大久保琉那(休)
-鈴木志乃
-凍雅
-上原わかな</t>
-    <rPh sb="5" eb="9">
-      <t>アシダミフ</t>
-    </rPh>
-    <rPh sb="10" eb="15">
-      <t>オオクボルナ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ヤス</t>
-    </rPh>
-    <rPh sb="19" eb="23">
-      <t>スズキシノ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>トウガ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ウエハラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ジュリア(WWE)</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -886,13 +854,6 @@
     </rPh>
     <rPh sb="5" eb="6">
       <t>ナギサ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>あきば栞(SECRETBASE)</t>
-    <rPh sb="3" eb="4">
-      <t>シオリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1027,18 +988,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>VENY
-尾崎妹加
-ジャングル叫女(休)</t>
-    <rPh sb="5" eb="9">
-      <t>オザキマイカ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>キュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>荒幡寧々
 福永莉子
 水嶋さくら
@@ -1358,16 +1307,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>鹿島沙希(2026.4.26引退予定)</t>
-    <rPh sb="14" eb="16">
-      <t>インタイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>小橋マリカ
 凛(5.1引退予定)</t>
     <phoneticPr fontId="1"/>
@@ -1414,25 +1353,6 @@
   </si>
   <si>
     <t>羽南</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ビクトリア弓月
-田中きずな(休)
-勇気みなみ
-瀬戸レア</t>
-    <rPh sb="8" eb="10">
-      <t>タナカ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ユウキ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>セト</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1534,21 +1454,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>志真うた(伊藤道場)
-CoCo(MyWay)
-大竹仁美(BBJ)</t>
-    <rPh sb="0" eb="2">
-      <t>シマ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>イトウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ドウジョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>梨央
 弥福かな
 ゴんべ
@@ -1562,20 +1467,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;小谷さつき&gt;
-&lt;松﨑紗弥&gt;
-&lt;山根百合&gt;(4.5デビュー予定)
-&lt;桃羽もえは&gt;
-&lt;確変むぎ&gt;(4.5デビュー予定)</t>
-    <rPh sb="42" eb="44">
-      <t>カクヘン</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>未愛</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1609,31 +1500,6 @@
     </rPh>
     <rPh sb="24" eb="26">
       <t>サキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;七世真理子&gt;(Rose)
-&lt;星野 さやか&gt;(九州女子プロレス)
-&lt;今野結菜&gt;(伊藤道場)(仮合格)
-&lt;鰻マスクウーマン&gt;(DDT?)(4.19デビュー予定)</t>
-    <rPh sb="23" eb="27">
-      <t>キュウシュウジョシ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>イトウ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ドウジョウ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>カリ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>ゴウカク</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1668,12 +1534,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>コグマ(休)
-葉月
-AZM</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>遠藤有栖
 ハットリ桜
 荒井優希</t>
@@ -1747,17 +1607,15 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>郷田明日香(休)
-ブランキー真帆
-Chi Chi
-ZONES</t>
+    <t>浦幌ちほ(北都)
+ソイ(EVO)</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>苺畑ひより(666)
 横井真菜(REINA)
 タギリヒメ真夢(九州女子プロレス)
-彩月悠叶(2AW)
+彩月悠叶(Evolution, 2AW)
 さいとう(アップタウン)
 しおの(アップタウン)
 小久保アリサ(BBJ)
@@ -1771,8 +1629,142 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>浦幌ちほ(北都)
-ソイ(EVO)</t>
+    <t>ビクトリア弓月
+田中きずな(休)
+瀬戸レア</t>
+    <rPh sb="8" eb="10">
+      <t>タナカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>郷田明日香(休)
+ブランキー真帆
+Chi Chi
+ZONES
+勇気みなみ(休)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あきば栞(SECRETBASE)
+MICHIKO(休)</t>
+    <rPh sb="3" eb="4">
+      <t>シオリ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コグマ
+葉月
+AZM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鹿島沙希</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山根百合
+確変むぎ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;松﨑紗弥&gt;(4.30デビュー予定)&lt;小谷さつき&gt;
+&lt;桃羽もえは&gt;
+</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チェリー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水波綾</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;七世真理子&gt;(Rose)
+&lt;星野 さやか&gt;(九州女子プロレス)
+&lt;今野結菜&gt;(伊藤道場)(仮合格)</t>
+    <rPh sb="23" eb="27">
+      <t>キュウシュウジョシ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>イトウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ドウジョウ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ゴウカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>志真うた(伊藤道場)
+CoCo(MyWay)
+大竹仁美(BBJ)
+鰻マスクウーマン(DDT?/別名あり)</t>
+    <rPh sb="0" eb="2">
+      <t>シマ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イトウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ドウジョウ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ベツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風城ハル
+芦田美歩(別名あり)
+大久保琉那(休)
+鈴木志乃
+凍雅
+上原わかな</t>
+    <rPh sb="5" eb="9">
+      <t>アシダミフ</t>
+    </rPh>
+    <rPh sb="16" eb="21">
+      <t>オオクボルナ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヤス</t>
+    </rPh>
+    <rPh sb="25" eb="29">
+      <t>スズキシノ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>トウガ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ウエハラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VENY
+尾崎妹加
+ジャングル叫女</t>
+    <rPh sb="5" eb="9">
+      <t>オザキマイカ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2728,41 +2720,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4F8F56-06F6-4E1D-8D81-5A485042419D}">
   <dimension ref="A1:AD56"/>
-  <sheetFormatPr defaultColWidth="27.33203125" defaultRowHeight="18" x14ac:dyDescent="0.8"/>
+  <sheetFormatPr defaultColWidth="27.3125" defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="1.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.38671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="20.27734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.94140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.71875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.0546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.38671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.609375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.9375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.0625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.625" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.609375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.27734375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.94140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="17.4375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.9375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.27734375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="41.0546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="30.27734375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="30.0546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="41.0625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.1875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.1875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="30.0625" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="27.33203125" style="1"/>
-    <col min="31" max="16384" width="27.33203125" style="1"/>
+    <col min="29" max="29" width="27.3125" style="1"/>
+    <col min="31" max="16384" width="27.3125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="16" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2780,10 +2772,10 @@
       <c r="Z1" s="1"/>
       <c r="AD1" s="1"/>
     </row>
-    <row r="2" spans="1:30" ht="16" x14ac:dyDescent="0.8">
+    <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RX2)</f>
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2815,7 +2807,7 @@
      LEN(F5:F1001) - LEN(SUBSTITUTE(F5:F1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="1" cm="1">
         <f t="array" ref="G2">SUMPRODUCT(
@@ -2879,7 +2871,7 @@
      LEN(N5:N1001) - LEN(SUBSTITUTE(N5:N1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" s="1" cm="1">
         <f t="array" ref="O2">SUMPRODUCT(
@@ -2951,7 +2943,7 @@
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="X2" s="1" cm="1">
         <f t="array" ref="X2">SUMPRODUCT(
@@ -2965,7 +2957,7 @@
       <c r="Z2" s="1"/>
       <c r="AD2" s="1"/>
     </row>
-    <row r="3" spans="1:30" ht="16" x14ac:dyDescent="0.8">
+    <row r="3" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
@@ -2982,7 +2974,7 @@
       <c r="Z3" s="1"/>
       <c r="AD3" s="1"/>
     </row>
-    <row r="4" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="4" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
@@ -3011,19 +3003,19 @@
         <v>47</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>56</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>50</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>19</v>
@@ -3038,13 +3030,13 @@
         <v>7</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>35</v>
@@ -3056,7 +3048,7 @@
       <c r="Z4" s="1"/>
       <c r="AD4" s="1"/>
     </row>
-    <row r="5" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="5" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B5" s="3">
         <v>1977</v>
       </c>
@@ -3088,7 +3080,7 @@
       <c r="Z5" s="1"/>
       <c r="AD5" s="1"/>
     </row>
-    <row r="6" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="6" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B6" s="3">
         <v>1978</v>
       </c>
@@ -3118,7 +3110,7 @@
       <c r="Z6" s="1"/>
       <c r="AD6" s="1"/>
     </row>
-    <row r="7" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="7" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B7" s="3">
         <v>1979</v>
       </c>
@@ -3148,7 +3140,7 @@
       <c r="Z7" s="1"/>
       <c r="AD7" s="1"/>
     </row>
-    <row r="8" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="8" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B8" s="3">
         <v>1980</v>
       </c>
@@ -3182,7 +3174,7 @@
       <c r="Z8" s="1"/>
       <c r="AD8" s="1"/>
     </row>
-    <row r="9" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="9" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B9" s="3">
         <v>1981</v>
       </c>
@@ -3212,7 +3204,7 @@
       <c r="Z9" s="1"/>
       <c r="AD9" s="1"/>
     </row>
-    <row r="10" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="10" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B10" s="3">
         <v>1982</v>
       </c>
@@ -3242,7 +3234,7 @@
       <c r="Z10" s="1"/>
       <c r="AD10" s="1"/>
     </row>
-    <row r="11" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="11" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B11" s="3">
         <v>1983</v>
       </c>
@@ -3272,7 +3264,7 @@
       <c r="Z11" s="1"/>
       <c r="AD11" s="1"/>
     </row>
-    <row r="12" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="12" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B12" s="3">
         <v>1984</v>
       </c>
@@ -3302,7 +3294,7 @@
       <c r="Z12" s="1"/>
       <c r="AD12" s="1"/>
     </row>
-    <row r="13" spans="1:30" ht="33.35" x14ac:dyDescent="0.8">
+    <row r="13" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B13" s="3">
         <v>1985</v>
       </c>
@@ -3327,14 +3319,14 @@
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="X13" s="3"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
       <c r="AD13" s="1"/>
     </row>
-    <row r="14" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="14" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B14" s="3">
         <v>1986</v>
       </c>
@@ -3370,7 +3362,7 @@
       <c r="Z14" s="1"/>
       <c r="AD14" s="1"/>
     </row>
-    <row r="15" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="15" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B15" s="3">
         <v>1987</v>
       </c>
@@ -3396,13 +3388,13 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AD15" s="1"/>
     </row>
-    <row r="16" spans="1:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="16" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B16" s="3">
         <v>1988</v>
       </c>
@@ -3436,7 +3428,7 @@
       <c r="Z16" s="1"/>
       <c r="AD16" s="1"/>
     </row>
-    <row r="17" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+    <row r="17" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B17" s="3">
         <v>1989</v>
       </c>
@@ -3461,16 +3453,16 @@
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
       <c r="AD17" s="1"/>
     </row>
-    <row r="18" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="18" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B18" s="3">
         <v>1990</v>
       </c>
@@ -3500,7 +3492,7 @@
       <c r="Z18" s="1"/>
       <c r="AD18" s="1"/>
     </row>
-    <row r="19" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="19" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B19" s="3">
         <v>1991</v>
       </c>
@@ -3530,7 +3522,7 @@
       <c r="Z19" s="1"/>
       <c r="AD19" s="1"/>
     </row>
-    <row r="20" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="20" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B20" s="3">
         <v>1992</v>
       </c>
@@ -3560,7 +3552,7 @@
       <c r="Z20" s="1"/>
       <c r="AD20" s="1"/>
     </row>
-    <row r="21" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="21" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B21" s="3">
         <v>1993</v>
       </c>
@@ -3590,7 +3582,7 @@
       <c r="Z21" s="1"/>
       <c r="AD21" s="1"/>
     </row>
-    <row r="22" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="22" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B22" s="3">
         <v>1994</v>
       </c>
@@ -3620,7 +3612,7 @@
       <c r="Z22" s="1"/>
       <c r="AD22" s="1"/>
     </row>
-    <row r="23" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+    <row r="23" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B23" s="3">
         <v>1995</v>
       </c>
@@ -3647,7 +3639,7 @@
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>63</v>
@@ -3656,7 +3648,7 @@
       <c r="Z23" s="1"/>
       <c r="AD23" s="1"/>
     </row>
-    <row r="24" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="24" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B24" s="3">
         <v>1996</v>
       </c>
@@ -3682,13 +3674,13 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
       <c r="AD24" s="1"/>
     </row>
-    <row r="25" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="25" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B25" s="3">
         <v>1997</v>
       </c>
@@ -3703,7 +3695,7 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -3716,13 +3708,13 @@
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
       <c r="AD25" s="1"/>
     </row>
-    <row r="26" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="26" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B26" s="3">
         <v>1998</v>
       </c>
@@ -3756,7 +3748,7 @@
       <c r="Z26" s="1"/>
       <c r="AD26" s="1"/>
     </row>
-    <row r="27" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+    <row r="27" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B27" s="3">
         <v>1999</v>
       </c>
@@ -3790,7 +3782,7 @@
       <c r="Z27" s="1"/>
       <c r="AD27" s="1"/>
     </row>
-    <row r="28" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+    <row r="28" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B28" s="3">
         <v>2000</v>
       </c>
@@ -3807,7 +3799,7 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -3820,13 +3812,13 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
       <c r="AD28" s="1"/>
     </row>
-    <row r="29" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="29" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B29" s="3">
         <v>2001</v>
       </c>
@@ -3860,7 +3852,7 @@
       <c r="Z29" s="1"/>
       <c r="AD29" s="1"/>
     </row>
-    <row r="30" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+    <row r="30" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B30" s="3">
         <v>2002</v>
       </c>
@@ -3885,14 +3877,14 @@
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="X30" s="3"/>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
       <c r="AD30" s="1"/>
     </row>
-    <row r="31" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="31" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B31" s="3">
         <v>2003</v>
       </c>
@@ -3922,7 +3914,7 @@
       <c r="Z31" s="1"/>
       <c r="AD31" s="1"/>
     </row>
-    <row r="32" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+    <row r="32" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B32" s="3">
         <v>2004</v>
       </c>
@@ -3937,7 +3929,9 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
+      <c r="N32" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
@@ -3950,13 +3944,13 @@
         <v>59</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
       <c r="AD32" s="1"/>
     </row>
-    <row r="33" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+    <row r="33" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B33" s="3">
         <v>2005</v>
       </c>
@@ -3977,20 +3971,20 @@
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="X33" s="3"/>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
       <c r="AD33" s="1"/>
     </row>
-    <row r="34" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
+    <row r="34" spans="2:30" ht="66" x14ac:dyDescent="0.7">
       <c r="B34" s="3">
         <v>2006</v>
       </c>
@@ -3999,17 +3993,17 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>51</v>
@@ -4026,13 +4020,13 @@
       </c>
       <c r="W34" s="3"/>
       <c r="X34" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
       <c r="AD34" s="1"/>
     </row>
-    <row r="35" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+    <row r="35" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B35" s="3">
         <v>2007</v>
       </c>
@@ -4056,28 +4050,28 @@
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W35" s="3"/>
       <c r="X35" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
       <c r="AD35" s="1"/>
     </row>
-    <row r="36" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+    <row r="36" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B36" s="3">
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4098,13 +4092,13 @@
       </c>
       <c r="W36" s="3"/>
       <c r="X36" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
       <c r="AD36" s="1"/>
     </row>
-    <row r="37" spans="2:30" ht="16.7" x14ac:dyDescent="0.8">
+    <row r="37" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B37" s="3">
         <v>2009</v>
       </c>
@@ -4136,7 +4130,7 @@
       <c r="Z37" s="1"/>
       <c r="AD37" s="1"/>
     </row>
-    <row r="38" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+    <row r="38" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B38" s="3">
         <v>2010</v>
       </c>
@@ -4165,27 +4159,27 @@
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X38" s="3"/>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
       <c r="AD38" s="1"/>
     </row>
-    <row r="39" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+    <row r="39" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B39" s="3">
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -4194,7 +4188,7 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
@@ -4208,27 +4202,27 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
       <c r="AD39" s="1"/>
     </row>
-    <row r="40" spans="2:30" ht="33.35" x14ac:dyDescent="0.8">
+    <row r="40" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B40" s="3">
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4239,7 +4233,7 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
@@ -4250,36 +4244,36 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W40" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="X40" s="3"/>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
       <c r="AD40" s="1"/>
     </row>
-    <row r="41" spans="2:30" ht="100" x14ac:dyDescent="0.8">
+    <row r="41" spans="2:30" ht="99" x14ac:dyDescent="0.7">
       <c r="B41" s="3">
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4294,24 +4288,24 @@
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
       <c r="AD41" s="1"/>
     </row>
-    <row r="42" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+    <row r="42" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B42" s="3">
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4335,21 +4329,21 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>130</v>
+        <v>217</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
       <c r="AD42" s="1"/>
     </row>
-    <row r="43" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
+    <row r="43" spans="2:30" ht="66" x14ac:dyDescent="0.7">
       <c r="B43" s="3">
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4374,22 +4368,22 @@
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
       <c r="V43" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>143</v>
+        <v>227</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
       <c r="AD43" s="1"/>
     </row>
-    <row r="44" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+    <row r="44" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B44" s="3">
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
@@ -4415,21 +4409,21 @@
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
       <c r="AD44" s="1"/>
     </row>
-    <row r="45" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
+    <row r="45" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B45" s="3">
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4437,10 +4431,10 @@
         <v>12</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -4448,44 +4442,44 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
       <c r="AD45" s="1"/>
     </row>
-    <row r="46" spans="2:30" ht="200" x14ac:dyDescent="0.8">
+    <row r="46" spans="2:30" ht="99" x14ac:dyDescent="0.7">
       <c r="B46" s="3">
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>14</v>
@@ -4501,7 +4495,7 @@
         <v>69</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -4512,28 +4506,28 @@
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
       <c r="AD46" s="1"/>
     </row>
-    <row r="47" spans="2:30" ht="100" x14ac:dyDescent="0.8">
+    <row r="47" spans="2:30" ht="99" x14ac:dyDescent="0.7">
       <c r="B47" s="3">
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4541,21 +4535,21 @@
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
         <v>70</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>53</v>
@@ -4569,16 +4563,16 @@
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
       <c r="AD47" s="1"/>
     </row>
-    <row r="48" spans="2:30" ht="66.7" x14ac:dyDescent="0.8">
+    <row r="48" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B48" s="3">
         <v>2020</v>
       </c>
@@ -4597,7 +4591,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
@@ -4605,22 +4599,22 @@
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
       <c r="S48" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
       <c r="AD48" s="1"/>
     </row>
-    <row r="49" spans="2:30" ht="116.7" x14ac:dyDescent="0.8">
+    <row r="49" spans="2:30" ht="66" x14ac:dyDescent="0.7">
       <c r="B49" s="3">
         <v>2021</v>
       </c>
@@ -4628,16 +4622,16 @@
         <v>49</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4661,35 +4655,35 @@
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="X49" s="3"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AD49" s="1"/>
     </row>
-    <row r="50" spans="2:30" ht="133.35" x14ac:dyDescent="0.8">
+    <row r="50" spans="2:30" ht="132" x14ac:dyDescent="0.7">
       <c r="B50" s="3">
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>22</v>
@@ -4699,7 +4693,7 @@
         <v>73</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>71</v>
@@ -4707,7 +4701,7 @@
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4715,20 +4709,20 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
       <c r="AD50" s="1"/>
     </row>
-    <row r="51" spans="2:30" ht="100" x14ac:dyDescent="0.8">
+    <row r="51" spans="2:30" ht="99" x14ac:dyDescent="0.7">
       <c r="B51" s="3">
         <v>2023</v>
       </c>
@@ -4736,19 +4730,19 @@
         <v>25</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>107</v>
+        <v>226</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
@@ -4760,35 +4754,35 @@
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
       <c r="AD51" s="1"/>
     </row>
-    <row r="52" spans="2:30" ht="100" x14ac:dyDescent="0.8">
+    <row r="52" spans="2:30" ht="99" x14ac:dyDescent="0.7">
       <c r="B52" s="3">
         <v>2024</v>
       </c>
@@ -4802,32 +4796,32 @@
         <v>44</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>75</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
@@ -4836,104 +4830,106 @@
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
       <c r="AD52" s="1"/>
     </row>
-    <row r="53" spans="2:30" ht="266.7" x14ac:dyDescent="0.8">
+    <row r="53" spans="2:30" ht="132" x14ac:dyDescent="0.7">
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
       <c r="AD53" s="1"/>
     </row>
-    <row r="54" spans="2:30" ht="50" x14ac:dyDescent="0.8">
+    <row r="54" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B54" s="3">
         <v>2026</v>
       </c>
       <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
+      <c r="D54" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="E54" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4941,42 +4937,42 @@
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
       <c r="AD54" s="1"/>
     </row>
-    <row r="55" spans="2:30" ht="200" x14ac:dyDescent="0.8">
+    <row r="55" spans="2:30" ht="99" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -4985,14 +4981,14 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
       <c r="AD55" s="1"/>
     </row>
-    <row r="56" spans="2:30" x14ac:dyDescent="0.8">
+    <row r="56" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -5001,7 +4997,7 @@
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7690C10-DD07-4A9B-BD41-E3381F4ECE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2386EEE-BEBC-420E-8A23-39DB3E616FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-68" yWindow="-68" windowWidth="28936" windowHeight="15616" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -67,9 +67,6 @@
     <t>彩羽匠</t>
   </si>
   <si>
-    <t>まなせゆうな</t>
-  </si>
-  <si>
     <t>マリゴ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1764,6 +1761,13 @@
 ジャングル叫女</t>
     <rPh sb="5" eb="9">
       <t>オザキマイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まなせゆうな(休)</t>
+    <rPh sb="7" eb="8">
+      <t>キュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2754,7 +2758,7 @@
   <sheetData>
     <row r="1" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2976,73 +2980,73 @@
     </row>
     <row r="4" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="R4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
@@ -3058,7 +3062,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -3151,7 +3155,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3168,7 +3172,7 @@
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
@@ -3319,7 +3323,7 @@
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="X13" s="3"/>
       <c r="Y13" s="1"/>
@@ -3344,7 +3348,7 @@
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
@@ -3353,10 +3357,10 @@
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
@@ -3388,7 +3392,7 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
@@ -3404,7 +3408,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
@@ -3414,7 +3418,7 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
@@ -3453,10 +3457,10 @@
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
@@ -3626,7 +3630,7 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
@@ -3639,10 +3643,10 @@
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3674,7 +3678,7 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
@@ -3695,7 +3699,7 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -3708,7 +3712,7 @@
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
@@ -3739,10 +3743,10 @@
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
@@ -3753,7 +3757,7 @@
         <v>1999</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -3775,7 +3779,7 @@
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="X27" s="3"/>
       <c r="Y27" s="1"/>
@@ -3788,7 +3792,7 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -3799,7 +3803,7 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -3812,7 +3816,7 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
@@ -3828,7 +3832,7 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -3840,7 +3844,7 @@
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
@@ -3877,7 +3881,7 @@
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X30" s="3"/>
       <c r="Y30" s="1"/>
@@ -3930,7 +3934,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3941,10 +3945,10 @@
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -3971,13 +3975,13 @@
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="X33" s="3"/>
       <c r="Y33" s="1"/>
@@ -3993,20 +3997,20 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -4016,11 +4020,11 @@
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W34" s="3"/>
       <c r="X34" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
@@ -4050,11 +4054,11 @@
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W35" s="3"/>
       <c r="X35" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
@@ -4065,13 +4069,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4088,11 +4092,11 @@
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W36" s="3"/>
       <c r="X36" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4123,7 +4127,7 @@
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="X37" s="3"/>
       <c r="Y37" s="1"/>
@@ -4144,14 +4148,14 @@
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
       <c r="Q38" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
@@ -4159,7 +4163,7 @@
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="X38" s="3"/>
       <c r="Y38" s="1"/>
@@ -4171,15 +4175,15 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -4188,21 +4192,21 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
@@ -4213,16 +4217,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4233,7 +4237,7 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
@@ -4244,10 +4248,10 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W40" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X40" s="3"/>
       <c r="Y40" s="1"/>
@@ -4259,21 +4263,21 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4283,18 +4287,18 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>2</v>
+        <v>227</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4305,11 +4309,11 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
@@ -4329,10 +4333,10 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
@@ -4343,11 +4347,11 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -4358,7 +4362,7 @@
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
@@ -4368,11 +4372,11 @@
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
       <c r="V43" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4383,17 +4387,17 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
@@ -4409,10 +4413,10 @@
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4423,18 +4427,18 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -4442,27 +4446,27 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
@@ -4473,50 +4477,50 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4527,32 +4531,32 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O47" s="3"/>
       <c r="P47" s="3"/>
@@ -4563,10 +4567,10 @@
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4577,12 +4581,12 @@
         <v>2020</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4591,7 +4595,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
@@ -4599,16 +4603,16 @@
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
       <c r="S48" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4619,26 +4623,26 @@
         <v>2021</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
@@ -4647,19 +4651,19 @@
       <c r="O49" s="3"/>
       <c r="P49" s="3"/>
       <c r="Q49" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="X49" s="3"/>
       <c r="Y49" s="1"/>
@@ -4671,37 +4675,37 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4709,14 +4713,14 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
@@ -4727,56 +4731,56 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4787,55 +4791,55 @@
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G52" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K52" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="I52" s="3" t="s">
+      <c r="L52" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M52" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="1"/>
@@ -4847,53 +4851,53 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
@@ -4906,30 +4910,30 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4937,7 +4941,7 @@
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="1"/>
@@ -4946,33 +4950,33 @@
     </row>
     <row r="55" spans="2:30" ht="99" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -4981,7 +4985,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>
@@ -4997,7 +5001,7 @@
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2386EEE-BEBC-420E-8A23-39DB3E616FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377A2A18-CA98-4C33-BF93-FAF05C5A9D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-68" yWindow="-68" windowWidth="28936" windowHeight="15616" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="1560" yWindow="4125" windowWidth="21600" windowHeight="11295" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -470,11 +470,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>永島千佳世
-倉垣翼</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>桜花由美</t>
     <rPh sb="0" eb="4">
       <t>オウカユミ</t>
@@ -1767,6 +1762,14 @@
   <si>
     <t>まなせゆうな(休)</t>
     <rPh sb="7" eb="8">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>永島千佳世
+倉垣翼(休)</t>
+    <rPh sb="10" eb="11">
       <t>キュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -2758,7 +2761,7 @@
   <sheetData>
     <row r="1" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2995,7 +2998,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>16</v>
@@ -3007,19 +3010,19 @@
         <v>46</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>55</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>49</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>18</v>
@@ -3034,13 +3037,13 @@
         <v>6</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>34</v>
@@ -3323,7 +3326,7 @@
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="X13" s="3"/>
       <c r="Y13" s="1"/>
@@ -3392,7 +3395,7 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
@@ -3457,10 +3460,10 @@
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
@@ -3643,10 +3646,10 @@
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>62</v>
+        <v>227</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3678,7 +3681,7 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
@@ -3699,7 +3702,7 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -3712,7 +3715,7 @@
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
@@ -3743,7 +3746,7 @@
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>31</v>
@@ -3779,7 +3782,7 @@
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X27" s="3"/>
       <c r="Y27" s="1"/>
@@ -3803,7 +3806,7 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -3816,7 +3819,7 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
@@ -3844,7 +3847,7 @@
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
@@ -3881,7 +3884,7 @@
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="X30" s="3"/>
       <c r="Y30" s="1"/>
@@ -3934,7 +3937,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3948,7 +3951,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -3975,13 +3978,13 @@
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="X33" s="3"/>
       <c r="Y33" s="1"/>
@@ -3997,17 +4000,17 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>50</v>
@@ -4024,7 +4027,7 @@
       </c>
       <c r="W34" s="3"/>
       <c r="X34" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
@@ -4054,11 +4057,11 @@
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="W35" s="3"/>
       <c r="X35" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
@@ -4069,13 +4072,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4096,7 +4099,7 @@
       </c>
       <c r="W36" s="3"/>
       <c r="X36" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4148,7 +4151,7 @@
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
@@ -4163,7 +4166,7 @@
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="X38" s="3"/>
       <c r="Y38" s="1"/>
@@ -4175,15 +4178,15 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -4192,7 +4195,7 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
@@ -4206,7 +4209,7 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
@@ -4217,16 +4220,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4237,7 +4240,7 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
@@ -4248,10 +4251,10 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W40" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="X40" s="3"/>
       <c r="Y40" s="1"/>
@@ -4263,21 +4266,21 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4287,18 +4290,18 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4309,7 +4312,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4333,10 +4336,10 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
@@ -4347,7 +4350,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4372,11 +4375,11 @@
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
       <c r="V43" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4387,7 +4390,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>23</v>
@@ -4413,10 +4416,10 @@
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4427,7 +4430,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4435,10 +4438,10 @@
         <v>11</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -4446,27 +4449,27 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
@@ -4477,13 +4480,13 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>13</v>
@@ -4496,31 +4499,31 @@
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4531,7 +4534,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4539,21 +4542,21 @@
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>52</v>
@@ -4567,10 +4570,10 @@
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4595,7 +4598,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
@@ -4603,16 +4606,16 @@
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
       <c r="S48" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4626,23 +4629,23 @@
         <v>48</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
         <v>27</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
@@ -4654,16 +4657,16 @@
         <v>60</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="X49" s="3"/>
       <c r="Y49" s="1"/>
@@ -4675,37 +4678,37 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4713,14 +4716,14 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
@@ -4734,19 +4737,19 @@
         <v>24</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
@@ -4754,33 +4757,33 @@
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4791,7 +4794,7 @@
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>33</v>
@@ -4800,32 +4803,32 @@
         <v>43</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G52" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K52" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="I52" s="3" t="s">
+      <c r="L52" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M52" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
@@ -4834,12 +4837,12 @@
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="1"/>
@@ -4851,53 +4854,53 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
@@ -4910,30 +4913,30 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4941,7 +4944,7 @@
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="1"/>
@@ -4950,33 +4953,33 @@
     </row>
     <row r="55" spans="2:30" ht="99" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -4985,7 +4988,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>
@@ -5001,7 +5004,7 @@
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377A2A18-CA98-4C33-BF93-FAF05C5A9D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B189E3DC-258B-4B33-B199-97125FBB037C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="4125" windowWidth="21600" windowHeight="11295" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="-68" yWindow="-68" windowWidth="28936" windowHeight="15616" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -1348,20 +1348,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>なる
-夏葵(5.2引退予定)</t>
-    <rPh sb="3" eb="5">
-      <t>ナツキ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>インタイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>星ハム子(IR)(休)</t>
     <rPh sb="0" eb="1">
       <t>ホシ</t>
@@ -1772,6 +1758,10 @@
     <rPh sb="10" eb="11">
       <t>キュウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なる</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2782,7 +2772,7 @@
     <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RX2)</f>
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2798,7 +2788,7 @@
      LEN(D5:D1001) - LEN(SUBSTITUTE(D5:D1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1" cm="1">
         <f t="array" ref="E2">SUMPRODUCT(
@@ -3649,7 +3639,7 @@
         <v>163</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3937,7 +3927,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3951,7 +3941,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -4078,7 +4068,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4099,7 +4089,7 @@
       </c>
       <c r="W36" s="3"/>
       <c r="X36" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4178,7 +4168,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4266,7 +4256,7 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
@@ -4290,7 +4280,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -4301,7 +4291,7 @@
         <v>133</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4336,7 +4326,7 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>187</v>
@@ -4379,7 +4369,7 @@
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4502,7 +4492,7 @@
         <v>67</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -4520,7 +4510,7 @@
         <v>93</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="X46" s="3" t="s">
         <v>128</v>
@@ -4573,7 +4563,7 @@
         <v>147</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4612,10 +4602,10 @@
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4629,16 +4619,16 @@
         <v>48</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4740,10 +4730,10 @@
         <v>175</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>174</v>
@@ -4780,10 +4770,10 @@
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4821,7 +4811,7 @@
         <v>149</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>106</v>
@@ -4842,7 +4832,7 @@
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="1"/>
@@ -4857,7 +4847,7 @@
         <v>182</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>159</v>
@@ -4873,7 +4863,7 @@
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K53" s="3" t="s">
         <v>171</v>
@@ -4900,7 +4890,7 @@
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
@@ -4913,13 +4903,13 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>179</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
@@ -4930,13 +4920,13 @@
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4944,7 +4934,7 @@
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="1"/>
@@ -4957,22 +4947,22 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>157</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -4988,7 +4978,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B189E3DC-258B-4B33-B199-97125FBB037C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE91907-A338-486E-9A73-8B69E3EF0C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-68" yWindow="-68" windowWidth="28936" windowHeight="15616" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1204,10 +1204,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>松橋ななを</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>吏南
 妃南
 鈴季すず
@@ -1428,19 +1424,6 @@
     </rPh>
     <rPh sb="70" eb="72">
       <t>シンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>梨央
-弥福かな
-ゴんべ
-西村摩利乃</t>
-    <rPh sb="0" eb="2">
-      <t>リオ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ニシムラ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1656,12 +1639,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">&lt;松﨑紗弥&gt;(4.30デビュー予定)&lt;小谷さつき&gt;
-&lt;桃羽もえは&gt;
-</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>チェリー</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1762,6 +1739,30 @@
   </si>
   <si>
     <t>なる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;松﨑紗弥&gt;(4.30デビュー予定)&lt;小谷さつき&gt;
+&lt;桃羽もえは&gt;
+&lt;AHI&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>梨央
+弥福かな
+ゴんべ
+西村摩利乃
+松橋ななを</t>
+    <rPh sb="0" eb="2">
+      <t>リオ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニシムラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>松橋ななを?</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2772,7 +2773,7 @@
     <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RX2)</f>
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2788,7 +2789,7 @@
      LEN(D5:D1001) - LEN(SUBSTITUTE(D5:D1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="1" cm="1">
         <f t="array" ref="E2">SUMPRODUCT(
@@ -3000,7 +3001,7 @@
         <v>46</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>55</v>
@@ -3639,7 +3640,7 @@
         <v>163</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3927,7 +3928,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3941,7 +3942,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -4068,7 +4069,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4089,7 +4090,7 @@
       </c>
       <c r="W36" s="3"/>
       <c r="X36" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4168,7 +4169,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4244,7 +4245,7 @@
         <v>91</v>
       </c>
       <c r="W40" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="X40" s="3"/>
       <c r="Y40" s="1"/>
@@ -4256,7 +4257,7 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
@@ -4280,7 +4281,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -4291,7 +4292,7 @@
         <v>133</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4326,10 +4327,10 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
@@ -4340,7 +4341,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4369,7 +4370,7 @@
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4380,7 +4381,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>23</v>
@@ -4409,7 +4410,7 @@
         <v>114</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4420,7 +4421,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4443,7 +4444,7 @@
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
@@ -4470,7 +4471,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>145</v>
@@ -4492,7 +4493,7 @@
         <v>67</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -4510,7 +4511,7 @@
         <v>93</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="X46" s="3" t="s">
         <v>128</v>
@@ -4539,7 +4540,7 @@
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4563,7 +4564,7 @@
         <v>147</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4602,10 +4603,10 @@
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4619,16 +4620,16 @@
         <v>48</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4668,7 +4669,7 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>138</v>
@@ -4727,16 +4728,16 @@
         <v>24</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>108</v>
@@ -4770,10 +4771,10 @@
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4811,7 +4812,7 @@
         <v>149</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>106</v>
@@ -4832,7 +4833,7 @@
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="1"/>
@@ -4844,10 +4845,10 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>159</v>
@@ -4863,10 +4864,10 @@
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>171</v>
+        <v>227</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -4875,7 +4876,7 @@
         <v>169</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>156</v>
@@ -4886,11 +4887,11 @@
         <v>119</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
@@ -4903,30 +4904,30 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4934,7 +4935,7 @@
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="1"/>
@@ -4947,22 +4948,22 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>157</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -4978,7 +4979,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE91907-A338-486E-9A73-8B69E3EF0C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FE199D-49C0-4CC5-AED9-2F25FDD3B7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-68" yWindow="-68" windowWidth="28936" windowHeight="15616" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1445,11 +1445,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;アンリ&gt;(仮)
-&lt;ユウカ&gt;(仮)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ホルスタイン・エンジュ
 ラブリカ・ヒナーノ
 枢夜佐季</t>
@@ -1763,6 +1758,11 @@
   </si>
   <si>
     <t>松橋ななを?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;ユウカ&gt;(仮)
+&lt;里見真帆&gt;</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3640,7 +3640,7 @@
         <v>163</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3928,7 +3928,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3942,7 +3942,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -4169,7 +4169,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4257,7 +4257,7 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
@@ -4281,7 +4281,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -4292,7 +4292,7 @@
         <v>133</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4327,7 +4327,7 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>186</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4493,7 +4493,7 @@
         <v>67</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -4620,16 +4620,16 @@
         <v>48</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4731,10 +4731,10 @@
         <v>174</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>173</v>
@@ -4771,10 +4771,10 @@
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4812,7 +4812,7 @@
         <v>149</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>106</v>
@@ -4833,7 +4833,7 @@
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="1"/>
@@ -4848,7 +4848,7 @@
         <v>181</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>159</v>
@@ -4864,10 +4864,10 @@
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>178</v>
@@ -4948,16 +4948,16 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>157</v>
@@ -4979,7 +4979,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FE199D-49C0-4CC5-AED9-2F25FDD3B7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270F27C8-7DC3-4C3A-9507-F1AFE0568460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-68" yWindow="-68" windowWidth="28936" windowHeight="15616" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1762,7 +1762,7 @@
   </si>
   <si>
     <t>&lt;ユウカ&gt;(仮)
-&lt;里見真帆&gt;</t>
+&lt;さとうもも&gt;</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270F27C8-7DC3-4C3A-9507-F1AFE0568460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CD577A-A37A-474B-8012-65322DB6F968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-68" yWindow="-68" windowWidth="28936" windowHeight="15616" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="229">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1517,45 +1517,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;天羽瑠迦&gt;(あまはねるか, 5.5デビュー予定)
-&lt;早乙女聖&gt;(さおとめひじり, 5.5デビュー予定)
-&lt;州王叶多&gt;(すおうかなた, プロテスト合格)</t>
-    <rPh sb="1" eb="2">
-      <t>アマ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ハネ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>リュウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ヨテイ</t>
-    </rPh>
-    <rPh sb="27" eb="30">
-      <t>サオトメ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ヒジリ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>カナタ</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>ゴウカク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>松下楓歩(IR)</t>
     <rPh sb="0" eb="4">
       <t>マツシタカホ</t>
@@ -1629,11 +1590,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>山根百合
-確変むぎ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>チェリー</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1737,12 +1693,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;松﨑紗弥&gt;(4.30デビュー予定)&lt;小谷さつき&gt;
-&lt;桃羽もえは&gt;
-&lt;AHI&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>梨央
 弥福かな
 ゴんべ
@@ -1763,6 +1713,39 @@
   <si>
     <t>&lt;ユウカ&gt;(仮)
 &lt;さとうもも&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;州王叶多&gt;(すおうかなた, プロテスト合格)</t>
+    <rPh sb="1" eb="2">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カナタ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ゴウカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天羽瑠迦
+早乙女聖</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山根百合
+確変むぎ
+松﨑紗弥</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;小谷さつき&gt;
+&lt;桃羽もえは&gt;
+&lt;AHI&gt;</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2773,7 +2756,7 @@
     <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RX2)</f>
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2789,7 +2772,7 @@
      LEN(D5:D1001) - LEN(SUBSTITUTE(D5:D1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="1" cm="1">
         <f t="array" ref="E2">SUMPRODUCT(
@@ -3640,7 +3623,7 @@
         <v>163</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3928,7 +3911,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3942,7 +3925,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -4169,7 +4152,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4257,7 +4240,7 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
@@ -4281,7 +4264,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -4327,7 +4310,7 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>186</v>
@@ -4370,7 +4353,7 @@
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4620,7 +4603,7 @@
         <v>48</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>202</v>
@@ -4629,7 +4612,7 @@
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4731,10 +4714,10 @@
         <v>174</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>173</v>
@@ -4771,10 +4754,10 @@
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4833,7 +4816,7 @@
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="1"/>
@@ -4848,7 +4831,7 @@
         <v>181</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>159</v>
@@ -4867,7 +4850,7 @@
         <v>200</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -4891,7 +4874,7 @@
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
@@ -4904,7 +4887,7 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>178</v>
@@ -4914,7 +4897,9 @@
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
+      <c r="I54" s="3" t="s">
+        <v>226</v>
+      </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
         <v>177</v>
@@ -4942,22 +4927,22 @@
       <c r="Z54" s="1"/>
       <c r="AD54" s="1"/>
     </row>
-    <row r="55" spans="2:30" ht="99" x14ac:dyDescent="0.7">
+    <row r="55" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
         <v>160</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>227</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>157</v>
@@ -4979,7 +4964,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CD577A-A37A-474B-8012-65322DB6F968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B07DF9-1DA6-4C18-8E14-0A43FA0EAF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-68" yWindow="-68" windowWidth="28936" windowHeight="15616" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1295,11 +1295,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>小橋マリカ
-凛(5.1引退予定)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>伊藤麻希
 刀羅ナツコ
 琉悪夏</t>
@@ -1746,6 +1741,10 @@
     <t>&lt;小谷さつき&gt;
 &lt;桃羽もえは&gt;
 &lt;AHI&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小橋マリカ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2756,7 +2755,7 @@
     <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RX2)</f>
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2932,7 +2931,7 @@
      LEN(X5:X1001) - LEN(SUBSTITUTE(X5:X1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
@@ -3623,7 +3622,7 @@
         <v>163</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3911,7 +3910,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3925,7 +3924,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -4052,7 +4051,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4073,7 +4072,7 @@
       </c>
       <c r="W36" s="3"/>
       <c r="X36" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4152,7 +4151,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4228,7 +4227,7 @@
         <v>91</v>
       </c>
       <c r="W40" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="X40" s="3"/>
       <c r="Y40" s="1"/>
@@ -4240,7 +4239,7 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
@@ -4264,7 +4263,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -4275,7 +4274,7 @@
         <v>133</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4310,10 +4309,10 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
@@ -4324,7 +4323,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4353,7 +4352,7 @@
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4364,7 +4363,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>23</v>
@@ -4393,7 +4392,7 @@
         <v>114</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>182</v>
+        <v>228</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4404,7 +4403,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4427,7 +4426,7 @@
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
@@ -4476,7 +4475,7 @@
         <v>67</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -4494,7 +4493,7 @@
         <v>93</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="X46" s="3" t="s">
         <v>128</v>
@@ -4547,7 +4546,7 @@
         <v>147</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4586,10 +4585,10 @@
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4603,16 +4602,16 @@
         <v>48</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4714,10 +4713,10 @@
         <v>174</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>173</v>
@@ -4754,10 +4753,10 @@
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4795,7 +4794,7 @@
         <v>149</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>106</v>
@@ -4816,7 +4815,7 @@
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="1"/>
@@ -4831,7 +4830,7 @@
         <v>181</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>159</v>
@@ -4847,10 +4846,10 @@
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -4874,7 +4873,7 @@
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
@@ -4887,18 +4886,18 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>178</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
@@ -4906,13 +4905,13 @@
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4920,7 +4919,7 @@
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="1"/>
@@ -4933,22 +4932,22 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>157</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -4964,7 +4963,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B07DF9-1DA6-4C18-8E14-0A43FA0EAF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445932DE-C36F-45B4-B4B5-BFC96511D0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-68" yWindow="-68" windowWidth="28936" windowHeight="15616" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -394,10 +394,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>DASHチサコ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>岩田美香
 橋本千紘</t>
     <rPh sb="0" eb="4">
@@ -1276,11 +1272,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>わかな
-藤原あむ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>天咲光由
 ボジラ</t>
     <phoneticPr fontId="1"/>
@@ -1745,6 +1736,21 @@
   </si>
   <si>
     <t>小橋マリカ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DASHチサコ(休)</t>
+    <rPh sb="8" eb="9">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>わかな
+藤原あむ(休)</t>
+    <rPh sb="9" eb="10">
+      <t>キュウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2734,7 +2740,7 @@
   <sheetData>
     <row r="1" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2971,7 +2977,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>16</v>
@@ -2983,19 +2989,19 @@
         <v>46</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>49</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>18</v>
@@ -3010,13 +3016,13 @@
         <v>6</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>34</v>
@@ -3299,7 +3305,7 @@
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X13" s="3"/>
       <c r="Y13" s="1"/>
@@ -3333,7 +3339,7 @@
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>14</v>
@@ -3368,7 +3374,7 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
@@ -3433,10 +3439,10 @@
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
@@ -3606,7 +3612,7 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
@@ -3619,10 +3625,10 @@
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3654,7 +3660,7 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
@@ -3675,7 +3681,7 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -3688,7 +3694,7 @@
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
@@ -3719,7 +3725,7 @@
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>31</v>
@@ -3755,7 +3761,7 @@
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X27" s="3"/>
       <c r="Y27" s="1"/>
@@ -3779,7 +3785,7 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -3792,7 +3798,7 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
@@ -3820,7 +3826,7 @@
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
@@ -3857,7 +3863,7 @@
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="X30" s="3"/>
       <c r="Y30" s="1"/>
@@ -3910,7 +3916,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3921,10 +3927,10 @@
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -3951,13 +3957,13 @@
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="X33" s="3"/>
       <c r="Y33" s="1"/>
@@ -3973,20 +3979,20 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>50</v>
+        <v>227</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -3996,11 +4002,11 @@
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W34" s="3"/>
       <c r="X34" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
@@ -4030,11 +4036,11 @@
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="W35" s="3"/>
       <c r="X35" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
@@ -4045,13 +4051,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4068,11 +4074,11 @@
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="W36" s="3"/>
       <c r="X36" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4103,7 +4109,7 @@
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="X37" s="3"/>
       <c r="Y37" s="1"/>
@@ -4124,7 +4130,7 @@
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
@@ -4139,7 +4145,7 @@
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X38" s="3"/>
       <c r="Y38" s="1"/>
@@ -4151,15 +4157,15 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -4168,7 +4174,7 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
@@ -4182,7 +4188,7 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
@@ -4193,16 +4199,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4213,7 +4219,7 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
@@ -4224,10 +4230,10 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="W40" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="X40" s="3"/>
       <c r="Y40" s="1"/>
@@ -4239,21 +4245,21 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4263,18 +4269,18 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4285,7 +4291,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4309,10 +4315,10 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
@@ -4323,7 +4329,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4338,7 +4344,7 @@
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
@@ -4348,11 +4354,11 @@
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
       <c r="V43" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4363,7 +4369,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>23</v>
@@ -4389,10 +4395,10 @@
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4403,7 +4409,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4411,10 +4417,10 @@
         <v>11</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -4422,27 +4428,27 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
@@ -4453,13 +4459,13 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>13</v>
@@ -4472,31 +4478,31 @@
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4507,7 +4513,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4515,24 +4521,24 @@
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O47" s="3"/>
       <c r="P47" s="3"/>
@@ -4543,10 +4549,10 @@
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4571,7 +4577,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
@@ -4579,16 +4585,16 @@
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
       <c r="S48" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4602,23 +4608,23 @@
         <v>48</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
         <v>27</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
@@ -4627,19 +4633,19 @@
       <c r="O49" s="3"/>
       <c r="P49" s="3"/>
       <c r="Q49" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="X49" s="3"/>
       <c r="Y49" s="1"/>
@@ -4651,37 +4657,37 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4689,14 +4695,14 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
@@ -4710,19 +4716,19 @@
         <v>24</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
@@ -4730,33 +4736,33 @@
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4767,7 +4773,7 @@
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>33</v>
@@ -4776,46 +4782,46 @@
         <v>43</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G52" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K52" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I52" s="3" t="s">
+      <c r="L52" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M52" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="1"/>
@@ -4827,53 +4833,53 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>179</v>
+        <v>228</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
@@ -4886,32 +4892,32 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4919,7 +4925,7 @@
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="1"/>
@@ -4928,33 +4934,33 @@
     </row>
     <row r="55" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -4963,7 +4969,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>
@@ -4979,7 +4985,7 @@
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445932DE-C36F-45B4-B4B5-BFC96511D0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40514B3B-056D-4380-A207-3E1E07DC0B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-68" yWindow="-68" windowWidth="28936" windowHeight="15616" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -1356,11 +1356,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>鈴木ユラ(アルマリブレ)
-真白優希(Rose)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>堀このみ(Rose)</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1749,6 +1744,14 @@
     <t>わかな
 藤原あむ(休)</t>
     <rPh sb="9" eb="10">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鈴木ユラ(アルマリブレ)
+真白優希(Rose)(休)</t>
+    <rPh sb="24" eb="25">
       <t>キュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -3628,7 +3631,7 @@
         <v>162</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3916,7 +3919,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3930,7 +3933,7 @@
         <v>57</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -3992,7 +3995,7 @@
         <v>85</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -4157,7 +4160,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4245,7 +4248,7 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
@@ -4269,7 +4272,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -4280,7 +4283,7 @@
         <v>132</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4315,7 +4318,7 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>183</v>
@@ -4358,7 +4361,7 @@
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4398,7 +4401,7 @@
         <v>113</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4481,7 +4484,7 @@
         <v>66</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -4499,7 +4502,7 @@
         <v>92</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="X46" s="3" t="s">
         <v>127</v>
@@ -4552,7 +4555,7 @@
         <v>146</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4591,7 +4594,7 @@
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>188</v>
@@ -4608,16 +4611,16 @@
         <v>48</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4719,10 +4722,10 @@
         <v>173</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>172</v>
@@ -4759,10 +4762,10 @@
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4800,7 +4803,7 @@
         <v>148</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>105</v>
@@ -4821,7 +4824,7 @@
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="1"/>
@@ -4836,7 +4839,7 @@
         <v>179</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>158</v>
@@ -4852,10 +4855,10 @@
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -4864,7 +4867,7 @@
         <v>168</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>155</v>
@@ -4879,7 +4882,7 @@
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
@@ -4892,18 +4895,18 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>177</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
@@ -4911,13 +4914,13 @@
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4925,7 +4928,7 @@
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="1"/>
@@ -4938,22 +4941,22 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>156</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -4969,7 +4972,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40514B3B-056D-4380-A207-3E1E07DC0B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9FB900-2246-4F70-BB6F-B9832AEA3652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="229">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1542,14 +1542,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>郷田明日香(休)
-ブランキー真帆
-Chi Chi
-ZONES
-勇気みなみ(休)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>あきば栞(SECRETBASE)
 MICHIKO(休)</t>
     <rPh sb="3" eb="4">
@@ -1754,6 +1746,14 @@
     <rPh sb="24" eb="25">
       <t>キュウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>郷田明日香(休)
+ブランキー真帆(休)
+Chi Chi
+ZONES
+勇気みなみ(休)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3631,7 +3631,7 @@
         <v>162</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3919,7 +3919,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3933,7 +3933,7 @@
         <v>57</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -3995,7 +3995,7 @@
         <v>85</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -4160,7 +4160,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4248,7 +4248,7 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
@@ -4272,7 +4272,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -4318,7 +4318,7 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>183</v>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4401,7 +4401,7 @@
         <v>113</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4594,7 +4594,7 @@
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>188</v>
@@ -4611,7 +4611,7 @@
         <v>48</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>198</v>
@@ -4722,7 +4722,7 @@
         <v>173</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>204</v>
@@ -4762,10 +4762,10 @@
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4839,7 +4839,7 @@
         <v>179</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>158</v>
@@ -4858,7 +4858,7 @@
         <v>196</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -4867,7 +4867,7 @@
         <v>168</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>155</v>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>177</v>
@@ -4906,7 +4906,7 @@
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
@@ -4941,16 +4941,16 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>156</v>
@@ -4972,7 +4972,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9FB900-2246-4F70-BB6F-B9832AEA3652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB11C459-045E-4807-8F7E-D611F2317511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1510,23 +1510,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>苺畑ひより(666)
-横井真菜(REINA)
-タギリヒメ真夢(九州女子プロレス)
-彩月悠叶(Evolution, 2AW)
-さいとう(アップタウン)
-しおの(アップタウン)
-小久保アリサ(BBJ)
-CHIKA(EVO)</t>
-    <rPh sb="31" eb="33">
-      <t>キュウシュウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ジョシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ビクトリア弓月
 田中きずな(休)
 瀬戸レア</t>
@@ -1754,6 +1737,22 @@
 Chi Chi
 ZONES
 勇気みなみ(休)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>苺畑ひより(666)
+横井真菜(REINA)
+タギリヒメ真夢(九州女子プロレス)
+彩月悠叶(Evolution, 2AW)
+さいとう(アップタウン)
+小久保アリサ(BBJ)
+CHIKA(EVO)</t>
+    <rPh sb="31" eb="33">
+      <t>キュウシュウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジョシ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2764,7 +2763,7 @@
     <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RX2)</f>
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2932,7 +2931,7 @@
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="X2" s="1" cm="1">
         <f t="array" ref="X2">SUMPRODUCT(
@@ -3631,7 +3630,7 @@
         <v>162</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3919,7 +3918,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3933,7 +3932,7 @@
         <v>57</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -3995,7 +3994,7 @@
         <v>85</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -4160,7 +4159,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4248,7 +4247,7 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
@@ -4272,7 +4271,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -4318,7 +4317,7 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>183</v>
@@ -4361,7 +4360,7 @@
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4401,7 +4400,7 @@
         <v>113</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4594,7 +4593,7 @@
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>188</v>
@@ -4611,7 +4610,7 @@
         <v>48</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>198</v>
@@ -4722,10 +4721,10 @@
         <v>173</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>172</v>
@@ -4762,10 +4761,10 @@
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4831,7 +4830,7 @@
       <c r="Z52" s="1"/>
       <c r="AD52" s="1"/>
     </row>
-    <row r="53" spans="2:30" ht="132" x14ac:dyDescent="0.7">
+    <row r="53" spans="2:30" ht="115.5" x14ac:dyDescent="0.7">
       <c r="B53" s="3">
         <v>2025</v>
       </c>
@@ -4839,7 +4838,7 @@
         <v>179</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>158</v>
@@ -4858,7 +4857,7 @@
         <v>196</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -4867,7 +4866,7 @@
         <v>168</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>155</v>
@@ -4882,7 +4881,7 @@
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
@@ -4895,7 +4894,7 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>177</v>
@@ -4906,7 +4905,7 @@
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
@@ -4941,16 +4940,16 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>156</v>
@@ -4972,7 +4971,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB11C459-045E-4807-8F7E-D611F2317511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6220F564-B67B-4506-B54A-B0CECF59E463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -788,10 +788,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>沙恵</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>マリ卍</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1113,11 +1109,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>風南ユキ
-望天セレネ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>&lt;Y&gt;</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1590,33 +1581,6 @@
     </rPh>
     <rPh sb="47" eb="49">
       <t>ベツメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>風城ハル
-芦田美歩(別名あり)
-大久保琉那(休)
-鈴木志乃
-凍雅
-上原わかな</t>
-    <rPh sb="5" eb="9">
-      <t>アシダミフ</t>
-    </rPh>
-    <rPh sb="16" eb="21">
-      <t>オオクボルナ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ヤス</t>
-    </rPh>
-    <rPh sb="25" eb="29">
-      <t>スズキシノ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>トウガ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ウエハラ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1752,6 +1716,48 @@
     </rPh>
     <rPh sb="33" eb="35">
       <t>ジョシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風南ユキ(休)
+望天セレネ</t>
+    <rPh sb="5" eb="6">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沙恵(休)</t>
+    <rPh sb="3" eb="4">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風城ハル
+芦田美歩(別名あり)
+大久保琉那(休)
+鈴木志乃(休)
+凍雅
+上原わかな</t>
+    <rPh sb="5" eb="9">
+      <t>アシダミフ</t>
+    </rPh>
+    <rPh sb="16" eb="21">
+      <t>オオクボルナ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヤス</t>
+    </rPh>
+    <rPh sb="25" eb="29">
+      <t>スズキシノ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>トウガ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ウエハラ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2991,7 +2997,7 @@
         <v>46</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>54</v>
@@ -3003,7 +3009,7 @@
         <v>49</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>18</v>
@@ -3021,7 +3027,7 @@
         <v>115</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="V4" s="2" t="s">
         <v>88</v>
@@ -3441,10 +3447,10 @@
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
@@ -3627,10 +3633,10 @@
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3662,7 +3668,7 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
@@ -3918,7 +3924,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3932,7 +3938,7 @@
         <v>57</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -3965,7 +3971,7 @@
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X33" s="3"/>
       <c r="Y33" s="1"/>
@@ -3981,20 +3987,20 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
         <v>85</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -4042,7 +4048,7 @@
       </c>
       <c r="W35" s="3"/>
       <c r="X35" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
@@ -4053,13 +4059,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4080,7 +4086,7 @@
       </c>
       <c r="W36" s="3"/>
       <c r="X36" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4159,7 +4165,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4190,7 +4196,7 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
@@ -4201,10 +4207,10 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>40</v>
@@ -4235,7 +4241,7 @@
         <v>90</v>
       </c>
       <c r="W40" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="X40" s="3"/>
       <c r="Y40" s="1"/>
@@ -4247,21 +4253,21 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4271,7 +4277,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -4279,10 +4285,10 @@
         <v>93</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4293,7 +4299,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4317,10 +4323,10 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
@@ -4331,7 +4337,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4360,7 +4366,7 @@
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4371,7 +4377,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>23</v>
@@ -4400,7 +4406,7 @@
         <v>113</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4411,7 +4417,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4422,7 +4428,7 @@
         <v>96</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -4434,20 +4440,20 @@
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>116</v>
+        <v>227</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3" t="s">
         <v>103</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>111</v>
@@ -4461,13 +4467,13 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>13</v>
@@ -4483,7 +4489,7 @@
         <v>66</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -4494,17 +4500,17 @@
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3" t="s">
         <v>92</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4515,7 +4521,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4530,7 +4536,7 @@
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4551,10 +4557,10 @@
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4593,10 +4599,10 @@
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4610,16 +4616,16 @@
         <v>48</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4643,11 +4649,11 @@
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X49" s="3"/>
       <c r="Y49" s="1"/>
@@ -4659,19 +4665,19 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>21</v>
@@ -4681,7 +4687,7 @@
         <v>70</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>68</v>
@@ -4689,7 +4695,7 @@
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4697,14 +4703,14 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
@@ -4718,16 +4724,16 @@
         <v>24</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>107</v>
@@ -4742,29 +4748,29 @@
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O51" s="3" t="s">
         <v>108</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4784,13 +4790,13 @@
         <v>43</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>104</v>
@@ -4799,17 +4805,17 @@
         <v>72</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>105</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
@@ -4818,12 +4824,12 @@
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="1"/>
@@ -4835,13 +4841,13 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>102</v>
@@ -4850,38 +4856,38 @@
         <v>94</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>155</v>
+        <v>226</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
@@ -4894,32 +4900,32 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4927,7 +4933,7 @@
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="1"/>
@@ -4936,33 +4942,33 @@
     </row>
     <row r="55" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -4971,7 +4977,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="229">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6220F564-B67B-4506-B54A-B0CECF59E463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665DE478-AA51-457F-9C99-7C984BE24545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -130,14 +130,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>林下詩美
-松井珠紗</t>
-    <rPh sb="5" eb="9">
-      <t>マツイミサ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>アジャコング</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -853,13 +845,6 @@
     </rPh>
     <rPh sb="4" eb="5">
       <t>マレ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>藍川はるか</t>
-    <rPh sb="0" eb="2">
-      <t>アイカワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1758,6 +1743,21 @@
     </rPh>
     <rPh sb="36" eb="38">
       <t>ウエハラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>松井珠紗</t>
+    <rPh sb="0" eb="4">
+      <t>マツイミサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>藍川はるか
+林下詩美</t>
+    <rPh sb="0" eb="2">
+      <t>アイカワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2748,7 +2748,7 @@
   <sheetData>
     <row r="1" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2801,7 +2801,7 @@
      LEN(F5:F1001) - LEN(SUBSTITUTE(F5:F1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2" s="1" cm="1">
         <f t="array" ref="G2">SUMPRODUCT(
@@ -2945,7 +2945,7 @@
      LEN(X5:X1001) - LEN(SUBSTITUTE(X5:X1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
@@ -2979,61 +2979,61 @@
         <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>9</v>
@@ -3145,7 +3145,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3162,7 +3162,7 @@
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
@@ -3313,7 +3313,7 @@
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="X13" s="3"/>
       <c r="Y13" s="1"/>
@@ -3338,7 +3338,7 @@
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
@@ -3347,10 +3347,10 @@
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
@@ -3382,7 +3382,7 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
@@ -3398,7 +3398,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
@@ -3408,7 +3408,7 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
@@ -3447,10 +3447,10 @@
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
@@ -3620,7 +3620,7 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
@@ -3633,10 +3633,10 @@
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3668,7 +3668,7 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
@@ -3689,7 +3689,7 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -3702,7 +3702,7 @@
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
@@ -3733,10 +3733,10 @@
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
@@ -3747,7 +3747,7 @@
         <v>1999</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -3769,7 +3769,7 @@
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X27" s="3"/>
       <c r="Y27" s="1"/>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -3793,7 +3793,7 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -3806,7 +3806,7 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
@@ -3822,7 +3822,7 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -3834,7 +3834,7 @@
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
@@ -3871,7 +3871,7 @@
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X30" s="3"/>
       <c r="Y30" s="1"/>
@@ -3924,7 +3924,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3935,10 +3935,10 @@
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -3965,13 +3965,13 @@
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="X33" s="3"/>
       <c r="Y33" s="1"/>
@@ -3987,20 +3987,20 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -4010,11 +4010,11 @@
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="W34" s="3"/>
       <c r="X34" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
@@ -4044,11 +4044,11 @@
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="W35" s="3"/>
       <c r="X35" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
@@ -4059,13 +4059,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4082,11 +4082,11 @@
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W36" s="3"/>
       <c r="X36" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4117,7 +4117,7 @@
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="X37" s="3"/>
       <c r="Y37" s="1"/>
@@ -4138,14 +4138,14 @@
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
       <c r="Q38" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
@@ -4153,7 +4153,7 @@
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="X38" s="3"/>
       <c r="Y38" s="1"/>
@@ -4165,15 +4165,15 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -4182,21 +4182,21 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
@@ -4207,16 +4207,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4227,7 +4227,7 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
@@ -4238,10 +4238,10 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="W40" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="X40" s="3"/>
       <c r="Y40" s="1"/>
@@ -4253,21 +4253,21 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4277,18 +4277,18 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4299,11 +4299,11 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
@@ -4323,10 +4323,10 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
@@ -4337,11 +4337,11 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -4352,7 +4352,7 @@
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
@@ -4362,11 +4362,11 @@
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
       <c r="V43" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4377,17 +4377,17 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
@@ -4403,10 +4403,10 @@
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4417,7 +4417,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4425,10 +4425,10 @@
         <v>11</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -4436,27 +4436,27 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
@@ -4467,50 +4467,50 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>13</v>
+        <v>227</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>126</v>
+        <v>228</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4521,32 +4521,32 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O47" s="3"/>
       <c r="P47" s="3"/>
@@ -4557,10 +4557,10 @@
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4571,7 +4571,7 @@
         <v>2020</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -4585,7 +4585,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
@@ -4593,16 +4593,16 @@
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
       <c r="S48" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4613,26 +4613,26 @@
         <v>2021</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
@@ -4641,19 +4641,19 @@
       <c r="O49" s="3"/>
       <c r="P49" s="3"/>
       <c r="Q49" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="X49" s="3"/>
       <c r="Y49" s="1"/>
@@ -4665,37 +4665,37 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4703,14 +4703,14 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
@@ -4721,56 +4721,56 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4781,55 +4781,55 @@
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I52" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="M52" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="1"/>
@@ -4841,53 +4841,53 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
@@ -4900,32 +4900,32 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4933,7 +4933,7 @@
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="1"/>
@@ -4942,33 +4942,33 @@
     </row>
     <row r="55" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -4977,7 +4977,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>
@@ -4993,7 +4993,7 @@
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665DE478-AA51-457F-9C99-7C984BE24545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AE674A-7C4E-436B-945A-D1177AC8C11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1355,36 +1355,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>櫻井裕子(COLORS)
-網倉理奈(COLORS)
-KONOHA(銀河)(2026.5.24引退予定)
-花園桃花(アップタウン)
-杏ちゃむ(信州, DIE)
-竹林早苗(BBJ)</t>
-    <rPh sb="0" eb="4">
-      <t>サクライユウコ</t>
-    </rPh>
-    <rPh sb="13" eb="17">
-      <t>アミクラリナ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ギンガ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>インタイ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ヨテイ</t>
-    </rPh>
-    <rPh sb="52" eb="56">
-      <t>ハナゾノモモカ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>シンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>未愛</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1758,6 +1728,26 @@
 林下詩美</t>
     <rPh sb="0" eb="2">
       <t>アイカワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>櫻井裕子(COLORS)
+網倉理奈(COLORS)
+花園桃花(アップタウン)
+杏ちゃむ(信州, DIE)
+竹林早苗(BBJ)</t>
+    <rPh sb="0" eb="4">
+      <t>サクライユウコ</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>アミクラリナ</t>
+    </rPh>
+    <rPh sb="26" eb="30">
+      <t>ハナゾノモモカ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>シンシュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2769,7 +2759,7 @@
     <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RX2)</f>
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2937,7 +2927,7 @@
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="X2" s="1" cm="1">
         <f t="array" ref="X2">SUMPRODUCT(
@@ -3636,7 +3626,7 @@
         <v>158</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3924,7 +3914,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3938,7 +3928,7 @@
         <v>56</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -4000,7 +3990,7 @@
         <v>84</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -4165,7 +4155,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4253,7 +4243,7 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
@@ -4277,7 +4267,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -4288,7 +4278,7 @@
         <v>129</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4323,7 +4313,7 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>179</v>
@@ -4366,7 +4356,7 @@
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4406,7 +4396,7 @@
         <v>112</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4446,7 +4436,7 @@
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3" t="s">
@@ -4476,7 +4466,7 @@
         <v>131</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4489,7 +4479,7 @@
         <v>65</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -4507,10 +4497,10 @@
         <v>91</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4599,7 +4589,7 @@
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>184</v>
@@ -4616,16 +4606,16 @@
         <v>47</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4727,10 +4717,10 @@
         <v>169</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>168</v>
@@ -4767,10 +4757,10 @@
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4808,7 +4798,7 @@
         <v>145</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>104</v>
@@ -4829,7 +4819,7 @@
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="1"/>
@@ -4844,7 +4834,7 @@
         <v>175</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>154</v>
@@ -4860,10 +4850,10 @@
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -4872,10 +4862,10 @@
         <v>164</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
@@ -4887,7 +4877,7 @@
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
@@ -4900,18 +4890,18 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
@@ -4919,7 +4909,7 @@
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
@@ -4946,22 +4936,22 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>152</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -4977,7 +4967,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AE674A-7C4E-436B-945A-D1177AC8C11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8996700E-7971-4636-B4A4-17A854FC016D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="503" yWindow="1972" windowWidth="21599" windowHeight="11296" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -1176,27 +1176,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>吏南
-妃南
-鈴季すず
-水森由菜
-星来芽依
-ジーナ</t>
-    <rPh sb="6" eb="8">
-      <t>スズキ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ミズモリ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ユナ</t>
-    </rPh>
-    <rPh sb="16" eb="20">
-      <t>セイラメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>虎牙のん</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1329,10 +1308,6 @@
   <si>
     <t>柳川澄樺
 神姫楽ミサ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>堀このみ(Rose)</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1724,14 +1699,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>藍川はるか
-林下詩美</t>
-    <rPh sb="0" eb="2">
-      <t>アイカワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>櫻井裕子(COLORS)
 網倉理奈(COLORS)
 花園桃花(アップタウン)
@@ -1749,6 +1716,40 @@
     <rPh sb="44" eb="46">
       <t>シンシュウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>藍川はるか</t>
+    <rPh sb="0" eb="2">
+      <t>アイカワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吏南
+妃南
+鈴季すず
+水森由菜
+星来芽依
+ジーナ
+林下詩美</t>
+    <rPh sb="6" eb="8">
+      <t>スズキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ミズモリ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ユナ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>セイラメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>堀このみ(Rose)
+彩桜(アップタウン)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2759,7 +2760,7 @@
     <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RX2)</f>
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2767,7 +2768,7 @@
      LEN(C5:C1001) - LEN(SUBSTITUTE(C5:C1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1" cm="1">
         <f t="array" ref="D2">SUMPRODUCT(
@@ -2927,7 +2928,7 @@
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="X2" s="1" cm="1">
         <f t="array" ref="X2">SUMPRODUCT(
@@ -2935,7 +2936,7 @@
      LEN(X5:X1001) - LEN(SUBSTITUTE(X5:X1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
@@ -2987,7 +2988,7 @@
         <v>45</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>53</v>
@@ -3626,7 +3627,7 @@
         <v>158</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3914,7 +3915,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3928,7 +3929,7 @@
         <v>56</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -3990,7 +3991,7 @@
         <v>84</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -4055,7 +4056,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4076,7 +4077,7 @@
       </c>
       <c r="W36" s="3"/>
       <c r="X36" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4155,7 +4156,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4231,7 +4232,7 @@
         <v>89</v>
       </c>
       <c r="W40" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="X40" s="3"/>
       <c r="Y40" s="1"/>
@@ -4243,7 +4244,7 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
@@ -4267,7 +4268,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -4278,7 +4279,7 @@
         <v>129</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4313,10 +4314,10 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
@@ -4327,7 +4328,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4356,7 +4357,7 @@
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4367,7 +4368,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>22</v>
@@ -4396,7 +4397,7 @@
         <v>112</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4407,7 +4408,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4430,13 +4431,13 @@
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3" t="s">
@@ -4452,12 +4453,12 @@
       <c r="Z45" s="1"/>
       <c r="AD45" s="1"/>
     </row>
-    <row r="46" spans="2:30" ht="99" x14ac:dyDescent="0.7">
+    <row r="46" spans="2:30" ht="115.5" x14ac:dyDescent="0.7">
       <c r="B46" s="3">
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>141</v>
@@ -4466,7 +4467,7 @@
         <v>131</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4479,7 +4480,7 @@
         <v>65</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -4497,10 +4498,10 @@
         <v>91</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4526,7 +4527,7 @@
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4550,7 +4551,7 @@
         <v>143</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4589,10 +4590,10 @@
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4606,16 +4607,16 @@
         <v>47</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4655,7 +4656,7 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>134</v>
@@ -4714,16 +4715,16 @@
         <v>23</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>106</v>
@@ -4757,10 +4758,10 @@
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4798,7 +4799,7 @@
         <v>145</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>104</v>
@@ -4819,7 +4820,7 @@
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="1"/>
@@ -4831,10 +4832,10 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>154</v>
@@ -4850,10 +4851,10 @@
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -4862,10 +4863,10 @@
         <v>164</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
@@ -4873,11 +4874,11 @@
         <v>116</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
@@ -4890,32 +4891,32 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4923,7 +4924,7 @@
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="1"/>
@@ -4936,22 +4937,22 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>152</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -4967,7 +4968,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8996700E-7971-4636-B4A4-17A854FC016D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A11A467-6588-49E2-BC04-F5B8FE720F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="503" yWindow="1972" windowWidth="21599" windowHeight="11296" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -1009,10 +1009,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>リアラ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>入江彩乃</t>
     <rPh sb="0" eb="4">
       <t>イリエアヤノ</t>
@@ -1750,6 +1746,13 @@
   <si>
     <t>堀このみ(Rose)
 彩桜(アップタウン)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リアラ(休)</t>
+    <rPh sb="4" eb="5">
+      <t>キュウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2721,7 +2724,7 @@
     <col min="13" max="13" width="13.5" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="17.4375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.5625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.9375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10.25" bestFit="1" customWidth="1"/>
@@ -2988,7 +2991,7 @@
         <v>45</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>53</v>
@@ -3000,7 +3003,7 @@
         <v>48</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>17</v>
@@ -3624,10 +3627,10 @@
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3659,7 +3662,7 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
@@ -3915,7 +3918,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3929,7 +3932,7 @@
         <v>56</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -3978,20 +3981,20 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
         <v>84</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -4050,13 +4053,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4077,7 +4080,7 @@
       </c>
       <c r="W36" s="3"/>
       <c r="X36" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4156,7 +4159,7 @@
         <v>2011</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4201,7 +4204,7 @@
         <v>123</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>39</v>
@@ -4232,7 +4235,7 @@
         <v>89</v>
       </c>
       <c r="W40" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="X40" s="3"/>
       <c r="Y40" s="1"/>
@@ -4244,7 +4247,7 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
@@ -4252,13 +4255,13 @@
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4268,7 +4271,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -4279,7 +4282,7 @@
         <v>129</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4290,7 +4293,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4314,10 +4317,10 @@
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
@@ -4328,7 +4331,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4357,7 +4360,7 @@
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4368,7 +4371,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>22</v>
@@ -4397,7 +4400,7 @@
         <v>112</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4408,7 +4411,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4431,13 +4434,13 @@
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3" t="s">
@@ -4458,16 +4461,16 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>131</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4480,7 +4483,7 @@
         <v>65</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -4498,10 +4501,10 @@
         <v>91</v>
       </c>
       <c r="W46" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="X46" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>226</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4512,7 +4515,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4527,7 +4530,7 @@
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4548,10 +4551,10 @@
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4590,10 +4593,10 @@
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4607,16 +4610,16 @@
         <v>47</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4656,7 +4659,7 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>134</v>
@@ -4668,7 +4671,7 @@
         <v>133</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>20</v>
@@ -4678,7 +4681,7 @@
         <v>69</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>67</v>
@@ -4686,7 +4689,7 @@
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
@@ -4701,7 +4704,7 @@
         <v>137</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
@@ -4715,16 +4718,16 @@
         <v>23</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>106</v>
@@ -4754,14 +4757,14 @@
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>140</v>
+        <v>228</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4784,10 +4787,10 @@
         <v>122</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>103</v>
@@ -4796,17 +4799,17 @@
         <v>71</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>104</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
@@ -4820,7 +4823,7 @@
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="1"/>
@@ -4832,13 +4835,13 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>101</v>
@@ -4847,26 +4850,26 @@
         <v>93</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
@@ -4874,11 +4877,11 @@
         <v>116</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
@@ -4891,32 +4894,32 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -4924,7 +4927,7 @@
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="1"/>
@@ -4933,33 +4936,33 @@
     </row>
     <row r="55" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -4968,7 +4971,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A11A467-6588-49E2-BC04-F5B8FE720F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703E72C8-850B-4049-9823-342B3C562F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="230">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1539,20 +1539,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>梨央
-弥福かな
-ゴんべ
-西村摩利乃
-松橋ななを</t>
-    <rPh sb="0" eb="2">
-      <t>リオ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ニシムラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>松橋ななを?</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1580,12 +1566,6 @@
   <si>
     <t>天羽瑠迦
 早乙女聖</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>山根百合
-確変むぎ
-松﨑紗弥</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1753,6 +1733,30 @@
     <rPh sb="4" eb="5">
       <t>キュウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;高野玲菜&gt;6.13プロテスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>梨央
+弥福かな
+ゴんべ
+西村摩利乃</t>
+    <rPh sb="0" eb="2">
+      <t>リオ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニシムラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>松橋ななを
+山根百合
+確変むぎ
+松﨑紗弥</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2763,7 +2767,7 @@
     <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RX2)</f>
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2859,7 +2863,7 @@
      LEN(N5:N1001) - LEN(SUBSTITUTE(N5:N1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O2" s="1" cm="1">
         <f t="array" ref="O2">SUMPRODUCT(
@@ -3994,7 +3998,7 @@
         <v>84</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -4400,7 +4404,7 @@
         <v>112</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4440,7 +4444,7 @@
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3" t="s">
@@ -4461,7 +4465,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>140</v>
@@ -4470,7 +4474,7 @@
         <v>131</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4501,10 +4505,10 @@
         <v>91</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4593,7 +4597,7 @@
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>182</v>
@@ -4721,7 +4725,7 @@
         <v>167</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>195</v>
@@ -4757,14 +4761,14 @@
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
         <v>202</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4838,7 +4842,7 @@
         <v>173</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>153</v>
@@ -4857,7 +4861,7 @@
         <v>188</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -4866,10 +4870,10 @@
         <v>163</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
@@ -4881,20 +4885,20 @@
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
       <c r="AD53" s="1"/>
     </row>
-    <row r="54" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
+    <row r="54" spans="2:30" ht="66" x14ac:dyDescent="0.7">
       <c r="B54" s="3">
         <v>2026</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>171</v>
@@ -4905,7 +4909,7 @@
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
@@ -4927,7 +4931,7 @@
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="1"/>
@@ -4940,16 +4944,16 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>151</v>
@@ -4959,7 +4963,9 @@
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
+      <c r="N55" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
         <v>152</v>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703E72C8-850B-4049-9823-342B3C562F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0445209-5A28-4369-A3B7-37CBF1BF679C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="229">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1456,10 +1456,6 @@
     <t>コグマ
 葉月
 AZM</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>鹿島沙希</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2767,7 +2763,7 @@
     <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RX2)</f>
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2775,7 +2771,7 @@
      LEN(C5:C1001) - LEN(SUBSTITUTE(C5:C1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" cm="1">
         <f t="array" ref="D2">SUMPRODUCT(
@@ -3634,7 +3630,7 @@
         <v>157</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3922,7 +3918,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3936,7 +3932,7 @@
         <v>56</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -3998,7 +3994,7 @@
         <v>84</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -4162,9 +4158,7 @@
       <c r="B39" s="3">
         <v>2011</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>198</v>
-      </c>
+      <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
@@ -4275,7 +4269,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -4364,7 +4358,7 @@
       </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4404,7 +4398,7 @@
         <v>112</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4444,7 +4438,7 @@
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3" t="s">
@@ -4465,7 +4459,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>140</v>
@@ -4474,7 +4468,7 @@
         <v>131</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4505,10 +4499,10 @@
         <v>91</v>
       </c>
       <c r="W46" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="X46" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>223</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4597,7 +4591,7 @@
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>182</v>
@@ -4614,7 +4608,7 @@
         <v>47</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>190</v>
@@ -4725,7 +4719,7 @@
         <v>167</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>195</v>
@@ -4761,14 +4755,14 @@
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -4842,7 +4836,7 @@
         <v>173</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>153</v>
@@ -4861,7 +4855,7 @@
         <v>188</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -4870,10 +4864,10 @@
         <v>163</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
@@ -4885,7 +4879,7 @@
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="1"/>
@@ -4898,7 +4892,7 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>171</v>
@@ -4909,7 +4903,7 @@
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
@@ -4931,7 +4925,7 @@
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="1"/>
@@ -4944,16 +4938,16 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>151</v>
@@ -4964,7 +4958,7 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
@@ -4977,7 +4971,7 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0445209-5A28-4369-A3B7-37CBF1BF679C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21200964-921D-4BA6-B562-15FE9DC869ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="229">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -697,15 +698,6 @@
     </rPh>
     <rPh sb="12" eb="15">
       <t>シズクアキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>山岡聖怜
-心希
-山﨑裕花</t>
-    <rPh sb="5" eb="7">
-      <t>シンノ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1732,10 +1724,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;高野玲菜&gt;6.13プロテスト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>梨央
 弥福かな
 ゴんべ
@@ -1753,6 +1741,25 @@
 山根百合
 確変むぎ
 松﨑紗弥</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;高野玲菜&gt;プロテスト合格</t>
+    <rPh sb="11" eb="13">
+      <t>ゴウカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山岡聖怜(休)
+心希
+山﨑裕花</t>
+    <rPh sb="5" eb="6">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シンノ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1837,7 +1844,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="24">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1960,26 +1967,6 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2359,19 +2346,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}" name="テーブル1" displayName="テーブル1" ref="B4:X56" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
-  <autoFilter ref="B4:X56" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}"/>
-  <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{C5BCADDE-F600-4480-BD2B-E93168A1BF7F}" name="デビュー年" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{7319872F-B1DE-47E8-ADFA-F5962E445AE2}" name="Stardom" dataDxfId="21"/>
-    <tableColumn id="18" xr3:uid="{6DD05DFF-D195-4CF5-BFC5-531553A9ADC5}" name="AWG" dataDxfId="20"/>
-    <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリゴ" dataDxfId="18"/>
-    <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ" dataDxfId="17"/>
-    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="15"/>
-    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{0D2ABC96-F0CF-44E9-912A-CA35E8452616}" name="Venus" dataDxfId="13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}" name="テーブル1" displayName="テーブル1" ref="B4:W56" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+  <autoFilter ref="B4:W56" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}"/>
+  <tableColumns count="22">
+    <tableColumn id="1" xr3:uid="{C5BCADDE-F600-4480-BD2B-E93168A1BF7F}" name="デビュー年" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{7319872F-B1DE-47E8-ADFA-F5962E445AE2}" name="Stardom" dataDxfId="20"/>
+    <tableColumn id="18" xr3:uid="{6DD05DFF-D195-4CF5-BFC5-531553A9ADC5}" name="AWG" dataDxfId="19"/>
+    <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリゴ" dataDxfId="17"/>
+    <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ" dataDxfId="16"/>
+    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="14"/>
+    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="13"/>
     <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="12"/>
     <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="11"/>
     <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="10"/>
@@ -2707,63 +2693,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4F8F56-06F6-4E1D-8D81-5A485042419D}">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr defaultColWidth="27.3125" defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="1.875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.6875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.5625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.3125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.9375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.0625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="17.4375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.5625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.9375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="41.0625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.1875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="30.25" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="21.1875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="30.0625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="27.3125" style="1"/>
-    <col min="31" max="16384" width="27.3125" style="1"/>
+    <col min="6" max="6" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.6875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.8125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.6875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.4375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.3125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.9375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="30.375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.3125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.1875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="30.0625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="27.3125" style="1"/>
+    <col min="30" max="16384" width="27.3125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="K1" s="1"/>
+      <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
+      <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AD1" s="1"/>
-    </row>
-    <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC1" s="1"/>
+    </row>
+    <row r="2" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
-        <f>SUM(C2:RX2)</f>
-        <v>372</v>
+        <f>SUM(C2:RW2)</f>
+        <v>361</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2835,7 +2821,7 @@
      LEN(K5:K1001) - LEN(SUBSTITUTE(K5:K1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L2" s="1" cm="1">
         <f t="array" ref="L2">SUMPRODUCT(
@@ -2851,7 +2837,7 @@
      LEN(M5:M1001) - LEN(SUBSTITUTE(M5:M1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N2" s="1" cm="1">
         <f t="array" ref="N2">SUMPRODUCT(
@@ -2859,7 +2845,7 @@
      LEN(N5:N1001) - LEN(SUBSTITUTE(N5:N1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" cm="1">
         <f t="array" ref="O2">SUMPRODUCT(
@@ -2867,7 +2853,7 @@
      LEN(O5:O1001) - LEN(SUBSTITUTE(O5:O1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P2" s="1" cm="1">
         <f t="array" ref="P2">SUMPRODUCT(
@@ -2875,7 +2861,7 @@
      LEN(P5:P1001) - LEN(SUBSTITUTE(P5:P1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q2" s="1" cm="1">
         <f t="array" ref="Q2">SUMPRODUCT(
@@ -2883,7 +2869,7 @@
      LEN(Q5:Q1001) - LEN(SUBSTITUTE(Q5:Q1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R2" s="1" cm="1">
         <f t="array" ref="R2">SUMPRODUCT(
@@ -2915,7 +2901,7 @@
      LEN(U5:U1001) - LEN(SUBSTITUTE(U5:U1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" cm="1">
         <f t="array" ref="V2">SUMPRODUCT(
@@ -2923,7 +2909,7 @@
      LEN(V5:V1001) - LEN(SUBSTITUTE(V5:V1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="W2" s="1" cm="1">
         <f t="array" ref="W2">SUMPRODUCT(
@@ -2931,38 +2917,29 @@
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>53</v>
-      </c>
-      <c r="X2" s="1" cm="1">
-        <f t="array" ref="X2">SUMPRODUCT(
-  IF(LEN(X5:X1001)=0, 0,
-     LEN(X5:X1001) - LEN(SUBSTITUTE(X5:X1001, CHAR(10), "")) + 1
-  )
-)</f>
         <v>51</v>
       </c>
+      <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
-      <c r="AD2" s="1"/>
-    </row>
-    <row r="3" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC2" s="1"/>
+    </row>
+    <row r="3" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="K3" s="1"/>
+      <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
       <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
+      <c r="V3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
-      <c r="AD3" s="1"/>
-    </row>
-    <row r="4" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC3" s="1"/>
+    </row>
+    <row r="4" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
@@ -2991,52 +2968,49 @@
         <v>45</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>169</v>
+        <v>53</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>159</v>
+        <v>17</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X4" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AD4" s="1"/>
-    </row>
-    <row r="5" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC4" s="1"/>
+    </row>
+    <row r="5" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B5" s="3">
         <v>1977</v>
       </c>
@@ -3063,12 +3037,11 @@
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
+      <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AD5" s="1"/>
-    </row>
-    <row r="6" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC5" s="1"/>
+    </row>
+    <row r="6" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B6" s="3">
         <v>1978</v>
       </c>
@@ -3093,12 +3066,11 @@
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
+      <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AD6" s="1"/>
-    </row>
-    <row r="7" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC6" s="1"/>
+    </row>
+    <row r="7" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B7" s="3">
         <v>1979</v>
       </c>
@@ -3123,12 +3095,11 @@
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
+      <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
-      <c r="Z7" s="1"/>
-      <c r="AD7" s="1"/>
-    </row>
-    <row r="8" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC7" s="1"/>
+    </row>
+    <row r="8" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B8" s="3">
         <v>1980</v>
       </c>
@@ -3154,15 +3125,14 @@
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3" t="s">
+      <c r="W8" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
-      <c r="Z8" s="1"/>
-      <c r="AD8" s="1"/>
-    </row>
-    <row r="9" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC8" s="1"/>
+    </row>
+    <row r="9" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B9" s="3">
         <v>1981</v>
       </c>
@@ -3187,12 +3157,11 @@
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
+      <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
-      <c r="Z9" s="1"/>
-      <c r="AD9" s="1"/>
-    </row>
-    <row r="10" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC9" s="1"/>
+    </row>
+    <row r="10" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B10" s="3">
         <v>1982</v>
       </c>
@@ -3217,12 +3186,11 @@
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
+      <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
-      <c r="Z10" s="1"/>
-      <c r="AD10" s="1"/>
-    </row>
-    <row r="11" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC10" s="1"/>
+    </row>
+    <row r="11" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B11" s="3">
         <v>1983</v>
       </c>
@@ -3247,12 +3215,11 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
+      <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
-      <c r="Z11" s="1"/>
-      <c r="AD11" s="1"/>
-    </row>
-    <row r="12" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC11" s="1"/>
+    </row>
+    <row r="12" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B12" s="3">
         <v>1984</v>
       </c>
@@ -3277,12 +3244,11 @@
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
+      <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
-      <c r="Z12" s="1"/>
-      <c r="AD12" s="1"/>
-    </row>
-    <row r="13" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC12" s="1"/>
+    </row>
+    <row r="13" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B13" s="3">
         <v>1985</v>
       </c>
@@ -3305,16 +3271,15 @@
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="X13" s="3"/>
+      <c r="V13" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W13" s="3"/>
+      <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
-      <c r="Z13" s="1"/>
-      <c r="AD13" s="1"/>
-    </row>
-    <row r="14" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC13" s="1"/>
+    </row>
+    <row r="14" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B14" s="3">
         <v>1986</v>
       </c>
@@ -3330,27 +3295,26 @@
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
+      <c r="V14" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="W14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="X14" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
-      <c r="Z14" s="1"/>
-      <c r="AD14" s="1"/>
-    </row>
-    <row r="15" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC14" s="1"/>
+    </row>
+    <row r="15" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B15" s="3">
         <v>1987</v>
       </c>
@@ -3374,15 +3338,14 @@
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3" t="s">
+      <c r="W15" s="3" t="s">
         <v>99</v>
       </c>
+      <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
-      <c r="Z15" s="1"/>
-      <c r="AD15" s="1"/>
-    </row>
-    <row r="16" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC15" s="1"/>
+    </row>
+    <row r="16" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B16" s="3">
         <v>1988</v>
       </c>
@@ -3400,10 +3363,10 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3" t="s">
+      <c r="O16" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
@@ -3411,12 +3374,11 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
+      <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
-      <c r="Z16" s="1"/>
-      <c r="AD16" s="1"/>
-    </row>
-    <row r="17" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC16" s="1"/>
+    </row>
+    <row r="17" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B17" s="3">
         <v>1989</v>
       </c>
@@ -3439,18 +3401,17 @@
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
+      <c r="V17" s="3" t="s">
+        <v>119</v>
+      </c>
       <c r="W17" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>119</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
-      <c r="Z17" s="1"/>
-      <c r="AD17" s="1"/>
-    </row>
-    <row r="18" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC17" s="1"/>
+    </row>
+    <row r="18" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B18" s="3">
         <v>1990</v>
       </c>
@@ -3475,12 +3436,11 @@
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
+      <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
-      <c r="Z18" s="1"/>
-      <c r="AD18" s="1"/>
-    </row>
-    <row r="19" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC18" s="1"/>
+    </row>
+    <row r="19" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B19" s="3">
         <v>1991</v>
       </c>
@@ -3505,12 +3465,11 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
+      <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
-      <c r="Z19" s="1"/>
-      <c r="AD19" s="1"/>
-    </row>
-    <row r="20" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC19" s="1"/>
+    </row>
+    <row r="20" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B20" s="3">
         <v>1992</v>
       </c>
@@ -3535,12 +3494,11 @@
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
+      <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
-      <c r="Z20" s="1"/>
-      <c r="AD20" s="1"/>
-    </row>
-    <row r="21" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC20" s="1"/>
+    </row>
+    <row r="21" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B21" s="3">
         <v>1993</v>
       </c>
@@ -3565,12 +3523,11 @@
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
+      <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
-      <c r="Z21" s="1"/>
-      <c r="AD21" s="1"/>
-    </row>
-    <row r="22" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC21" s="1"/>
+    </row>
+    <row r="22" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B22" s="3">
         <v>1994</v>
       </c>
@@ -3595,12 +3552,11 @@
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
+      <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
-      <c r="Z22" s="1"/>
-      <c r="AD22" s="1"/>
-    </row>
-    <row r="23" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+      <c r="AC22" s="1"/>
+    </row>
+    <row r="23" spans="2:29" ht="33" x14ac:dyDescent="0.7">
       <c r="B23" s="3">
         <v>1995</v>
       </c>
@@ -3612,10 +3568,10 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>54</v>
       </c>
+      <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -3625,18 +3581,17 @@
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
+      <c r="V23" s="3" t="s">
+        <v>156</v>
+      </c>
       <c r="W23" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>204</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
-      <c r="Z23" s="1"/>
-      <c r="AD23" s="1"/>
-    </row>
-    <row r="24" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC23" s="1"/>
+    </row>
+    <row r="24" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B24" s="3">
         <v>1996</v>
       </c>
@@ -3660,15 +3615,14 @@
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3" t="s">
-        <v>156</v>
-      </c>
+      <c r="W24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
-      <c r="Z24" s="1"/>
-      <c r="AD24" s="1"/>
-    </row>
-    <row r="25" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC24" s="1"/>
+    </row>
+    <row r="25" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B25" s="3">
         <v>1997</v>
       </c>
@@ -3681,10 +3635,10 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3" t="s">
+      <c r="L25" s="3" t="s">
         <v>82</v>
       </c>
+      <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -3694,15 +3648,14 @@
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3" t="s">
+      <c r="W25" s="3" t="s">
         <v>75</v>
       </c>
+      <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
-      <c r="Z25" s="1"/>
-      <c r="AD25" s="1"/>
-    </row>
-    <row r="26" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC25" s="1"/>
+    </row>
+    <row r="26" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B26" s="3">
         <v>1998</v>
       </c>
@@ -3725,18 +3678,17 @@
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
+      <c r="V26" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="W26" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="X26" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
-      <c r="Z26" s="1"/>
-      <c r="AD26" s="1"/>
-    </row>
-    <row r="27" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC26" s="1"/>
+    </row>
+    <row r="27" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B27" s="3">
         <v>1999</v>
       </c>
@@ -3761,16 +3713,15 @@
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3" t="s">
+      <c r="V27" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="X27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
-      <c r="Z27" s="1"/>
-      <c r="AD27" s="1"/>
-    </row>
-    <row r="28" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+      <c r="AC27" s="1"/>
+    </row>
+    <row r="28" spans="2:29" ht="33" x14ac:dyDescent="0.7">
       <c r="B28" s="3">
         <v>2000</v>
       </c>
@@ -3785,10 +3736,10 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3" t="s">
+      <c r="L28" s="3" t="s">
         <v>83</v>
       </c>
+      <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
@@ -3798,15 +3749,14 @@
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3" t="s">
+      <c r="W28" s="3" t="s">
         <v>77</v>
       </c>
+      <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
-      <c r="Z28" s="1"/>
-      <c r="AD28" s="1"/>
-    </row>
-    <row r="29" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC28" s="1"/>
+    </row>
+    <row r="29" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B29" s="3">
         <v>2001</v>
       </c>
@@ -3826,21 +3776,20 @@
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="3" t="s">
+      <c r="Q29" s="3" t="s">
         <v>60</v>
       </c>
+      <c r="R29" s="3"/>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
+      <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
-      <c r="Z29" s="1"/>
-      <c r="AD29" s="1"/>
-    </row>
-    <row r="30" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC29" s="1"/>
+    </row>
+    <row r="30" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B30" s="3">
         <v>2002</v>
       </c>
@@ -3863,16 +3812,15 @@
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
-      <c r="W30" s="3" t="s">
+      <c r="V30" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="X30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
-      <c r="AD30" s="1"/>
-    </row>
-    <row r="31" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC30" s="1"/>
+    </row>
+    <row r="31" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B31" s="3">
         <v>2003</v>
       </c>
@@ -3897,12 +3845,11 @@
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
-      <c r="X31" s="3"/>
+      <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
-      <c r="Z31" s="1"/>
-      <c r="AD31" s="1"/>
-    </row>
-    <row r="32" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC31" s="1"/>
+    </row>
+    <row r="32" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B32" s="3">
         <v>2004</v>
       </c>
@@ -3916,10 +3863,10 @@
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3" t="s">
-        <v>199</v>
-      </c>
+      <c r="M32" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
@@ -3927,18 +3874,17 @@
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
+      <c r="V32" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="W32" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="X32" s="3" t="s">
-        <v>198</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
-      <c r="Z32" s="1"/>
-      <c r="AD32" s="1"/>
-    </row>
-    <row r="33" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+      <c r="AC32" s="1"/>
+    </row>
+    <row r="33" spans="2:29" ht="33" x14ac:dyDescent="0.7">
       <c r="B33" s="3">
         <v>2005</v>
       </c>
@@ -3957,22 +3903,21 @@
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
-      <c r="S33" s="3" t="s">
+      <c r="R33" s="3" t="s">
         <v>80</v>
       </c>
+      <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
-      <c r="W33" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="X33" s="3"/>
+      <c r="V33" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="W33" s="3"/>
+      <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
-      <c r="Z33" s="1"/>
-      <c r="AD33" s="1"/>
-    </row>
-    <row r="34" spans="2:30" ht="66" x14ac:dyDescent="0.7">
+      <c r="AC33" s="1"/>
+    </row>
+    <row r="34" spans="2:29" ht="66" x14ac:dyDescent="0.7">
       <c r="B34" s="3">
         <v>2006</v>
       </c>
@@ -3981,40 +3926,37 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="L34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="M34" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>212</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N34" s="3"/>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3" t="s">
+      <c r="U34" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="W34" s="3"/>
-      <c r="X34" s="3" t="s">
+      <c r="V34" s="3"/>
+      <c r="W34" s="3" t="s">
         <v>100</v>
       </c>
+      <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
-      <c r="Z34" s="1"/>
-      <c r="AD34" s="1"/>
-    </row>
-    <row r="35" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AC34" s="1"/>
+    </row>
+    <row r="35" spans="2:29" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B35" s="3">
         <v>2007</v>
       </c>
@@ -4036,30 +3978,29 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3" t="s">
+      <c r="U35" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="W35" s="3"/>
-      <c r="X35" s="3" t="s">
-        <v>126</v>
-      </c>
+      <c r="V35" s="3"/>
+      <c r="W35" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
-      <c r="Z35" s="1"/>
-      <c r="AD35" s="1"/>
-    </row>
-    <row r="36" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+      <c r="AC35" s="1"/>
+    </row>
+    <row r="36" spans="2:29" ht="33" x14ac:dyDescent="0.7">
       <c r="B36" s="3">
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4074,19 +4015,18 @@
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3" t="s">
+      <c r="U36" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="W36" s="3"/>
-      <c r="X36" s="3" t="s">
-        <v>181</v>
-      </c>
+      <c r="V36" s="3"/>
+      <c r="W36" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
-      <c r="Z36" s="1"/>
-      <c r="AD36" s="1"/>
-    </row>
-    <row r="37" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC36" s="1"/>
+    </row>
+    <row r="37" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B37" s="3">
         <v>2009</v>
       </c>
@@ -4109,16 +4049,15 @@
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
-      <c r="W37" s="3" t="s">
+      <c r="V37" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="X37" s="3"/>
+      <c r="W37" s="3"/>
+      <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
-      <c r="Z37" s="1"/>
-      <c r="AD37" s="1"/>
-    </row>
-    <row r="38" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AC37" s="1"/>
+    </row>
+    <row r="38" spans="2:29" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B38" s="3">
         <v>2010</v>
       </c>
@@ -4130,31 +4069,30 @@
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3" t="s">
+      <c r="K38" s="3" t="s">
         <v>64</v>
       </c>
+      <c r="L38" s="3"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
-      <c r="P38" s="3"/>
-      <c r="Q38" s="3" t="s">
+      <c r="P38" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
-      <c r="V38" s="3"/>
-      <c r="W38" s="3" t="s">
+      <c r="V38" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="X38" s="3"/>
+      <c r="W38" s="3"/>
+      <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
-      <c r="Z38" s="1"/>
-      <c r="AD38" s="1"/>
-    </row>
-    <row r="39" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+      <c r="AC38" s="1"/>
+    </row>
+    <row r="39" spans="2:29" ht="33" x14ac:dyDescent="0.7">
       <c r="B39" s="3">
         <v>2011</v>
       </c>
@@ -4162,7 +4100,7 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>96</v>
@@ -4172,43 +4110,42 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3" t="s">
+      <c r="M39" s="3" t="s">
         <v>98</v>
       </c>
+      <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-      <c r="R39" s="3"/>
-      <c r="S39" s="3" t="s">
+      <c r="R39" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3" t="s">
-        <v>128</v>
-      </c>
+      <c r="W39" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
-      <c r="Z39" s="1"/>
-      <c r="AD39" s="1"/>
-    </row>
-    <row r="40" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AC39" s="1"/>
+    </row>
+    <row r="40" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B40" s="3">
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4217,10 +4154,10 @@
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3" t="s">
+      <c r="L40" s="3" t="s">
         <v>85</v>
       </c>
+      <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
@@ -4228,70 +4165,66 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
+      <c r="U40" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="V40" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W40" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="X40" s="3"/>
+        <v>175</v>
+      </c>
+      <c r="W40" s="3"/>
+      <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
-      <c r="Z40" s="1"/>
-      <c r="AD40" s="1"/>
-    </row>
-    <row r="41" spans="2:30" ht="99" x14ac:dyDescent="0.7">
+      <c r="AC40" s="1"/>
+    </row>
+    <row r="41" spans="2:29" ht="99" x14ac:dyDescent="0.7">
       <c r="B41" s="3">
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="3" t="s">
-        <v>158</v>
-      </c>
+      <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
-      <c r="R41" s="3"/>
-      <c r="S41" s="3" t="s">
-        <v>203</v>
-      </c>
+      <c r="R41" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="S41" s="3"/>
       <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
+      <c r="U41" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="V41" s="3" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>189</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
-      <c r="Z41" s="1"/>
-      <c r="AD41" s="1"/>
-    </row>
-    <row r="42" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+      <c r="AC41" s="1"/>
+    </row>
+    <row r="42" spans="2:29" ht="33" x14ac:dyDescent="0.7">
       <c r="B42" s="3">
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4313,23 +4246,22 @@
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
-      <c r="V42" s="3"/>
+      <c r="V42" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="W42" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="X42" s="3" t="s">
-        <v>177</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
-      <c r="Z42" s="1"/>
-      <c r="AD42" s="1"/>
-    </row>
-    <row r="43" spans="2:30" ht="66" x14ac:dyDescent="0.7">
+      <c r="AC42" s="1"/>
+    </row>
+    <row r="43" spans="2:29" ht="66" x14ac:dyDescent="0.7">
       <c r="B43" s="3">
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4342,34 +4274,33 @@
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3" t="s">
+      <c r="M43" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
-      <c r="U43" s="3"/>
-      <c r="V43" s="3" t="s">
+      <c r="U43" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="W43" s="3"/>
-      <c r="X43" s="3" t="s">
-        <v>202</v>
-      </c>
+      <c r="V43" s="3"/>
+      <c r="W43" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
-      <c r="Z43" s="1"/>
-      <c r="AD43" s="1"/>
-    </row>
-    <row r="44" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AC43" s="1"/>
+    </row>
+    <row r="44" spans="2:29" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B44" s="3">
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>22</v>
@@ -4393,23 +4324,22 @@
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
-      <c r="V44" s="3"/>
+      <c r="V44" s="3" t="s">
+        <v>111</v>
+      </c>
       <c r="W44" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="X44" s="3" t="s">
-        <v>211</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
-      <c r="Z44" s="1"/>
-      <c r="AD44" s="1"/>
-    </row>
-    <row r="45" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+      <c r="AC44" s="1"/>
+    </row>
+    <row r="45" spans="2:29" ht="33" x14ac:dyDescent="0.7">
       <c r="B45" s="3">
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4420,55 +4350,54 @@
         <v>95</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O45" s="3"/>
-      <c r="P45" s="3" t="s">
-        <v>178</v>
-      </c>
+      <c r="M45" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
-      <c r="S45" s="3"/>
-      <c r="T45" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="U45" s="3"/>
+      <c r="S45" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="T45" s="3"/>
+      <c r="U45" s="3" t="s">
+        <v>101</v>
+      </c>
       <c r="V45" s="3" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>110</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
-      <c r="Z45" s="1"/>
-      <c r="AD45" s="1"/>
-    </row>
-    <row r="46" spans="2:30" ht="115.5" x14ac:dyDescent="0.7">
+      <c r="AC45" s="1"/>
+    </row>
+    <row r="46" spans="2:29" ht="115.5" x14ac:dyDescent="0.7">
       <c r="B46" s="3">
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4476,44 +4405,43 @@
         <v>27</v>
       </c>
       <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
+      <c r="K46" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="L46" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>191</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="M46" s="3"/>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
-      <c r="Q46" s="3"/>
-      <c r="R46" s="3" t="s">
+      <c r="Q46" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S46" s="3"/>
-      <c r="T46" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="U46" s="3"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="T46" s="3"/>
+      <c r="U46" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="V46" s="3" t="s">
-        <v>91</v>
+        <v>220</v>
       </c>
       <c r="W46" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>222</v>
-      </c>
+      <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
-      <c r="Z46" s="1"/>
-      <c r="AD46" s="1"/>
-    </row>
-    <row r="47" spans="2:30" ht="99" x14ac:dyDescent="0.7">
+      <c r="AC46" s="1"/>
+    </row>
+    <row r="47" spans="2:29" ht="99" x14ac:dyDescent="0.7">
       <c r="B47" s="3">
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4528,18 +4456,18 @@
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="K47" s="3"/>
+        <v>167</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="L47" s="3" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="N47" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="N47" s="3"/>
       <c r="O47" s="3"/>
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
@@ -4547,18 +4475,17 @@
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
-      <c r="V47" s="3"/>
+      <c r="V47" s="3" t="s">
+        <v>141</v>
+      </c>
       <c r="W47" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>184</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
-      <c r="Z47" s="1"/>
-      <c r="AD47" s="1"/>
-    </row>
-    <row r="48" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AC47" s="1"/>
+    </row>
+    <row r="48" spans="2:29" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B48" s="3">
         <v>2020</v>
       </c>
@@ -4575,32 +4502,31 @@
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3" t="s">
+      <c r="L48" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="M48" s="3"/>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
-      <c r="R48" s="3"/>
-      <c r="S48" s="3" t="s">
+      <c r="R48" s="3" t="s">
         <v>79</v>
       </c>
+      <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
-      <c r="V48" s="3"/>
+      <c r="V48" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="W48" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="X48" s="3" t="s">
-        <v>182</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
-      <c r="Z48" s="1"/>
-      <c r="AD48" s="1"/>
-    </row>
-    <row r="49" spans="2:30" ht="66" x14ac:dyDescent="0.7">
+      <c r="AC48" s="1"/>
+    </row>
+    <row r="49" spans="2:29" ht="66" x14ac:dyDescent="0.7">
       <c r="B49" s="3">
         <v>2021</v>
       </c>
@@ -4608,16 +4534,16 @@
         <v>47</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4631,45 +4557,44 @@
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
+      <c r="P49" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="Q49" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R49" s="3" t="s">
         <v>62</v>
       </c>
+      <c r="R49" s="3"/>
       <c r="S49" s="3"/>
-      <c r="T49" s="3"/>
-      <c r="U49" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="V49" s="3"/>
-      <c r="W49" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="X49" s="3"/>
+      <c r="T49" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="U49" s="3"/>
+      <c r="V49" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="W49" s="3"/>
+      <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
-      <c r="Z49" s="1"/>
-      <c r="AD49" s="1"/>
-    </row>
-    <row r="50" spans="2:30" ht="132" x14ac:dyDescent="0.7">
+      <c r="AC49" s="1"/>
+    </row>
+    <row r="50" spans="2:29" ht="132" x14ac:dyDescent="0.7">
       <c r="B50" s="3">
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>20</v>
@@ -4679,36 +4604,33 @@
         <v>69</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="L50" s="3" t="s">
         <v>67</v>
       </c>
+      <c r="L50" s="3"/>
       <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3" t="s">
-        <v>162</v>
-      </c>
+      <c r="N50" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="O50" s="3"/>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
-      <c r="T50" s="3"/>
-      <c r="U50" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="V50" s="3"/>
+      <c r="T50" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3" t="s">
+        <v>136</v>
+      </c>
       <c r="W50" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="X50" s="3" t="s">
-        <v>161</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
-      <c r="Z50" s="1"/>
-      <c r="AD50" s="1"/>
-    </row>
-    <row r="51" spans="2:30" ht="99" x14ac:dyDescent="0.7">
+      <c r="AC50" s="1"/>
+    </row>
+    <row r="51" spans="2:29" ht="99" x14ac:dyDescent="0.7">
       <c r="B51" s="3">
         <v>2023</v>
       </c>
@@ -4716,59 +4638,58 @@
         <v>23</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3" t="s">
+      <c r="K51" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="N51" s="3" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="P51" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q51" s="3"/>
-      <c r="R51" s="3" t="s">
-        <v>127</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="R51" s="3"/>
       <c r="S51" s="3"/>
-      <c r="T51" s="3"/>
-      <c r="U51" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="V51" s="3"/>
+      <c r="T51" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="U51" s="3"/>
+      <c r="V51" s="3" t="s">
+        <v>200</v>
+      </c>
       <c r="W51" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="X51" s="3" t="s">
-        <v>215</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
-      <c r="Z51" s="1"/>
-      <c r="AD51" s="1"/>
-    </row>
-    <row r="52" spans="2:30" ht="99" x14ac:dyDescent="0.7">
+      <c r="AC51" s="1"/>
+    </row>
+    <row r="52" spans="2:29" ht="99" x14ac:dyDescent="0.7">
       <c r="B52" s="3">
         <v>2024</v>
       </c>
@@ -4782,203 +4703,191 @@
         <v>42</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>71</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="N52" s="3"/>
-      <c r="O52" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="P52" s="3"/>
-      <c r="Q52" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3" t="s">
         <v>57</v>
       </c>
+      <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
-      <c r="S52" s="3"/>
-      <c r="T52" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="S52" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="T52" s="3"/>
       <c r="U52" s="3"/>
-      <c r="V52" s="3"/>
-      <c r="W52" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="X52" s="3"/>
+      <c r="V52" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="W52" s="3"/>
+      <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
-      <c r="Z52" s="1"/>
-      <c r="AD52" s="1"/>
-    </row>
-    <row r="53" spans="2:30" ht="115.5" x14ac:dyDescent="0.7">
+      <c r="AC52" s="1"/>
+    </row>
+    <row r="53" spans="2:29" ht="115.5" x14ac:dyDescent="0.7">
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>93</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>206</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
+      <c r="N53" s="3" t="s">
+        <v>162</v>
+      </c>
       <c r="O53" s="3" t="s">
-        <v>163</v>
+        <v>212</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q53" s="3" t="s">
-        <v>217</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
-      <c r="S53" s="3"/>
+      <c r="S53" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="T53" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="U53" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="V53" s="3"/>
-      <c r="W53" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="X53" s="3"/>
+        <v>164</v>
+      </c>
+      <c r="U53" s="3"/>
+      <c r="V53" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="W53" s="3"/>
+      <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
-      <c r="Z53" s="1"/>
-      <c r="AD53" s="1"/>
-    </row>
-    <row r="54" spans="2:30" ht="66" x14ac:dyDescent="0.7">
+      <c r="AC53" s="1"/>
+    </row>
+    <row r="54" spans="2:29" ht="66" x14ac:dyDescent="0.7">
       <c r="B54" s="3">
         <v>2026</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J54" s="3"/>
-      <c r="K54" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="L54" s="3"/>
-      <c r="M54" s="3" t="s">
-        <v>185</v>
-      </c>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
-      <c r="P54" s="3"/>
-      <c r="Q54" s="3" t="s">
-        <v>183</v>
-      </c>
+      <c r="P54" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
-      <c r="V54" s="3"/>
-      <c r="W54" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="X54" s="3"/>
+      <c r="V54" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="W54" s="3"/>
+      <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
-      <c r="Z54" s="1"/>
-      <c r="AD54" s="1"/>
-    </row>
-    <row r="55" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AC54" s="1"/>
+    </row>
+    <row r="55" spans="2:29" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J55" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="K55" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="O55" s="3"/>
-      <c r="P55" s="3" t="s">
-        <v>152</v>
-      </c>
+      <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-      <c r="V55" s="3"/>
-      <c r="W55" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="X55" s="3"/>
+      <c r="V55" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="W55" s="3"/>
+      <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
-      <c r="Z55" s="1"/>
-      <c r="AD55" s="1"/>
-    </row>
-    <row r="56" spans="2:30" x14ac:dyDescent="0.7">
+      <c r="AC55" s="1"/>
+    </row>
+    <row r="56" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -5003,11 +4912,10 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-      <c r="X56" s="3"/>
+      <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
-      <c r="Z56" s="1"/>
-      <c r="AB56"/>
-      <c r="AD56" s="1"/>
+      <c r="AA56"/>
+      <c r="AC56" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -5017,4 +4925,371 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E1BF3CE-E2E1-4863-A741-2B6FD3C7028A}">
+  <dimension ref="A1:B56"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="1" max="1" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6875" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A2" s="1" cm="1">
+        <f t="array" ref="A2">SUMPRODUCT(
+  IF(LEN(A5:A1001)=0, 0,
+     LEN(A5:A1001) - LEN(SUBSTITUTE(A5:A1001, CHAR(10), "")) + 1
+  )
+)</f>
+        <v>11</v>
+      </c>
+      <c r="B2" s="1">
+        <f>SUM(C2:RX2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A3" s="1"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A4" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A34" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B34" s="3">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A41" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B41" s="3">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A50" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B50" s="3">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A52" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B52" s="3">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A53" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B53" s="3">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="A54" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B54" s="3">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="A55" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21200964-921D-4BA6-B562-15FE9DC869ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3607A437-C2AF-47F4-9BB2-107009A32924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="231">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1760,6 +1760,14 @@
     <rPh sb="8" eb="10">
       <t>シンノ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NENE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Anna</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1845,6 +1853,26 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="24">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Noto Serif JP SemiBold"/>
+        <family val="1"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1967,26 +1995,6 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2355,22 +2363,22 @@
     <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="18"/>
     <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリゴ" dataDxfId="17"/>
     <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ" dataDxfId="16"/>
-    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="14"/>
-    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="13"/>
-    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="12"/>
-    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="11"/>
-    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="10"/>
-    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="8"/>
-    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="7"/>
-    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="3"/>
-    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="15"/>
+    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="0"/>
+    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="14"/>
+    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="13"/>
+    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="11"/>
+    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="10"/>
+    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="9"/>
+    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="8"/>
+    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="4"/>
+    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2693,7 +2701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4F8F56-06F6-4E1D-8D81-5A485042419D}">
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AD56"/>
   <sheetFormatPr defaultColWidth="27.3125" defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="1.875" style="1" bestFit="1" customWidth="1"/>
@@ -2702,54 +2710,55 @@
     <col min="4" max="4" width="12.3125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.6875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.8125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.6875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.4375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28.375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.3125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.9375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="30.375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21.3125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="30.25" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.1875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="30.0625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="27.3125" style="1"/>
-    <col min="30" max="16384" width="27.3125" style="1"/>
+    <col min="7" max="7" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.8125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.4375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.3125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.5625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.9375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="30.375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.3125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.1875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="30.0625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="27.3125" style="1"/>
+    <col min="31" max="16384" width="27.3125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="Q1" s="1"/>
       <c r="S1" s="1"/>
-      <c r="V1" s="1"/>
+      <c r="T1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="AC1" s="1"/>
-    </row>
-    <row r="2" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z1" s="1"/>
+      <c r="AD1" s="1"/>
+    </row>
+    <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2793,153 +2802,155 @@
       </c>
       <c r="H2" s="1" cm="1">
         <f t="array" ref="H2">SUMPRODUCT(
-  IF(LEN(H5:H1001)=0, 0,
-     LEN(H5:H1001) - LEN(SUBSTITUTE(H5:H1001, CHAR(10), "")) + 1
-  )
-)</f>
-        <v>13</v>
-      </c>
-      <c r="I2" s="1" cm="1">
-        <f t="array" ref="I2">SUMPRODUCT(
   IF(LEN(I5:I1001)=0, 0,
      LEN(I5:I1001) - LEN(SUBSTITUTE(I5:I1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>12</v>
-      </c>
-      <c r="J2" s="1" cm="1">
-        <f t="array" ref="J2">SUMPRODUCT(
+        <v>11</v>
+      </c>
+      <c r="I2" s="1" cm="1">
+        <f t="array" ref="I2">SUMPRODUCT(
   IF(LEN(J5:J1001)=0, 0,
      LEN(J5:J1001) - LEN(SUBSTITUTE(J5:J1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>11</v>
       </c>
-      <c r="K2" s="1" cm="1">
-        <f t="array" ref="K2">SUMPRODUCT(
+      <c r="J2" s="1" cm="1">
+        <f t="array" ref="J2">SUMPRODUCT(
   IF(LEN(K5:K1001)=0, 0,
      LEN(K5:K1001) - LEN(SUBSTITUTE(K5:K1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>10</v>
       </c>
-      <c r="L2" s="1" cm="1">
-        <f t="array" ref="L2">SUMPRODUCT(
+      <c r="K2" s="1" cm="1">
+        <f t="array" ref="K2">SUMPRODUCT(
   IF(LEN(L5:L1001)=0, 0,
      LEN(L5:L1001) - LEN(SUBSTITUTE(L5:L1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>10</v>
       </c>
-      <c r="M2" s="1" cm="1">
-        <f t="array" ref="M2">SUMPRODUCT(
+      <c r="L2" s="1" cm="1">
+        <f t="array" ref="L2">SUMPRODUCT(
   IF(LEN(M5:M1001)=0, 0,
      LEN(M5:M1001) - LEN(SUBSTITUTE(M5:M1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>11</v>
       </c>
-      <c r="N2" s="1" cm="1">
-        <f t="array" ref="N2">SUMPRODUCT(
+      <c r="M2" s="1" cm="1">
+        <f t="array" ref="M2">SUMPRODUCT(
   IF(LEN(N5:N1001)=0, 0,
      LEN(N5:N1001) - LEN(SUBSTITUTE(N5:N1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>9</v>
       </c>
-      <c r="O2" s="1" cm="1">
-        <f t="array" ref="O2">SUMPRODUCT(
+      <c r="N2" s="1" cm="1">
+        <f t="array" ref="N2">SUMPRODUCT(
   IF(LEN(O5:O1001)=0, 0,
      LEN(O5:O1001) - LEN(SUBSTITUTE(O5:O1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>7</v>
       </c>
-      <c r="P2" s="1" cm="1">
-        <f t="array" ref="P2">SUMPRODUCT(
+      <c r="O2" s="1" cm="1">
+        <f t="array" ref="O2">SUMPRODUCT(
   IF(LEN(P5:P1001)=0, 0,
      LEN(P5:P1001) - LEN(SUBSTITUTE(P5:P1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>6</v>
       </c>
-      <c r="Q2" s="1" cm="1">
-        <f t="array" ref="Q2">SUMPRODUCT(
+      <c r="P2" s="1" cm="1">
+        <f t="array" ref="P2">SUMPRODUCT(
   IF(LEN(Q5:Q1001)=0, 0,
      LEN(Q5:Q1001) - LEN(SUBSTITUTE(Q5:Q1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="R2" s="1" cm="1">
-        <f t="array" ref="R2">SUMPRODUCT(
+      <c r="Q2" s="1" cm="1">
+        <f t="array" ref="Q2">SUMPRODUCT(
   IF(LEN(R5:R1001)=0, 0,
      LEN(R5:R1001) - LEN(SUBSTITUTE(R5:R1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="S2" s="1" cm="1">
-        <f t="array" ref="S2">SUMPRODUCT(
+      <c r="R2" s="1" cm="1">
+        <f t="array" ref="R2">SUMPRODUCT(
   IF(LEN(S5:S1001)=0, 0,
      LEN(S5:S1001) - LEN(SUBSTITUTE(S5:S1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="T2" s="1" cm="1">
-        <f t="array" ref="T2">SUMPRODUCT(
+      <c r="S2" s="1" cm="1">
+        <f t="array" ref="S2">SUMPRODUCT(
   IF(LEN(T5:T1001)=0, 0,
      LEN(T5:T1001) - LEN(SUBSTITUTE(T5:T1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="U2" s="1" cm="1">
-        <f t="array" ref="U2">SUMPRODUCT(
+      <c r="T2" s="1" cm="1">
+        <f t="array" ref="T2">SUMPRODUCT(
   IF(LEN(U5:U1001)=0, 0,
      LEN(U5:U1001) - LEN(SUBSTITUTE(U5:U1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>8</v>
       </c>
-      <c r="V2" s="1" cm="1">
-        <f t="array" ref="V2">SUMPRODUCT(
+      <c r="U2" s="1" cm="1">
+        <f t="array" ref="U2">SUMPRODUCT(
   IF(LEN(V5:V1001)=0, 0,
      LEN(V5:V1001) - LEN(SUBSTITUTE(V5:V1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>53</v>
       </c>
-      <c r="W2" s="1" cm="1">
-        <f t="array" ref="W2">SUMPRODUCT(
+      <c r="V2" s="1" cm="1">
+        <f t="array" ref="V2">SUMPRODUCT(
   IF(LEN(W5:W1001)=0, 0,
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>51</v>
       </c>
+      <c r="W2" s="1" cm="1">
+        <f t="array" ref="W2">SUMPRODUCT(
+  IF(LEN(X5:X1001)=0, 0,
+     LEN(X5:X1001) - LEN(SUBSTITUTE(X5:X1001, CHAR(10), "")) + 1
+  )
+)</f>
+        <v>0</v>
+      </c>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
-      <c r="AC2" s="1"/>
-    </row>
-    <row r="3" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z2" s="1"/>
+      <c r="AD2" s="1"/>
+    </row>
+    <row r="3" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
-      <c r="R3" s="1"/>
+      <c r="Q3" s="1"/>
       <c r="S3" s="1"/>
-      <c r="V3" s="1"/>
+      <c r="T3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
-      <c r="AC3" s="1"/>
-    </row>
-    <row r="4" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z3" s="1"/>
+      <c r="AD3" s="1"/>
+    </row>
+    <row r="4" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
@@ -2959,10 +2970,10 @@
         <v>72</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>45</v>
@@ -3008,9 +3019,10 @@
       </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
-      <c r="AC4" s="1"/>
-    </row>
-    <row r="5" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z4" s="1"/>
+      <c r="AD4" s="1"/>
+    </row>
+    <row r="5" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B5" s="3">
         <v>1977</v>
       </c>
@@ -3019,10 +3031,10 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -3039,9 +3051,10 @@
       <c r="W5" s="3"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
-      <c r="AC5" s="1"/>
-    </row>
-    <row r="6" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z5" s="1"/>
+      <c r="AD5" s="1"/>
+    </row>
+    <row r="6" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B6" s="3">
         <v>1978</v>
       </c>
@@ -3068,9 +3081,10 @@
       <c r="W6" s="3"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
-      <c r="AC6" s="1"/>
-    </row>
-    <row r="7" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z6" s="1"/>
+      <c r="AD6" s="1"/>
+    </row>
+    <row r="7" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B7" s="3">
         <v>1979</v>
       </c>
@@ -3097,9 +3111,10 @@
       <c r="W7" s="3"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
-      <c r="AC7" s="1"/>
-    </row>
-    <row r="8" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z7" s="1"/>
+      <c r="AD7" s="1"/>
+    </row>
+    <row r="8" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B8" s="3">
         <v>1980</v>
       </c>
@@ -3108,10 +3123,10 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -3130,9 +3145,10 @@
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
-      <c r="AC8" s="1"/>
-    </row>
-    <row r="9" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z8" s="1"/>
+      <c r="AD8" s="1"/>
+    </row>
+    <row r="9" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B9" s="3">
         <v>1981</v>
       </c>
@@ -3159,9 +3175,10 @@
       <c r="W9" s="3"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
-      <c r="AC9" s="1"/>
-    </row>
-    <row r="10" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z9" s="1"/>
+      <c r="AD9" s="1"/>
+    </row>
+    <row r="10" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B10" s="3">
         <v>1982</v>
       </c>
@@ -3188,9 +3205,10 @@
       <c r="W10" s="3"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
-      <c r="AC10" s="1"/>
-    </row>
-    <row r="11" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z10" s="1"/>
+      <c r="AD10" s="1"/>
+    </row>
+    <row r="11" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B11" s="3">
         <v>1983</v>
       </c>
@@ -3217,9 +3235,10 @@
       <c r="W11" s="3"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
-      <c r="AC11" s="1"/>
-    </row>
-    <row r="12" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z11" s="1"/>
+      <c r="AD11" s="1"/>
+    </row>
+    <row r="12" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B12" s="3">
         <v>1984</v>
       </c>
@@ -3246,9 +3265,10 @@
       <c r="W12" s="3"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
-      <c r="AC12" s="1"/>
-    </row>
-    <row r="13" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z12" s="1"/>
+      <c r="AD12" s="1"/>
+    </row>
+    <row r="13" spans="1:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B13" s="3">
         <v>1985</v>
       </c>
@@ -3277,9 +3297,10 @@
       <c r="W13" s="3"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
-      <c r="AC13" s="1"/>
-    </row>
-    <row r="14" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z13" s="1"/>
+      <c r="AD13" s="1"/>
+    </row>
+    <row r="14" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B14" s="3">
         <v>1986</v>
       </c>
@@ -3312,9 +3333,10 @@
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
-      <c r="AC14" s="1"/>
-    </row>
-    <row r="15" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z14" s="1"/>
+      <c r="AD14" s="1"/>
+    </row>
+    <row r="15" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B15" s="3">
         <v>1987</v>
       </c>
@@ -3343,9 +3365,10 @@
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
-      <c r="AC15" s="1"/>
-    </row>
-    <row r="16" spans="1:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z15" s="1"/>
+      <c r="AD15" s="1"/>
+    </row>
+    <row r="16" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B16" s="3">
         <v>1988</v>
       </c>
@@ -3354,10 +3377,10 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="3"/>
+      <c r="I16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -3376,9 +3399,10 @@
       <c r="W16" s="3"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
-      <c r="AC16" s="1"/>
-    </row>
-    <row r="17" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z16" s="1"/>
+      <c r="AD16" s="1"/>
+    </row>
+    <row r="17" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B17" s="3">
         <v>1989</v>
       </c>
@@ -3409,9 +3433,10 @@
       </c>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
-      <c r="AC17" s="1"/>
-    </row>
-    <row r="18" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z17" s="1"/>
+      <c r="AD17" s="1"/>
+    </row>
+    <row r="18" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B18" s="3">
         <v>1990</v>
       </c>
@@ -3438,9 +3463,10 @@
       <c r="W18" s="3"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
-      <c r="AC18" s="1"/>
-    </row>
-    <row r="19" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z18" s="1"/>
+      <c r="AD18" s="1"/>
+    </row>
+    <row r="19" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B19" s="3">
         <v>1991</v>
       </c>
@@ -3467,9 +3493,10 @@
       <c r="W19" s="3"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
-      <c r="AC19" s="1"/>
-    </row>
-    <row r="20" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z19" s="1"/>
+      <c r="AD19" s="1"/>
+    </row>
+    <row r="20" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B20" s="3">
         <v>1992</v>
       </c>
@@ -3496,9 +3523,10 @@
       <c r="W20" s="3"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
-      <c r="AC20" s="1"/>
-    </row>
-    <row r="21" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z20" s="1"/>
+      <c r="AD20" s="1"/>
+    </row>
+    <row r="21" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B21" s="3">
         <v>1993</v>
       </c>
@@ -3525,9 +3553,10 @@
       <c r="W21" s="3"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
-      <c r="AC21" s="1"/>
-    </row>
-    <row r="22" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z21" s="1"/>
+      <c r="AD21" s="1"/>
+    </row>
+    <row r="22" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B22" s="3">
         <v>1994</v>
       </c>
@@ -3554,9 +3583,10 @@
       <c r="W22" s="3"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
-      <c r="AC22" s="1"/>
-    </row>
-    <row r="23" spans="2:29" ht="33" x14ac:dyDescent="0.7">
+      <c r="Z22" s="1"/>
+      <c r="AD22" s="1"/>
+    </row>
+    <row r="23" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B23" s="3">
         <v>1995</v>
       </c>
@@ -3589,9 +3619,10 @@
       </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
-      <c r="AC23" s="1"/>
-    </row>
-    <row r="24" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z23" s="1"/>
+      <c r="AD23" s="1"/>
+    </row>
+    <row r="24" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B24" s="3">
         <v>1996</v>
       </c>
@@ -3620,9 +3651,10 @@
       </c>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
-      <c r="AC24" s="1"/>
-    </row>
-    <row r="25" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z24" s="1"/>
+      <c r="AD24" s="1"/>
+    </row>
+    <row r="25" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B25" s="3">
         <v>1997</v>
       </c>
@@ -3653,9 +3685,10 @@
       </c>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
-      <c r="AC25" s="1"/>
-    </row>
-    <row r="26" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z25" s="1"/>
+      <c r="AD25" s="1"/>
+    </row>
+    <row r="26" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B26" s="3">
         <v>1998</v>
       </c>
@@ -3686,9 +3719,10 @@
       </c>
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
-      <c r="AC26" s="1"/>
-    </row>
-    <row r="27" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z26" s="1"/>
+      <c r="AD26" s="1"/>
+    </row>
+    <row r="27" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B27" s="3">
         <v>1999</v>
       </c>
@@ -3719,9 +3753,10 @@
       <c r="W27" s="3"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
-      <c r="AC27" s="1"/>
-    </row>
-    <row r="28" spans="2:29" ht="33" x14ac:dyDescent="0.7">
+      <c r="Z27" s="1"/>
+      <c r="AD27" s="1"/>
+    </row>
+    <row r="28" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B28" s="3">
         <v>2000</v>
       </c>
@@ -3754,9 +3789,10 @@
       </c>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
-      <c r="AC28" s="1"/>
-    </row>
-    <row r="29" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z28" s="1"/>
+      <c r="AD28" s="1"/>
+    </row>
+    <row r="29" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B29" s="3">
         <v>2001</v>
       </c>
@@ -3765,10 +3801,10 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="3" t="s">
+      <c r="H29" s="3"/>
+      <c r="I29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
@@ -3787,9 +3823,10 @@
       <c r="W29" s="3"/>
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
-      <c r="AC29" s="1"/>
-    </row>
-    <row r="30" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z29" s="1"/>
+      <c r="AD29" s="1"/>
+    </row>
+    <row r="30" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B30" s="3">
         <v>2002</v>
       </c>
@@ -3818,9 +3855,10 @@
       <c r="W30" s="3"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
-      <c r="AC30" s="1"/>
-    </row>
-    <row r="31" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z30" s="1"/>
+      <c r="AD30" s="1"/>
+    </row>
+    <row r="31" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B31" s="3">
         <v>2003</v>
       </c>
@@ -3847,9 +3885,10 @@
       <c r="W31" s="3"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
-      <c r="AC31" s="1"/>
-    </row>
-    <row r="32" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z31" s="1"/>
+      <c r="AD31" s="1"/>
+    </row>
+    <row r="32" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B32" s="3">
         <v>2004</v>
       </c>
@@ -3882,9 +3921,10 @@
       </c>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
-      <c r="AC32" s="1"/>
-    </row>
-    <row r="33" spans="2:29" ht="33" x14ac:dyDescent="0.7">
+      <c r="Z32" s="1"/>
+      <c r="AD32" s="1"/>
+    </row>
+    <row r="33" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B33" s="3">
         <v>2005</v>
       </c>
@@ -3915,9 +3955,10 @@
       <c r="W33" s="3"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
-      <c r="AC33" s="1"/>
-    </row>
-    <row r="34" spans="2:29" ht="66" x14ac:dyDescent="0.7">
+      <c r="Z33" s="1"/>
+      <c r="AD33" s="1"/>
+    </row>
+    <row r="34" spans="2:30" ht="66" x14ac:dyDescent="0.7">
       <c r="B34" s="3">
         <v>2006</v>
       </c>
@@ -3954,9 +3995,10 @@
       </c>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
-      <c r="AC34" s="1"/>
-    </row>
-    <row r="35" spans="2:29" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="Z34" s="1"/>
+      <c r="AD34" s="1"/>
+    </row>
+    <row r="35" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B35" s="3">
         <v>2007</v>
       </c>
@@ -3987,9 +4029,10 @@
       </c>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
-      <c r="AC35" s="1"/>
-    </row>
-    <row r="36" spans="2:29" ht="33" x14ac:dyDescent="0.7">
+      <c r="Z35" s="1"/>
+      <c r="AD35" s="1"/>
+    </row>
+    <row r="36" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B36" s="3">
         <v>2008</v>
       </c>
@@ -4024,9 +4067,10 @@
       </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
-      <c r="AC36" s="1"/>
-    </row>
-    <row r="37" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z36" s="1"/>
+      <c r="AD36" s="1"/>
+    </row>
+    <row r="37" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B37" s="3">
         <v>2009</v>
       </c>
@@ -4055,9 +4099,10 @@
       <c r="W37" s="3"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
-      <c r="AC37" s="1"/>
-    </row>
-    <row r="38" spans="2:29" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="Z37" s="1"/>
+      <c r="AD37" s="1"/>
+    </row>
+    <row r="38" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B38" s="3">
         <v>2010</v>
       </c>
@@ -4090,9 +4135,10 @@
       <c r="W38" s="3"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
-      <c r="AC38" s="1"/>
-    </row>
-    <row r="39" spans="2:29" ht="33" x14ac:dyDescent="0.7">
+      <c r="Z38" s="1"/>
+      <c r="AD38" s="1"/>
+    </row>
+    <row r="39" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B39" s="3">
         <v>2011</v>
       </c>
@@ -4129,9 +4175,10 @@
       </c>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
-      <c r="AC39" s="1"/>
-    </row>
-    <row r="40" spans="2:29" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="Z39" s="1"/>
+      <c r="AD39" s="1"/>
+    </row>
+    <row r="40" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B40" s="3">
         <v>2012</v>
       </c>
@@ -4148,10 +4195,10 @@
         <v>107</v>
       </c>
       <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3" t="s">
+      <c r="H40" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3" t="s">
@@ -4174,9 +4221,10 @@
       <c r="W40" s="3"/>
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
-      <c r="AC40" s="1"/>
-    </row>
-    <row r="41" spans="2:29" ht="99" x14ac:dyDescent="0.7">
+      <c r="Z40" s="1"/>
+      <c r="AD40" s="1"/>
+    </row>
+    <row r="41" spans="2:30" ht="99" x14ac:dyDescent="0.7">
       <c r="B41" s="3">
         <v>2013</v>
       </c>
@@ -4217,9 +4265,10 @@
       </c>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
-      <c r="AC41" s="1"/>
-    </row>
-    <row r="42" spans="2:29" ht="33" x14ac:dyDescent="0.7">
+      <c r="Z41" s="1"/>
+      <c r="AD41" s="1"/>
+    </row>
+    <row r="42" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B42" s="3">
         <v>2014</v>
       </c>
@@ -4254,9 +4303,10 @@
       </c>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
-      <c r="AC42" s="1"/>
-    </row>
-    <row r="43" spans="2:29" ht="66" x14ac:dyDescent="0.7">
+      <c r="Z42" s="1"/>
+      <c r="AD42" s="1"/>
+    </row>
+    <row r="43" spans="2:30" ht="66" x14ac:dyDescent="0.7">
       <c r="B43" s="3">
         <v>2015</v>
       </c>
@@ -4293,9 +4343,10 @@
       </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
-      <c r="AC43" s="1"/>
-    </row>
-    <row r="44" spans="2:29" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="Z43" s="1"/>
+      <c r="AD43" s="1"/>
+    </row>
+    <row r="44" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B44" s="3">
         <v>2016</v>
       </c>
@@ -4308,10 +4359,10 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3" t="s">
+      <c r="H44" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="I44" s="3"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
@@ -4332,9 +4383,10 @@
       </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
-      <c r="AC44" s="1"/>
-    </row>
-    <row r="45" spans="2:29" ht="33" x14ac:dyDescent="0.7">
+      <c r="Z44" s="1"/>
+      <c r="AD44" s="1"/>
+    </row>
+    <row r="45" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B45" s="3">
         <v>2017</v>
       </c>
@@ -4349,10 +4401,10 @@
       <c r="G45" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="H45" s="3"/>
+      <c r="I45" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="I45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
@@ -4381,9 +4433,10 @@
       </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
-      <c r="AC45" s="1"/>
-    </row>
-    <row r="46" spans="2:29" ht="115.5" x14ac:dyDescent="0.7">
+      <c r="Z45" s="1"/>
+      <c r="AD45" s="1"/>
+    </row>
+    <row r="46" spans="2:30" ht="148.5" x14ac:dyDescent="0.7">
       <c r="B46" s="3">
         <v>2018</v>
       </c>
@@ -4400,10 +4453,10 @@
         <v>219</v>
       </c>
       <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3" t="s">
+      <c r="H46" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="I46" s="3"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
         <v>65</v>
@@ -4434,9 +4487,10 @@
       </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
-      <c r="AC46" s="1"/>
-    </row>
-    <row r="47" spans="2:29" ht="99" x14ac:dyDescent="0.7">
+      <c r="Z46" s="1"/>
+      <c r="AD46" s="1"/>
+    </row>
+    <row r="47" spans="2:30" ht="99" x14ac:dyDescent="0.7">
       <c r="B47" s="3">
         <v>2019</v>
       </c>
@@ -4451,10 +4505,10 @@
       <c r="G47" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H47" s="3"/>
+      <c r="I47" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
         <v>167</v>
       </c>
@@ -4483,9 +4537,10 @@
       </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
-      <c r="AC47" s="1"/>
-    </row>
-    <row r="48" spans="2:29" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="Z47" s="1"/>
+      <c r="AD47" s="1"/>
+    </row>
+    <row r="48" spans="2:30" ht="66" x14ac:dyDescent="0.7">
       <c r="B48" s="3">
         <v>2020</v>
       </c>
@@ -4524,9 +4579,10 @@
       </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
-      <c r="AC48" s="1"/>
-    </row>
-    <row r="49" spans="2:29" ht="66" x14ac:dyDescent="0.7">
+      <c r="Z48" s="1"/>
+      <c r="AD48" s="1"/>
+    </row>
+    <row r="49" spans="2:30" ht="99" x14ac:dyDescent="0.7">
       <c r="B49" s="3">
         <v>2021</v>
       </c>
@@ -4545,10 +4601,10 @@
       <c r="G49" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3" t="s">
+      <c r="H49" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
         <v>70</v>
       </c>
@@ -4575,9 +4631,10 @@
       <c r="W49" s="3"/>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
-      <c r="AC49" s="1"/>
-    </row>
-    <row r="50" spans="2:29" ht="132" x14ac:dyDescent="0.7">
+      <c r="Z49" s="1"/>
+      <c r="AD49" s="1"/>
+    </row>
+    <row r="50" spans="2:30" ht="132" x14ac:dyDescent="0.7">
       <c r="B50" s="3">
         <v>2022</v>
       </c>
@@ -4596,10 +4653,10 @@
       <c r="G50" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H50" s="3" t="s">
+      <c r="H50" s="3"/>
+      <c r="I50" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
         <v>69</v>
       </c>
@@ -4628,9 +4685,10 @@
       </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
-      <c r="AC50" s="1"/>
-    </row>
-    <row r="51" spans="2:29" ht="99" x14ac:dyDescent="0.7">
+      <c r="Z50" s="1"/>
+      <c r="AD50" s="1"/>
+    </row>
+    <row r="51" spans="2:30" ht="99" x14ac:dyDescent="0.7">
       <c r="B51" s="3">
         <v>2023</v>
       </c>
@@ -4649,10 +4707,10 @@
       <c r="G51" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="H51" s="3" t="s">
+      <c r="H51" s="3"/>
+      <c r="I51" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
         <v>46</v>
       </c>
@@ -4687,9 +4745,10 @@
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
-      <c r="AC51" s="1"/>
-    </row>
-    <row r="52" spans="2:29" ht="99" x14ac:dyDescent="0.7">
+      <c r="Z51" s="1"/>
+      <c r="AD51" s="1"/>
+    </row>
+    <row r="52" spans="2:30" ht="99" x14ac:dyDescent="0.7">
       <c r="B52" s="3">
         <v>2024</v>
       </c>
@@ -4709,10 +4768,10 @@
         <v>142</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>102</v>
+        <v>229</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>71</v>
@@ -4744,9 +4803,10 @@
       <c r="W52" s="3"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
-      <c r="AC52" s="1"/>
-    </row>
-    <row r="53" spans="2:29" ht="115.5" x14ac:dyDescent="0.7">
+      <c r="Z52" s="1"/>
+      <c r="AD52" s="1"/>
+    </row>
+    <row r="53" spans="2:30" ht="214.5" x14ac:dyDescent="0.7">
       <c r="B53" s="3">
         <v>2025</v>
       </c>
@@ -4765,10 +4825,10 @@
       <c r="G53" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H53" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="I53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="J53" s="3" t="s">
         <v>187</v>
       </c>
@@ -4799,9 +4859,10 @@
       <c r="W53" s="3"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
-      <c r="AC53" s="1"/>
-    </row>
-    <row r="54" spans="2:29" ht="66" x14ac:dyDescent="0.7">
+      <c r="Z53" s="1"/>
+      <c r="AD53" s="1"/>
+    </row>
+    <row r="54" spans="2:30" ht="66" x14ac:dyDescent="0.7">
       <c r="B54" s="3">
         <v>2026</v>
       </c>
@@ -4816,10 +4877,10 @@
         <v>185</v>
       </c>
       <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3" t="s">
+      <c r="H54" s="3" t="s">
         <v>208</v>
       </c>
+      <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3" t="s">
@@ -4842,9 +4903,10 @@
       <c r="W54" s="3"/>
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
-      <c r="AC54" s="1"/>
-    </row>
-    <row r="55" spans="2:29" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="Z54" s="1"/>
+      <c r="AD54" s="1"/>
+    </row>
+    <row r="55" spans="2:30" ht="99" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
         <v>153</v>
       </c>
@@ -4857,10 +4919,10 @@
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3" t="s">
+      <c r="H55" s="3" t="s">
         <v>207</v>
       </c>
+      <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
         <v>150</v>
       </c>
@@ -4885,19 +4947,20 @@
       <c r="W55" s="3"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
-      <c r="AC55" s="1"/>
-    </row>
-    <row r="56" spans="2:29" x14ac:dyDescent="0.7">
+      <c r="Z55" s="1"/>
+      <c r="AD55" s="1"/>
+    </row>
+    <row r="56" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3" t="s">
+      <c r="H56" s="3" t="s">
         <v>97</v>
       </c>
+      <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
@@ -4914,8 +4977,9 @@
       <c r="W56" s="3"/>
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
+      <c r="Z56" s="1"/>
       <c r="AA56"/>
-      <c r="AC56" s="1"/>
+      <c r="AD56" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -4929,17 +4993,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E1BF3CE-E2E1-4863-A741-2B6FD3C7028A}">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="15.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.6875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A2" s="1" cm="1">
         <f t="array" ref="A2">SUMPRODUCT(
   IF(LEN(A5:A1001)=0, 0,
@@ -4950,343 +5015,424 @@
       </c>
       <c r="B2" s="1">
         <f>SUM(C2:RX2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.7">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" cm="1">
+        <f t="array" ref="C2">SUMPRODUCT(
+  IF(LEN(C5:C1001)=0, 0,
+     LEN(C5:C1001) - LEN(SUBSTITUTE(C5:C1001, CHAR(10), "")) + 1
+  )
+)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" s="2" t="s">
         <v>168</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A5" s="3"/>
       <c r="B5" s="3">
         <v>1977</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A6" s="3"/>
       <c r="B6" s="3">
         <v>1978</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A7" s="3"/>
       <c r="B7" s="3">
         <v>1979</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A8" s="3"/>
       <c r="B8" s="3">
         <v>1980</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A9" s="3"/>
       <c r="B9" s="3">
         <v>1981</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A10" s="3"/>
       <c r="B10" s="3">
         <v>1982</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A11" s="3"/>
       <c r="B11" s="3">
         <v>1983</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A12" s="3"/>
       <c r="B12" s="3">
         <v>1984</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A13" s="3"/>
       <c r="B13" s="3">
         <v>1985</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A14" s="3"/>
       <c r="B14" s="3">
         <v>1986</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A15" s="3"/>
       <c r="B15" s="3">
         <v>1987</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A16" s="3"/>
       <c r="B16" s="3">
         <v>1988</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C16" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A17" s="3"/>
       <c r="B17" s="3">
         <v>1989</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A18" s="3"/>
       <c r="B18" s="3">
         <v>1990</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A19" s="3"/>
       <c r="B19" s="3">
         <v>1991</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A20" s="3"/>
       <c r="B20" s="3">
         <v>1992</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A21" s="3"/>
       <c r="B21" s="3">
         <v>1993</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A22" s="3"/>
       <c r="B22" s="3">
         <v>1994</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A23" s="3"/>
       <c r="B23" s="3">
         <v>1995</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A24" s="3"/>
       <c r="B24" s="3">
         <v>1996</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A25" s="3"/>
       <c r="B25" s="3">
         <v>1997</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A26" s="3"/>
       <c r="B26" s="3">
         <v>1998</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A27" s="3"/>
       <c r="B27" s="3">
         <v>1999</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A28" s="3"/>
       <c r="B28" s="3">
         <v>2000</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A29" s="3"/>
       <c r="B29" s="3">
         <v>2001</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C29" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A30" s="3"/>
       <c r="B30" s="3">
         <v>2002</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A31" s="3"/>
       <c r="B31" s="3">
         <v>2003</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A32" s="3"/>
       <c r="B32" s="3">
         <v>2004</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A33" s="3"/>
       <c r="B33" s="3">
         <v>2005</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A34" s="3" t="s">
         <v>146</v>
       </c>
       <c r="B34" s="3">
         <v>2006</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A35" s="3"/>
       <c r="B35" s="3">
         <v>2007</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A36" s="3"/>
       <c r="B36" s="3">
         <v>2008</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A37" s="3"/>
       <c r="B37" s="3">
         <v>2009</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A38" s="3"/>
       <c r="B38" s="3">
         <v>2010</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A39" s="3"/>
       <c r="B39" s="3">
         <v>2011</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A40" s="3"/>
       <c r="B40" s="3">
         <v>2012</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A41" s="3" t="s">
         <v>157</v>
       </c>
       <c r="B41" s="3">
         <v>2013</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A42" s="3"/>
       <c r="B42" s="3">
         <v>2014</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A43" s="3"/>
       <c r="B43" s="3">
         <v>2015</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A44" s="3"/>
       <c r="B44" s="3">
         <v>2016</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C44" s="3"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A45" s="3"/>
       <c r="B45" s="3">
         <v>2017</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C45" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A46" s="3"/>
       <c r="B46" s="3">
         <v>2018</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A47" s="3"/>
       <c r="B47" s="3">
         <v>2019</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C47" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A48" s="3"/>
       <c r="B48" s="3">
         <v>2020</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C48" s="3"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A49" s="3"/>
       <c r="B49" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C49" s="3"/>
+    </row>
+    <row r="50" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A50" s="3" t="s">
         <v>145</v>
       </c>
       <c r="B50" s="3">
         <v>2022</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C50" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A51" s="3"/>
       <c r="B51" s="3">
         <v>2023</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C51" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A52" s="3" t="s">
         <v>143</v>
       </c>
       <c r="B52" s="3">
         <v>2024</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C52" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="C53" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A54" s="3" t="s">
         <v>169</v>
       </c>
       <c r="B54" s="3">
         <v>2026</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="C54" s="3"/>
+    </row>
+    <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
         <v>186</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="C55" s="3"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3607A437-C2AF-47F4-9BB2-107009A32924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5542A9C-0CB5-4633-AA23-54167F3DC780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="233">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1019,26 +1019,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>若菜きらり(IR,V)
-緋彩ませ(HCC)</t>
-    <rPh sb="0" eb="2">
-      <t>ワカナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>若菜きらり(IR,V)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>海乃月雫(IR,V)
-しのせ愛梨紗(HCC・飛鳥兼任)</t>
-    <rPh sb="0" eb="4">
-      <t>ウミノツキナ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ケンニン</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1212,11 +1193,6 @@
   </si>
   <si>
     <t>神嵜志音</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>天咲光由
-ボジラ</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1768,6 +1744,44 @@
   </si>
   <si>
     <t>Anna</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天咲光由
+ボジラ(休)</t>
+    <rPh sb="9" eb="10">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>若菜きらり(IR)
+緋彩ませ(HCC)</t>
+    <rPh sb="0" eb="2">
+      <t>ワカナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>海乃月雫(IR)
+しのせ愛梨紗(HCC・飛鳥兼任)</t>
+    <rPh sb="0" eb="4">
+      <t>ウミノツキナ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ケンニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>優華(IR)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>みなみ飛香(IR)</t>
+    <rPh sb="3" eb="5">
+      <t>ヒカ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2709,24 +2723,24 @@
     <col min="3" max="3" width="22.5625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.3125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.75" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.5625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.8125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.8125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.6875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="23.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.4375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="28.375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.3125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.5625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.9375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="30.375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.3125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.3125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.9375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.9375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="30.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="21.3125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="30.25" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="21.1875" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="30.0625" style="1" bestFit="1" customWidth="1"/>
@@ -2988,7 +3002,7 @@
         <v>48</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>17</v>
@@ -3268,7 +3282,7 @@
       <c r="Z12" s="1"/>
       <c r="AD12" s="1"/>
     </row>
-    <row r="13" spans="1:30" ht="33" x14ac:dyDescent="0.7">
+    <row r="13" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B13" s="3">
         <v>1985</v>
       </c>
@@ -3612,10 +3626,10 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
@@ -3647,7 +3661,7 @@
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
@@ -3722,7 +3736,7 @@
       <c r="Z26" s="1"/>
       <c r="AD26" s="1"/>
     </row>
-    <row r="27" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+    <row r="27" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B27" s="3">
         <v>1999</v>
       </c>
@@ -3826,7 +3840,7 @@
       <c r="Z29" s="1"/>
       <c r="AD29" s="1"/>
     </row>
-    <row r="30" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+    <row r="30" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B30" s="3">
         <v>2002</v>
       </c>
@@ -3903,7 +3917,7 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
@@ -3917,14 +3931,14 @@
         <v>56</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
       <c r="AD32" s="1"/>
     </row>
-    <row r="33" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
+    <row r="33" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B33" s="3">
         <v>2005</v>
       </c>
@@ -3967,7 +3981,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -3977,7 +3991,7 @@
         <v>84</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
@@ -4037,13 +4051,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4063,7 +4077,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
@@ -4178,7 +4192,7 @@
       <c r="Z39" s="1"/>
       <c r="AD39" s="1"/>
     </row>
-    <row r="40" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+    <row r="40" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B40" s="3">
         <v>2012</v>
       </c>
@@ -4216,7 +4230,7 @@
         <v>89</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="W40" s="3"/>
       <c r="X40" s="1"/>
@@ -4229,7 +4243,7 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
@@ -4237,7 +4251,7 @@
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>157</v>
+        <v>231</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4250,7 +4264,7 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
@@ -4261,19 +4275,19 @@
         <v>128</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
       <c r="AD41" s="1"/>
     </row>
-    <row r="42" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
+    <row r="42" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B42" s="3">
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4296,10 +4310,10 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="W42" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
@@ -4311,7 +4325,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4339,7 +4353,7 @@
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
@@ -4351,7 +4365,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>22</v>
@@ -4379,19 +4393,19 @@
         <v>111</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
       <c r="AD44" s="1"/>
     </row>
-    <row r="45" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
+    <row r="45" spans="2:30" ht="33" x14ac:dyDescent="0.7">
       <c r="B45" s="3">
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4413,13 +4427,13 @@
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
@@ -4436,12 +4450,12 @@
       <c r="Z45" s="1"/>
       <c r="AD45" s="1"/>
     </row>
-    <row r="46" spans="2:30" ht="148.5" x14ac:dyDescent="0.7">
+    <row r="46" spans="2:30" ht="115.5" x14ac:dyDescent="0.7">
       <c r="B46" s="3">
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>139</v>
@@ -4450,7 +4464,7 @@
         <v>130</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
@@ -4462,7 +4476,7 @@
         <v>65</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
@@ -4480,10 +4494,10 @@
         <v>91</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
@@ -4495,7 +4509,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4510,7 +4524,7 @@
         <v>21</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>66</v>
@@ -4533,14 +4547,14 @@
         <v>141</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
       <c r="AD47" s="1"/>
     </row>
-    <row r="48" spans="2:30" ht="66" x14ac:dyDescent="0.7">
+    <row r="48" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B48" s="3">
         <v>2020</v>
       </c>
@@ -4572,17 +4586,17 @@
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
       <c r="AD48" s="1"/>
     </row>
-    <row r="49" spans="2:30" ht="99" x14ac:dyDescent="0.7">
+    <row r="49" spans="2:30" ht="66" x14ac:dyDescent="0.7">
       <c r="B49" s="3">
         <v>2021</v>
       </c>
@@ -4590,16 +4604,16 @@
         <v>47</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>26</v>
@@ -4639,7 +4653,7 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>171</v>
+        <v>228</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>133</v>
@@ -4651,7 +4665,7 @@
         <v>132</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>144</v>
+        <v>230</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3" t="s">
@@ -4666,7 +4680,7 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -4681,7 +4695,7 @@
         <v>136</v>
       </c>
       <c r="W50" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
@@ -4696,16 +4710,16 @@
         <v>23</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3" t="s">
@@ -4734,14 +4748,14 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
@@ -4765,26 +4779,26 @@
         <v>121</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>142</v>
+        <v>229</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>102</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>71</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>103</v>
       </c>
       <c r="M52" s="3"/>
       <c r="N52" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
@@ -4798,7 +4812,7 @@
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="W52" s="3"/>
       <c r="X52" s="1"/>
@@ -4806,43 +4820,43 @@
       <c r="Z52" s="1"/>
       <c r="AD52" s="1"/>
     </row>
-    <row r="53" spans="2:30" ht="214.5" x14ac:dyDescent="0.7">
+    <row r="53" spans="2:30" ht="115.5" x14ac:dyDescent="0.7">
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D53" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>93</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -4850,11 +4864,11 @@
         <v>115</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="1"/>
@@ -4868,29 +4882,29 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
@@ -4898,7 +4912,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="W54" s="3"/>
       <c r="X54" s="1"/>
@@ -4906,34 +4920,34 @@
       <c r="Z54" s="1"/>
       <c r="AD54" s="1"/>
     </row>
-    <row r="55" spans="2:30" ht="99" x14ac:dyDescent="0.7">
+    <row r="55" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
@@ -4942,7 +4956,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="W55" s="3"/>
       <c r="X55" s="1"/>
@@ -5031,7 +5045,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -5251,7 +5265,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A34" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B34" s="3">
         <v>2006</v>
@@ -5302,7 +5316,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A41" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B41" s="3">
         <v>2013</v>
@@ -5371,7 +5385,7 @@
     </row>
     <row r="50" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A50" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B50" s="3">
         <v>2022</v>
@@ -5391,29 +5405,29 @@
     </row>
     <row r="52" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A52" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B52" s="3">
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A54" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B54" s="3">
         <v>2026</v>
@@ -5422,10 +5436,10 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C55" s="3"/>
     </row>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5542A9C-0CB5-4633-AA23-54167F3DC780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC5566B-F97F-4DB3-87E4-C0BDB10B2A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="234">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1782,6 +1782,11 @@
     <rPh sb="3" eb="5">
       <t>ヒカ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;あんり&gt;
+&lt;鈴夏&gt;(すずか)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2772,7 +2777,7 @@
     <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2804,7 +2809,7 @@
      LEN(F5:F1001) - LEN(SUBSTITUTE(F5:F1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" cm="1">
         <f t="array" ref="G2">SUMPRODUCT(
@@ -4931,7 +4936,9 @@
       <c r="E55" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F55" s="3"/>
+      <c r="F55" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
         <v>204</v>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC5566B-F97F-4DB3-87E4-C0BDB10B2A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8273FA-6B82-4620-9389-112F9E2E0FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1249,27 +1249,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>星ハム子(IR)(休)</t>
-    <rPh sb="0" eb="1">
-      <t>ホシ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>コ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>松本都
-藤本つかさ(休)</t>
-    <rPh sb="0" eb="2">
-      <t>マツモト</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ミヤコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>柳川澄樺
 神姫楽ミサ</t>
     <phoneticPr fontId="1"/>
@@ -1787,6 +1766,30 @@
   <si>
     <t>&lt;あんり&gt;
 &lt;鈴夏&gt;(すずか)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>松本都</t>
+    <rPh sb="0" eb="2">
+      <t>マツモト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミヤコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>星ハム子(IR)(休)
+藤本つかさ(休8.15復帰)</t>
+    <rPh sb="0" eb="1">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>フッキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1872,26 +1875,6 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="24">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2014,6 +1997,26 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Noto Serif JP SemiBold"/>
+        <family val="1"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2383,21 +2386,21 @@
     <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリゴ" dataDxfId="17"/>
     <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ" dataDxfId="16"/>
     <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="15"/>
-    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="0"/>
-    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="14"/>
-    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="13"/>
-    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="12"/>
-    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="11"/>
-    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="10"/>
-    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="9"/>
-    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="8"/>
-    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="4"/>
-    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="1"/>
+    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="14"/>
+    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="13"/>
+    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="12"/>
+    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="11"/>
+    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="10"/>
+    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="9"/>
+    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="8"/>
+    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="7"/>
+    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="3"/>
+    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2817,7 +2820,7 @@
      LEN(G5:G1001) - LEN(SUBSTITUTE(G5:G1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="1" cm="1">
         <f t="array" ref="H2">SUMPRODUCT(
@@ -2937,7 +2940,7 @@
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="W2" s="1" cm="1">
         <f t="array" ref="W2">SUMPRODUCT(
@@ -3634,7 +3637,7 @@
         <v>154</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
@@ -3922,7 +3925,7 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
@@ -3936,7 +3939,7 @@
         <v>56</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
@@ -3986,7 +3989,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -3996,7 +3999,7 @@
         <v>84</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
@@ -4062,7 +4065,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>176</v>
+        <v>233</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4082,7 +4085,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>177</v>
+        <v>232</v>
       </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
@@ -4248,7 +4251,7 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
@@ -4256,7 +4259,7 @@
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4269,7 +4272,7 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
@@ -4280,7 +4283,7 @@
         <v>128</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
@@ -4315,7 +4318,7 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>173</v>
@@ -4358,7 +4361,7 @@
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
@@ -4398,7 +4401,7 @@
         <v>111</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
@@ -4438,7 +4441,7 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
@@ -4460,7 +4463,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>139</v>
@@ -4469,7 +4472,7 @@
         <v>130</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
@@ -4481,7 +4484,7 @@
         <v>65</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
@@ -4499,10 +4502,10 @@
         <v>91</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
@@ -4552,7 +4555,7 @@
         <v>141</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
@@ -4591,10 +4594,10 @@
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
@@ -4609,16 +4612,16 @@
         <v>47</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>26</v>
@@ -4658,7 +4661,7 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>133</v>
@@ -4670,7 +4673,7 @@
         <v>132</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3" t="s">
@@ -4718,10 +4721,10 @@
         <v>164</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>163</v>
@@ -4753,14 +4756,14 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
@@ -4784,19 +4787,19 @@
         <v>121</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>102</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>71</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>103</v>
@@ -4817,7 +4820,7 @@
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="W52" s="3"/>
       <c r="X52" s="1"/>
@@ -4833,23 +4836,23 @@
         <v>169</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>150</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>93</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
@@ -4858,10 +4861,10 @@
         <v>160</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -4873,7 +4876,7 @@
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="1"/>
@@ -4887,29 +4890,29 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>168</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
@@ -4917,7 +4920,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="W54" s="3"/>
       <c r="X54" s="1"/>
@@ -4931,17 +4934,17 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
@@ -4950,7 +4953,7 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3" t="s">
@@ -4963,7 +4966,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="W55" s="3"/>
       <c r="X55" s="1"/>
@@ -5423,7 +5426,7 @@
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
@@ -5443,7 +5446,7 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>151</v>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8273FA-6B82-4620-9389-112F9E2E0FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0529BC7-CB01-4AD2-8905-7DD9342E9058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1638,13 +1638,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>藍川はるか</t>
-    <rPh sb="0" eb="2">
-      <t>アイカワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>吏南
 妃南
 鈴季すず
@@ -1789,6 +1782,14 @@
     </rPh>
     <rPh sb="23" eb="25">
       <t>フッキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>藍川はるか
+ノア・ヒカリ</t>
+    <rPh sb="0" eb="2">
+      <t>アイカワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2780,7 +2781,7 @@
     <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2824,131 +2825,131 @@
       </c>
       <c r="H2" s="1" cm="1">
         <f t="array" ref="H2">SUMPRODUCT(
+  IF(LEN(H5:H1001)=0, 0,
+     LEN(H5:H1001) - LEN(SUBSTITUTE(H5:H1001, CHAR(10), "")) + 1
+  )
+)</f>
+        <v>12</v>
+      </c>
+      <c r="I2" s="1" cm="1">
+        <f t="array" ref="I2">SUMPRODUCT(
   IF(LEN(I5:I1001)=0, 0,
      LEN(I5:I1001) - LEN(SUBSTITUTE(I5:I1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>11</v>
       </c>
-      <c r="I2" s="1" cm="1">
-        <f t="array" ref="I2">SUMPRODUCT(
+      <c r="J2" s="1" cm="1">
+        <f t="array" ref="J2">SUMPRODUCT(
   IF(LEN(J5:J1001)=0, 0,
      LEN(J5:J1001) - LEN(SUBSTITUTE(J5:J1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>11</v>
       </c>
-      <c r="J2" s="1" cm="1">
-        <f t="array" ref="J2">SUMPRODUCT(
+      <c r="K2" s="1" cm="1">
+        <f t="array" ref="K2">SUMPRODUCT(
   IF(LEN(K5:K1001)=0, 0,
      LEN(K5:K1001) - LEN(SUBSTITUTE(K5:K1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>10</v>
       </c>
-      <c r="K2" s="1" cm="1">
-        <f t="array" ref="K2">SUMPRODUCT(
+      <c r="L2" s="1" cm="1">
+        <f t="array" ref="L2">SUMPRODUCT(
   IF(LEN(L5:L1001)=0, 0,
      LEN(L5:L1001) - LEN(SUBSTITUTE(L5:L1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>10</v>
       </c>
-      <c r="L2" s="1" cm="1">
-        <f t="array" ref="L2">SUMPRODUCT(
+      <c r="M2" s="1" cm="1">
+        <f t="array" ref="M2">SUMPRODUCT(
   IF(LEN(M5:M1001)=0, 0,
      LEN(M5:M1001) - LEN(SUBSTITUTE(M5:M1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>11</v>
       </c>
-      <c r="M2" s="1" cm="1">
-        <f t="array" ref="M2">SUMPRODUCT(
+      <c r="N2" s="1" cm="1">
+        <f t="array" ref="N2">SUMPRODUCT(
   IF(LEN(N5:N1001)=0, 0,
      LEN(N5:N1001) - LEN(SUBSTITUTE(N5:N1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>9</v>
       </c>
-      <c r="N2" s="1" cm="1">
-        <f t="array" ref="N2">SUMPRODUCT(
+      <c r="O2" s="1" cm="1">
+        <f t="array" ref="O2">SUMPRODUCT(
   IF(LEN(O5:O1001)=0, 0,
      LEN(O5:O1001) - LEN(SUBSTITUTE(O5:O1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>7</v>
       </c>
-      <c r="O2" s="1" cm="1">
-        <f t="array" ref="O2">SUMPRODUCT(
+      <c r="P2" s="1" cm="1">
+        <f t="array" ref="P2">SUMPRODUCT(
   IF(LEN(P5:P1001)=0, 0,
      LEN(P5:P1001) - LEN(SUBSTITUTE(P5:P1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>6</v>
       </c>
-      <c r="P2" s="1" cm="1">
-        <f t="array" ref="P2">SUMPRODUCT(
+      <c r="Q2" s="1" cm="1">
+        <f t="array" ref="Q2">SUMPRODUCT(
   IF(LEN(Q5:Q1001)=0, 0,
      LEN(Q5:Q1001) - LEN(SUBSTITUTE(Q5:Q1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="Q2" s="1" cm="1">
-        <f t="array" ref="Q2">SUMPRODUCT(
+      <c r="R2" s="1" cm="1">
+        <f t="array" ref="R2">SUMPRODUCT(
   IF(LEN(R5:R1001)=0, 0,
      LEN(R5:R1001) - LEN(SUBSTITUTE(R5:R1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="R2" s="1" cm="1">
-        <f t="array" ref="R2">SUMPRODUCT(
+      <c r="S2" s="1" cm="1">
+        <f t="array" ref="S2">SUMPRODUCT(
   IF(LEN(S5:S1001)=0, 0,
      LEN(S5:S1001) - LEN(SUBSTITUTE(S5:S1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="S2" s="1" cm="1">
-        <f t="array" ref="S2">SUMPRODUCT(
+      <c r="T2" s="1" cm="1">
+        <f t="array" ref="T2">SUMPRODUCT(
   IF(LEN(T5:T1001)=0, 0,
      LEN(T5:T1001) - LEN(SUBSTITUTE(T5:T1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="T2" s="1" cm="1">
-        <f t="array" ref="T2">SUMPRODUCT(
+      <c r="U2" s="1" cm="1">
+        <f t="array" ref="U2">SUMPRODUCT(
   IF(LEN(U5:U1001)=0, 0,
      LEN(U5:U1001) - LEN(SUBSTITUTE(U5:U1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>8</v>
       </c>
-      <c r="U2" s="1" cm="1">
-        <f t="array" ref="U2">SUMPRODUCT(
+      <c r="V2" s="1" cm="1">
+        <f t="array" ref="V2">SUMPRODUCT(
   IF(LEN(V5:V1001)=0, 0,
      LEN(V5:V1001) - LEN(SUBSTITUTE(V5:V1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>53</v>
       </c>
-      <c r="V2" s="1" cm="1">
-        <f t="array" ref="V2">SUMPRODUCT(
+      <c r="W2" s="1" cm="1">
+        <f t="array" ref="W2">SUMPRODUCT(
   IF(LEN(W5:W1001)=0, 0,
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>50</v>
-      </c>
-      <c r="W2" s="1" cm="1">
-        <f t="array" ref="W2">SUMPRODUCT(
-  IF(LEN(X5:X1001)=0, 0,
-     LEN(X5:X1001) - LEN(SUBSTITUTE(X5:X1001, CHAR(10), "")) + 1
-  )
-)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
@@ -3989,7 +3990,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -4065,7 +4066,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4085,7 +4086,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
@@ -4259,7 +4260,7 @@
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4463,7 +4464,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>139</v>
@@ -4505,7 +4506,7 @@
         <v>215</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
@@ -4661,7 +4662,7 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>133</v>
@@ -4673,7 +4674,7 @@
         <v>132</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3" t="s">
@@ -4756,7 +4757,7 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
@@ -4787,13 +4788,13 @@
         <v>121</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>102</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>71</v>
@@ -4836,20 +4837,20 @@
         <v>169</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>150</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>93</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>182</v>
@@ -4890,7 +4891,7 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>168</v>
@@ -4920,7 +4921,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="W54" s="3"/>
       <c r="X54" s="1"/>
@@ -4940,7 +4941,7 @@
         <v>201</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -4953,7 +4954,7 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3" t="s">

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0529BC7-CB01-4AD2-8905-7DD9342E9058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE180D5-10A1-4978-9C92-38CF9F47855F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1486,11 +1486,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;ユウカ&gt;(仮)
-&lt;さとうもも&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>&lt;州王叶多&gt;(すおうかなた, プロテスト合格)</t>
     <rPh sb="1" eb="2">
       <t>ス</t>
@@ -1790,6 +1785,14 @@
 ノア・ヒカリ</t>
     <rPh sb="0" eb="2">
       <t>アイカワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;ユウカ&gt;(仮)
+&lt;さとうもも&gt;(7/18デビュー予定)</t>
+    <rPh sb="25" eb="27">
+      <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3990,7 +3993,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -4000,7 +4003,7 @@
         <v>84</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
@@ -4066,7 +4069,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4086,7 +4089,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
@@ -4260,7 +4263,7 @@
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4402,7 +4405,7 @@
         <v>111</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
@@ -4442,7 +4445,7 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
@@ -4464,7 +4467,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>139</v>
@@ -4473,7 +4476,7 @@
         <v>130</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
@@ -4503,10 +4506,10 @@
         <v>91</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
@@ -4595,7 +4598,7 @@
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>176</v>
@@ -4662,7 +4665,7 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>133</v>
@@ -4674,7 +4677,7 @@
         <v>132</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3" t="s">
@@ -4722,7 +4725,7 @@
         <v>164</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>189</v>
@@ -4757,14 +4760,14 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
         <v>195</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
@@ -4788,13 +4791,13 @@
         <v>121</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>102</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>71</v>
@@ -4837,20 +4840,20 @@
         <v>169</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>150</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>93</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>182</v>
@@ -4862,10 +4865,10 @@
         <v>160</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -4877,7 +4880,7 @@
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="1"/>
@@ -4891,7 +4894,7 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>168</v>
@@ -4901,7 +4904,7 @@
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
@@ -4921,7 +4924,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="W54" s="3"/>
       <c r="X54" s="1"/>
@@ -4935,17 +4938,17 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
@@ -4954,7 +4957,7 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3" t="s">
